--- a/artfynd/A 13728-2025 artfynd.xlsx
+++ b/artfynd/A 13728-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,6 +782,113 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123524582</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78775</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Andljusbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>459844</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6808666</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Garnlav så långt jag kan se i en radie av ca 50 meter.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13728-2025 artfynd.xlsx
+++ b/artfynd/A 13728-2025 artfynd.xlsx
@@ -1462,7 +1462,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123543499</v>
+        <v>123547258</v>
       </c>
       <c r="B9" t="n">
         <v>78775</v>
@@ -1498,17 +1498,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459677</v>
+        <v>458828</v>
       </c>
       <c r="R9" t="n">
-        <v>6808949</v>
+        <v>6809065</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,12 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På Gran blandat med skägglav</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,22 +1562,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123543087</v>
+        <v>123546537</v>
       </c>
       <c r="B10" t="n">
-        <v>78775</v>
+        <v>78511</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,37 +1590,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459627</v>
+        <v>459128</v>
       </c>
       <c r="R10" t="n">
-        <v>6808925</v>
+        <v>6808999</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1654,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1664,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1679,19 +1674,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123547258</v>
+        <v>123543087</v>
       </c>
       <c r="B11" t="n">
         <v>78775</v>
@@ -1727,17 +1722,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458828</v>
+        <v>459627</v>
       </c>
       <c r="R11" t="n">
-        <v>6809065</v>
+        <v>6808925</v>
       </c>
       <c r="S11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1766,7 +1761,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1776,7 +1771,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,22 +1786,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123546537</v>
+        <v>123543499</v>
       </c>
       <c r="B12" t="n">
-        <v>78511</v>
+        <v>78775</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1819,34 +1814,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459128</v>
+        <v>459677</v>
       </c>
       <c r="R12" t="n">
-        <v>6808999</v>
+        <v>6808949</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1878,7 +1873,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1888,7 +1883,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På Gran blandat med skägglav</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2149,10 +2149,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123542950</v>
+        <v>123549099</v>
       </c>
       <c r="B15" t="n">
-        <v>57481</v>
+        <v>78775</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2165,41 +2165,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459697</v>
+        <v>459197</v>
       </c>
       <c r="R15" t="n">
-        <v>6808925</v>
+        <v>6808824</v>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2228,7 +2224,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2238,7 +2234,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,19 +2249,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123543363</v>
+        <v>123549137</v>
       </c>
       <c r="B16" t="n">
         <v>78775</v>
@@ -2305,10 +2301,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459631</v>
+        <v>459240</v>
       </c>
       <c r="R16" t="n">
-        <v>6808926</v>
+        <v>6808796</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2340,7 +2336,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2350,7 +2346,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2377,10 +2373,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123548423</v>
+        <v>123542950</v>
       </c>
       <c r="B17" t="n">
-        <v>78511</v>
+        <v>57481</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2393,37 +2389,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459082</v>
+        <v>459697</v>
       </c>
       <c r="R17" t="n">
-        <v>6808839</v>
+        <v>6808925</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,19 +2477,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123549099</v>
+        <v>123543363</v>
       </c>
       <c r="B18" t="n">
         <v>78775</v>
@@ -2525,17 +2525,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459197</v>
+        <v>459631</v>
       </c>
       <c r="R18" t="n">
-        <v>6808824</v>
+        <v>6808926</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,22 +2589,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123549137</v>
+        <v>123548423</v>
       </c>
       <c r="B19" t="n">
-        <v>78775</v>
+        <v>78511</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2617,37 +2617,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459240</v>
+        <v>459082</v>
       </c>
       <c r="R19" t="n">
-        <v>6808796</v>
+        <v>6808839</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,12 +2701,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123543848</v>
+        <v>123546440</v>
       </c>
       <c r="B24" t="n">
-        <v>78775</v>
+        <v>78512</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3182,21 +3182,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3206,13 +3206,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459556</v>
+        <v>459563</v>
       </c>
       <c r="R24" t="n">
-        <v>6808951</v>
+        <v>6808917</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3266,19 +3266,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123543842</v>
+        <v>123549730</v>
       </c>
       <c r="B25" t="n">
         <v>78775</v>
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459608</v>
+        <v>459461</v>
       </c>
       <c r="R25" t="n">
-        <v>6809012</v>
+        <v>6808868</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3363,12 +3363,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På Gran</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3395,10 +3390,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123546440</v>
+        <v>123549170</v>
       </c>
       <c r="B26" t="n">
-        <v>78512</v>
+        <v>78775</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3411,37 +3406,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459563</v>
+        <v>459062</v>
       </c>
       <c r="R26" t="n">
-        <v>6808917</v>
+        <v>6808854</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3470,7 +3465,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3480,7 +3475,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3507,7 +3502,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123549730</v>
+        <v>123543848</v>
       </c>
       <c r="B27" t="n">
         <v>78775</v>
@@ -3547,13 +3542,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459461</v>
+        <v>459556</v>
       </c>
       <c r="R27" t="n">
-        <v>6808868</v>
+        <v>6808951</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3582,7 +3577,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3592,7 +3587,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3607,19 +3602,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123549170</v>
+        <v>123543842</v>
       </c>
       <c r="B28" t="n">
         <v>78775</v>
@@ -3655,17 +3650,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459062</v>
+        <v>459608</v>
       </c>
       <c r="R28" t="n">
-        <v>6808854</v>
+        <v>6809012</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3694,7 +3689,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3704,7 +3699,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3719,12 +3719,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4301,7 +4301,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123549200</v>
+        <v>123549662</v>
       </c>
       <c r="B34" t="n">
         <v>78775</v>
@@ -4341,13 +4341,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459265</v>
+        <v>459479</v>
       </c>
       <c r="R34" t="n">
-        <v>6808827</v>
+        <v>6808853</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4401,19 +4401,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123549662</v>
+        <v>123545274</v>
       </c>
       <c r="B35" t="n">
         <v>78775</v>
@@ -4449,17 +4449,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459479</v>
+        <v>459304</v>
       </c>
       <c r="R35" t="n">
-        <v>6808853</v>
+        <v>6809019</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4513,19 +4513,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123545274</v>
+        <v>123549200</v>
       </c>
       <c r="B36" t="n">
         <v>78775</v>
@@ -4561,17 +4561,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459304</v>
+        <v>459265</v>
       </c>
       <c r="R36" t="n">
-        <v>6809019</v>
+        <v>6808827</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4625,12 +4625,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -6890,10 +6890,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123549577</v>
+        <v>123543718</v>
       </c>
       <c r="B57" t="n">
-        <v>78775</v>
+        <v>57481</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6906,37 +6906,45 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459420</v>
+        <v>459695</v>
       </c>
       <c r="R57" t="n">
-        <v>6808812</v>
+        <v>6808940</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6965,7 +6973,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6975,7 +6983,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack i gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6990,22 +7003,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123543718</v>
+        <v>123549577</v>
       </c>
       <c r="B58" t="n">
-        <v>57481</v>
+        <v>78775</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7018,45 +7031,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459695</v>
+        <v>459420</v>
       </c>
       <c r="R58" t="n">
-        <v>6808940</v>
+        <v>6808812</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7085,7 +7090,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7095,12 +7100,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack i gran</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7115,12 +7115,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7249,10 +7249,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123543992</v>
+        <v>123549477</v>
       </c>
       <c r="B60" t="n">
-        <v>78775</v>
+        <v>78512</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7265,37 +7265,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459530</v>
+        <v>459062</v>
       </c>
       <c r="R60" t="n">
-        <v>6809029</v>
+        <v>6808854</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7349,22 +7349,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123549477</v>
+        <v>123547657</v>
       </c>
       <c r="B61" t="n">
-        <v>78512</v>
+        <v>56691</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7373,41 +7373,49 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459062</v>
+        <v>459003</v>
       </c>
       <c r="R61" t="n">
-        <v>6808854</v>
+        <v>6808929</v>
       </c>
       <c r="S61" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7436,7 +7444,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7446,7 +7454,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Betestall., spillning från höna</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7461,22 +7474,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123547657</v>
+        <v>123543992</v>
       </c>
       <c r="B62" t="n">
-        <v>56691</v>
+        <v>78775</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7485,46 +7498,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459003</v>
+        <v>459530</v>
       </c>
       <c r="R62" t="n">
-        <v>6808929</v>
+        <v>6809029</v>
       </c>
       <c r="S62" t="n">
         <v>9</v>
@@ -7556,7 +7561,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7566,12 +7571,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Betestall., spillning från höna</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -11913,10 +11913,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123564034</v>
+        <v>123568223</v>
       </c>
       <c r="B101" t="n">
-        <v>78775</v>
+        <v>74869</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11929,21 +11929,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11953,10 +11953,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>459721</v>
+        <v>459796</v>
       </c>
       <c r="R101" t="n">
-        <v>6808937</v>
+        <v>6808830</v>
       </c>
       <c r="S101" t="n">
         <v>9</v>
@@ -11988,7 +11988,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12025,10 +12025,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123568223</v>
+        <v>123573768</v>
       </c>
       <c r="B102" t="n">
-        <v>74869</v>
+        <v>78775</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12041,34 +12041,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>459796</v>
+        <v>459699</v>
       </c>
       <c r="R102" t="n">
-        <v>6808830</v>
+        <v>6808517</v>
       </c>
       <c r="S102" t="n">
         <v>9</v>
@@ -12100,7 +12100,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12110,7 +12110,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12137,10 +12142,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123575257</v>
+        <v>123573011</v>
       </c>
       <c r="B103" t="n">
-        <v>78512</v>
+        <v>78775</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12153,37 +12158,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>459595</v>
+        <v>459739</v>
       </c>
       <c r="R103" t="n">
-        <v>6808516</v>
+        <v>6808597</v>
       </c>
       <c r="S103" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12212,7 +12217,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12222,7 +12227,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12237,22 +12242,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>123573011</v>
+        <v>123575257</v>
       </c>
       <c r="B104" t="n">
-        <v>78775</v>
+        <v>78512</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12265,37 +12270,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>459739</v>
+        <v>459595</v>
       </c>
       <c r="R104" t="n">
-        <v>6808597</v>
+        <v>6808516</v>
       </c>
       <c r="S104" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12324,7 +12329,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12334,7 +12339,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12349,19 +12354,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123573768</v>
+        <v>123564034</v>
       </c>
       <c r="B105" t="n">
         <v>78775</v>
@@ -12397,14 +12402,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>459699</v>
+        <v>459721</v>
       </c>
       <c r="R105" t="n">
-        <v>6808517</v>
+        <v>6808937</v>
       </c>
       <c r="S105" t="n">
         <v>9</v>
@@ -12436,7 +12441,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12446,12 +12451,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -14290,10 +14290,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123577958</v>
+        <v>123575827</v>
       </c>
       <c r="B122" t="n">
-        <v>79364</v>
+        <v>78512</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14306,37 +14306,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>459571</v>
+        <v>459707</v>
       </c>
       <c r="R122" t="n">
-        <v>6808546</v>
+        <v>6808935</v>
       </c>
       <c r="S122" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14375,7 +14375,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14390,22 +14390,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123573294</v>
+        <v>123566093</v>
       </c>
       <c r="B123" t="n">
-        <v>78775</v>
+        <v>78512</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14418,37 +14418,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>459753</v>
+        <v>459675</v>
       </c>
       <c r="R123" t="n">
-        <v>6808571</v>
+        <v>6808804</v>
       </c>
       <c r="S123" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14514,10 +14514,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123575840</v>
+        <v>123577958</v>
       </c>
       <c r="B124" t="n">
-        <v>78512</v>
+        <v>79364</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14530,21 +14530,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14554,13 +14554,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>459570</v>
+        <v>459571</v>
       </c>
       <c r="R124" t="n">
-        <v>6808531</v>
+        <v>6808546</v>
       </c>
       <c r="S124" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14626,7 +14626,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>123575827</v>
+        <v>123575840</v>
       </c>
       <c r="B125" t="n">
         <v>78512</v>
@@ -14662,17 +14662,17 @@
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>459707</v>
+        <v>459570</v>
       </c>
       <c r="R125" t="n">
-        <v>6808935</v>
+        <v>6808531</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14726,12 +14726,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
@@ -14855,10 +14855,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>123566093</v>
+        <v>123567939</v>
       </c>
       <c r="B127" t="n">
-        <v>78512</v>
+        <v>78775</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14871,21 +14871,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14895,13 +14895,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>459675</v>
+        <v>459726</v>
       </c>
       <c r="R127" t="n">
-        <v>6808804</v>
+        <v>6808663</v>
       </c>
       <c r="S127" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14955,19 +14955,19 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>123567939</v>
+        <v>123573294</v>
       </c>
       <c r="B128" t="n">
         <v>78775</v>
@@ -15003,17 +15003,17 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>459726</v>
+        <v>459753</v>
       </c>
       <c r="R128" t="n">
-        <v>6808663</v>
+        <v>6808571</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15052,7 +15052,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15067,12 +15067,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -15303,10 +15303,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>123573067</v>
+        <v>123564957</v>
       </c>
       <c r="B131" t="n">
-        <v>78511</v>
+        <v>78775</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15319,21 +15319,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15343,10 +15343,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>459717</v>
+        <v>459758</v>
       </c>
       <c r="R131" t="n">
-        <v>6808606</v>
+        <v>6808796</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -15378,7 +15378,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15388,7 +15388,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15415,10 +15415,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>123573487</v>
+        <v>123575835</v>
       </c>
       <c r="B132" t="n">
-        <v>78512</v>
+        <v>78775</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15431,21 +15431,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15455,13 +15455,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>459764</v>
+        <v>459553</v>
       </c>
       <c r="R132" t="n">
-        <v>6808549</v>
+        <v>6808474</v>
       </c>
       <c r="S132" t="n">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15500,7 +15500,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>På tallstammar 7st</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15515,22 +15520,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>123575835</v>
+        <v>123575648</v>
       </c>
       <c r="B133" t="n">
-        <v>78775</v>
+        <v>78512</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15543,21 +15548,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15567,10 +15572,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>459553</v>
+        <v>459612</v>
       </c>
       <c r="R133" t="n">
-        <v>6808474</v>
+        <v>6808443</v>
       </c>
       <c r="S133" t="n">
         <v>9</v>
@@ -15602,7 +15607,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15612,12 +15617,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>På tallstammar 7st</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15644,10 +15644,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>123575648</v>
+        <v>123573067</v>
       </c>
       <c r="B134" t="n">
-        <v>78512</v>
+        <v>78511</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15660,37 +15660,37 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>459612</v>
+        <v>459717</v>
       </c>
       <c r="R134" t="n">
-        <v>6808443</v>
+        <v>6808606</v>
       </c>
       <c r="S134" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15729,7 +15729,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15744,22 +15744,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>123564957</v>
+        <v>123573487</v>
       </c>
       <c r="B135" t="n">
-        <v>78775</v>
+        <v>78512</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15772,37 +15772,37 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>459758</v>
+        <v>459764</v>
       </c>
       <c r="R135" t="n">
-        <v>6808796</v>
+        <v>6808549</v>
       </c>
       <c r="S135" t="n">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15841,7 +15841,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15856,12 +15856,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -16881,10 +16881,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>123576167</v>
+        <v>123577228</v>
       </c>
       <c r="B145" t="n">
-        <v>78870</v>
+        <v>78511</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16897,37 +16897,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>967</v>
+        <v>6446</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>459499</v>
+        <v>459695</v>
       </c>
       <c r="R145" t="n">
-        <v>6808603</v>
+        <v>6808940</v>
       </c>
       <c r="S145" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16981,22 +16981,22 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>123577228</v>
+        <v>123576167</v>
       </c>
       <c r="B146" t="n">
-        <v>78511</v>
+        <v>78870</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -17009,37 +17009,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>459695</v>
+        <v>459499</v>
       </c>
       <c r="R146" t="n">
-        <v>6808940</v>
+        <v>6808603</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17078,7 +17078,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17093,12 +17093,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -22093,10 +22093,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>123568856</v>
+        <v>123549286</v>
       </c>
       <c r="B191" t="n">
-        <v>57481</v>
+        <v>56691</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -22105,46 +22105,49 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>459795</v>
+        <v>459241</v>
       </c>
       <c r="R191" t="n">
         <v>6808793</v>
       </c>
       <c r="S191" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -22168,22 +22171,27 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>Under betestall</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22198,19 +22206,19 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>123549286</v>
+        <v>123574682</v>
       </c>
       <c r="B192" t="n">
         <v>56691</v>
@@ -22258,10 +22266,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>459241</v>
+        <v>459681</v>
       </c>
       <c r="R192" t="n">
-        <v>6808793</v>
+        <v>6808458</v>
       </c>
       <c r="S192" t="n">
         <v>15</v>
@@ -22288,22 +22296,22 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC192" t="inlineStr">
@@ -22335,10 +22343,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>123574682</v>
+        <v>123568856</v>
       </c>
       <c r="B193" t="n">
-        <v>56691</v>
+        <v>57481</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -22347,49 +22355,46 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N193" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>459681</v>
+        <v>459795</v>
       </c>
       <c r="R193" t="n">
-        <v>6808458</v>
+        <v>6808793</v>
       </c>
       <c r="S193" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -22418,7 +22423,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -22428,12 +22433,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>Under betestall</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22448,12 +22448,12 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
@@ -23418,10 +23418,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>123544921</v>
+        <v>123566584</v>
       </c>
       <c r="B202" t="n">
-        <v>90931</v>
+        <v>57481</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -23430,41 +23430,43 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>459448</v>
+        <v>459754</v>
       </c>
       <c r="R202" t="n">
-        <v>6809112</v>
+        <v>6808887</v>
       </c>
       <c r="S202" t="n">
         <v>9</v>
@@ -23491,22 +23493,22 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23515,7 +23517,6 @@
       <c r="AE202" t="b">
         <v>0</v>
       </c>
-      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
@@ -23534,10 +23535,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>123566584</v>
+        <v>123544921</v>
       </c>
       <c r="B203" t="n">
-        <v>57481</v>
+        <v>90931</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23546,43 +23547,41 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>459754</v>
+        <v>459448</v>
       </c>
       <c r="R203" t="n">
-        <v>6808887</v>
+        <v>6809112</v>
       </c>
       <c r="S203" t="n">
         <v>9</v>
@@ -23609,22 +23608,22 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23633,6 +23632,7 @@
       <c r="AE203" t="b">
         <v>0</v>
       </c>
+      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13728-2025 artfynd.xlsx
+++ b/artfynd/A 13728-2025 artfynd.xlsx
@@ -3175,10 +3175,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123548646</v>
+        <v>123548439</v>
       </c>
       <c r="B24" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3191,34 +3191,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459185</v>
+        <v>459138</v>
       </c>
       <c r="R24" t="n">
-        <v>6808785</v>
+        <v>6808765</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3287,7 +3287,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123548439</v>
+        <v>123549501</v>
       </c>
       <c r="B25" t="n">
         <v>78781</v>
@@ -3323,17 +3323,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459138</v>
+        <v>459367</v>
       </c>
       <c r="R25" t="n">
-        <v>6808765</v>
+        <v>6808792</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3387,22 +3387,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123549501</v>
+        <v>123548646</v>
       </c>
       <c r="B26" t="n">
-        <v>78781</v>
+        <v>78518</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3415,37 +3415,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459367</v>
+        <v>459185</v>
       </c>
       <c r="R26" t="n">
-        <v>6808792</v>
+        <v>6808785</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3499,12 +3499,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -4868,10 +4868,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123545712</v>
+        <v>123549200</v>
       </c>
       <c r="B39" t="n">
-        <v>78876</v>
+        <v>78781</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4884,37 +4884,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459156</v>
+        <v>459265</v>
       </c>
       <c r="R39" t="n">
-        <v>6808985</v>
+        <v>6808827</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4968,19 +4968,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123549200</v>
+        <v>123549271</v>
       </c>
       <c r="B40" t="n">
         <v>78781</v>
@@ -5020,7 +5020,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459265</v>
+        <v>459269</v>
       </c>
       <c r="R40" t="n">
         <v>6808827</v>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5092,7 +5092,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123549271</v>
+        <v>123549009</v>
       </c>
       <c r="B41" t="n">
         <v>78781</v>
@@ -5128,14 +5128,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459269</v>
+        <v>459129</v>
       </c>
       <c r="R41" t="n">
-        <v>6808827</v>
+        <v>6808800</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5204,10 +5204,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123549009</v>
+        <v>123545712</v>
       </c>
       <c r="B42" t="n">
-        <v>78781</v>
+        <v>78876</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5220,21 +5220,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5244,13 +5244,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459129</v>
+        <v>459156</v>
       </c>
       <c r="R42" t="n">
-        <v>6808800</v>
+        <v>6808985</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5304,12 +5304,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5428,10 +5428,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123546479</v>
+        <v>123547657</v>
       </c>
       <c r="B44" t="n">
-        <v>78518</v>
+        <v>56697</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5440,38 +5440,46 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459128</v>
+        <v>459003</v>
       </c>
       <c r="R44" t="n">
-        <v>6808999</v>
+        <v>6808929</v>
       </c>
       <c r="S44" t="n">
         <v>9</v>
@@ -5503,7 +5511,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5513,7 +5521,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Betestall., spillning från höna</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5540,10 +5553,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123547657</v>
+        <v>123546479</v>
       </c>
       <c r="B45" t="n">
-        <v>56697</v>
+        <v>78518</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5552,46 +5565,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459003</v>
+        <v>459128</v>
       </c>
       <c r="R45" t="n">
-        <v>6808929</v>
+        <v>6808999</v>
       </c>
       <c r="S45" t="n">
         <v>9</v>
@@ -5623,7 +5628,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5633,12 +5638,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Betestall., spillning från höna</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -8168,10 +8168,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123549577</v>
+        <v>123549418</v>
       </c>
       <c r="B68" t="n">
-        <v>78781</v>
+        <v>56697</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8180,38 +8180,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>459420</v>
+        <v>459318</v>
       </c>
       <c r="R68" t="n">
-        <v>6808812</v>
+        <v>6808809</v>
       </c>
       <c r="S68" t="n">
         <v>9</v>
@@ -8243,7 +8248,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8253,7 +8258,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Under betestall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8280,7 +8290,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123548371</v>
+        <v>123549577</v>
       </c>
       <c r="B69" t="n">
         <v>78781</v>
@@ -8316,17 +8326,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>459133</v>
+        <v>459420</v>
       </c>
       <c r="R69" t="n">
-        <v>6808760</v>
+        <v>6808812</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8355,7 +8365,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8365,7 +8375,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8380,19 +8390,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123549730</v>
+        <v>123548371</v>
       </c>
       <c r="B70" t="n">
         <v>78781</v>
@@ -8428,17 +8438,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>459461</v>
+        <v>459133</v>
       </c>
       <c r="R70" t="n">
-        <v>6808868</v>
+        <v>6808760</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8467,7 +8477,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8477,7 +8487,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8492,19 +8502,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123549689</v>
+        <v>123549730</v>
       </c>
       <c r="B71" t="n">
         <v>78781</v>
@@ -8544,10 +8554,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>459457</v>
+        <v>459461</v>
       </c>
       <c r="R71" t="n">
-        <v>6808865</v>
+        <v>6808868</v>
       </c>
       <c r="S71" t="n">
         <v>9</v>
@@ -8579,7 +8589,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8589,7 +8599,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8616,10 +8626,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123549418</v>
+        <v>123549689</v>
       </c>
       <c r="B72" t="n">
-        <v>56697</v>
+        <v>78781</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8628,43 +8638,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>459318</v>
+        <v>459457</v>
       </c>
       <c r="R72" t="n">
-        <v>6808809</v>
+        <v>6808865</v>
       </c>
       <c r="S72" t="n">
         <v>9</v>
@@ -8696,7 +8701,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8706,12 +8711,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Under betestall</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -11792,10 +11792,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123575257</v>
+        <v>123574181</v>
       </c>
       <c r="B100" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11808,21 +11808,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11832,13 +11832,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>459595</v>
+        <v>459652</v>
       </c>
       <c r="R100" t="n">
-        <v>6808516</v>
+        <v>6808496</v>
       </c>
       <c r="S100" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11877,7 +11877,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11892,19 +11897,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123574181</v>
+        <v>123565429</v>
       </c>
       <c r="B101" t="n">
         <v>78781</v>
@@ -11940,14 +11945,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>459652</v>
+        <v>459753</v>
       </c>
       <c r="R101" t="n">
-        <v>6808496</v>
+        <v>6808887</v>
       </c>
       <c r="S101" t="n">
         <v>9</v>
@@ -11979,7 +11984,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11989,12 +11994,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12021,7 +12021,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123565429</v>
+        <v>123564457</v>
       </c>
       <c r="B102" t="n">
         <v>78781</v>
@@ -12061,13 +12061,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>459753</v>
+        <v>459751</v>
       </c>
       <c r="R102" t="n">
-        <v>6808887</v>
+        <v>6808828</v>
       </c>
       <c r="S102" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12121,19 +12121,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123564457</v>
+        <v>123575574</v>
       </c>
       <c r="B103" t="n">
         <v>78781</v>
@@ -12169,17 +12169,17 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>459751</v>
+        <v>459574</v>
       </c>
       <c r="R103" t="n">
-        <v>6808828</v>
+        <v>6808461</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12218,7 +12218,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12233,22 +12238,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>123575574</v>
+        <v>123565513</v>
       </c>
       <c r="B104" t="n">
-        <v>78781</v>
+        <v>57857</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12257,38 +12262,43 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>459574</v>
+        <v>459753</v>
       </c>
       <c r="R104" t="n">
-        <v>6808461</v>
+        <v>6808887</v>
       </c>
       <c r="S104" t="n">
         <v>9</v>
@@ -12320,7 +12330,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12330,12 +12340,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12362,10 +12367,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123565513</v>
+        <v>123575257</v>
       </c>
       <c r="B105" t="n">
-        <v>57857</v>
+        <v>78518</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12374,46 +12379,41 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>459753</v>
+        <v>459595</v>
       </c>
       <c r="R105" t="n">
-        <v>6808887</v>
+        <v>6808516</v>
       </c>
       <c r="S105" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12467,12 +12467,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -13609,10 +13609,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123564834</v>
+        <v>123575486</v>
       </c>
       <c r="B116" t="n">
-        <v>79399</v>
+        <v>79370</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13625,37 +13625,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>459734</v>
+        <v>459595</v>
       </c>
       <c r="R116" t="n">
-        <v>6808814</v>
+        <v>6808516</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13694,7 +13694,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13709,22 +13709,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123575846</v>
+        <v>123567883</v>
       </c>
       <c r="B117" t="n">
-        <v>78517</v>
+        <v>78518</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13737,37 +13737,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>459707</v>
+        <v>459673</v>
       </c>
       <c r="R117" t="n">
-        <v>6808935</v>
+        <v>6808740</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13821,22 +13821,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123575486</v>
+        <v>123579329</v>
       </c>
       <c r="B118" t="n">
-        <v>79370</v>
+        <v>78781</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13849,37 +13849,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>459595</v>
+        <v>459404</v>
       </c>
       <c r="R118" t="n">
-        <v>6808516</v>
+        <v>6808850</v>
       </c>
       <c r="S118" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13933,22 +13933,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123567883</v>
+        <v>123573294</v>
       </c>
       <c r="B119" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13961,37 +13961,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>459673</v>
+        <v>459753</v>
       </c>
       <c r="R119" t="n">
-        <v>6808740</v>
+        <v>6808571</v>
       </c>
       <c r="S119" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14057,10 +14057,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>123579329</v>
+        <v>123564834</v>
       </c>
       <c r="B120" t="n">
-        <v>78781</v>
+        <v>79399</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14073,21 +14073,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -14097,10 +14097,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>459404</v>
+        <v>459734</v>
       </c>
       <c r="R120" t="n">
-        <v>6808850</v>
+        <v>6808814</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14142,7 +14142,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14169,10 +14169,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123573294</v>
+        <v>123575846</v>
       </c>
       <c r="B121" t="n">
-        <v>78781</v>
+        <v>78517</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14185,37 +14185,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>459753</v>
+        <v>459707</v>
       </c>
       <c r="R121" t="n">
-        <v>6808571</v>
+        <v>6808935</v>
       </c>
       <c r="S121" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14269,12 +14269,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -18031,10 +18031,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>123567356</v>
+        <v>123564957</v>
       </c>
       <c r="B155" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18047,21 +18047,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -18071,13 +18071,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>459560</v>
+        <v>459758</v>
       </c>
       <c r="R155" t="n">
-        <v>6808986</v>
+        <v>6808796</v>
       </c>
       <c r="S155" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18131,19 +18131,19 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>123564957</v>
+        <v>123573959</v>
       </c>
       <c r="B156" t="n">
         <v>78781</v>
@@ -18179,17 +18179,17 @@
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>459758</v>
+        <v>459676</v>
       </c>
       <c r="R156" t="n">
-        <v>6808796</v>
+        <v>6808503</v>
       </c>
       <c r="S156" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18228,7 +18228,12 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18243,19 +18248,19 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>123573959</v>
+        <v>123573845</v>
       </c>
       <c r="B157" t="n">
         <v>78781</v>
@@ -18295,10 +18300,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>459676</v>
+        <v>459696</v>
       </c>
       <c r="R157" t="n">
-        <v>6808503</v>
+        <v>6808508</v>
       </c>
       <c r="S157" t="n">
         <v>9</v>
@@ -18330,7 +18335,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18340,12 +18345,12 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>På tallstammar</t>
+          <t>På tallstammar och gran</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18372,10 +18377,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>123573845</v>
+        <v>123577743</v>
       </c>
       <c r="B158" t="n">
-        <v>78781</v>
+        <v>77709</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18388,21 +18393,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18412,13 +18417,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>459696</v>
+        <v>459571</v>
       </c>
       <c r="R158" t="n">
-        <v>6808508</v>
+        <v>6808546</v>
       </c>
       <c r="S158" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18447,7 +18452,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -18457,12 +18462,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>På tallstammar och gran</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18477,22 +18477,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>123577743</v>
+        <v>123578184</v>
       </c>
       <c r="B159" t="n">
-        <v>77709</v>
+        <v>78165</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18505,37 +18505,37 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>459571</v>
+        <v>459409</v>
       </c>
       <c r="R159" t="n">
-        <v>6808546</v>
+        <v>6808860</v>
       </c>
       <c r="S159" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18574,7 +18574,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18601,10 +18601,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>123578184</v>
+        <v>123567356</v>
       </c>
       <c r="B160" t="n">
-        <v>78165</v>
+        <v>78518</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18617,21 +18617,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18641,13 +18641,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>459409</v>
+        <v>459560</v>
       </c>
       <c r="R160" t="n">
-        <v>6808860</v>
+        <v>6808986</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -22093,10 +22093,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>123576076</v>
+        <v>123569178</v>
       </c>
       <c r="B191" t="n">
-        <v>79370</v>
+        <v>78781</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -22109,37 +22109,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>459548</v>
+        <v>459776</v>
       </c>
       <c r="R191" t="n">
-        <v>6808471</v>
+        <v>6808767</v>
       </c>
       <c r="S191" t="n">
         <v>9</v>
@@ -22171,7 +22168,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -22181,7 +22178,12 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22190,7 +22192,6 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
-      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
@@ -22209,7 +22210,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>123569178</v>
+        <v>123611803</v>
       </c>
       <c r="B192" t="n">
         <v>78781</v>
@@ -22243,19 +22244,22 @@
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andjusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>459776</v>
+        <v>459326</v>
       </c>
       <c r="R192" t="n">
-        <v>6808767</v>
+        <v>6808836</v>
       </c>
       <c r="S192" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -22282,32 +22286,18 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
-        </is>
-      </c>
       <c r="AD192" t="b">
         <v>0</v>
       </c>
       <c r="AE192" t="b">
         <v>0</v>
       </c>
+      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
@@ -22326,10 +22316,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>123611803</v>
+        <v>123576076</v>
       </c>
       <c r="B193" t="n">
-        <v>78781</v>
+        <v>79370</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -22342,21 +22332,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -22365,17 +22355,17 @@
       <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Andjusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>459326</v>
+        <v>459548</v>
       </c>
       <c r="R193" t="n">
-        <v>6808836</v>
+        <v>6808471</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -22402,9 +22392,19 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -24007,10 +24007,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>123544600</v>
+        <v>123548240</v>
       </c>
       <c r="B207" t="n">
-        <v>78165</v>
+        <v>56697</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -24019,38 +24019,46 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>459426</v>
+        <v>459026</v>
       </c>
       <c r="R207" t="n">
-        <v>6808964</v>
+        <v>6808873</v>
       </c>
       <c r="S207" t="n">
         <v>15</v>
@@ -24082,7 +24090,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -24092,7 +24100,12 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>Under betestall</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -24119,10 +24132,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>123543658</v>
+        <v>123568467</v>
       </c>
       <c r="B208" t="n">
-        <v>91001</v>
+        <v>57487</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -24135,34 +24148,39 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>459656</v>
+        <v>459803</v>
       </c>
       <c r="R208" t="n">
-        <v>6808959</v>
+        <v>6808817</v>
       </c>
       <c r="S208" t="n">
         <v>9</v>
@@ -24189,22 +24207,22 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -24231,10 +24249,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>123568467</v>
+        <v>123544600</v>
       </c>
       <c r="B209" t="n">
-        <v>57487</v>
+        <v>78165</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -24247,42 +24265,37 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P209" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>459803</v>
+        <v>459426</v>
       </c>
       <c r="R209" t="n">
-        <v>6808817</v>
+        <v>6808964</v>
       </c>
       <c r="S209" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -24306,22 +24319,22 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -24336,22 +24349,22 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>123577342</v>
+        <v>123543658</v>
       </c>
       <c r="B210" t="n">
-        <v>56697</v>
+        <v>91001</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -24360,49 +24373,41 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>459446</v>
+        <v>459656</v>
       </c>
       <c r="R210" t="n">
-        <v>6808812</v>
+        <v>6808959</v>
       </c>
       <c r="S210" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -24426,27 +24431,22 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>Under betestall</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24461,19 +24461,19 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>123548240</v>
+        <v>123577342</v>
       </c>
       <c r="B211" t="n">
         <v>56697</v>
@@ -24517,14 +24517,14 @@
       <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>459026</v>
+        <v>459446</v>
       </c>
       <c r="R211" t="n">
-        <v>6808873</v>
+        <v>6808812</v>
       </c>
       <c r="S211" t="n">
         <v>15</v>
@@ -24551,22 +24551,22 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC211" t="inlineStr">
@@ -25531,7 +25531,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>123549286</v>
+        <v>123567138</v>
       </c>
       <c r="B220" t="n">
         <v>56697</v>
@@ -25575,14 +25575,14 @@
       <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>459241</v>
+        <v>459735</v>
       </c>
       <c r="R220" t="n">
-        <v>6808793</v>
+        <v>6808695</v>
       </c>
       <c r="S220" t="n">
         <v>15</v>
@@ -25609,22 +25609,22 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC220" t="inlineStr">
@@ -25656,10 +25656,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>123567138</v>
+        <v>123543338</v>
       </c>
       <c r="B221" t="n">
-        <v>56697</v>
+        <v>57503</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -25668,25 +25668,25 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -25694,7 +25694,7 @@
       <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N221" t="inlineStr"/>
@@ -25704,10 +25704,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>459735</v>
+        <v>459630</v>
       </c>
       <c r="R221" t="n">
-        <v>6808695</v>
+        <v>6808926</v>
       </c>
       <c r="S221" t="n">
         <v>15</v>
@@ -25734,27 +25734,22 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>Under betestall</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -25781,10 +25776,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>123543338</v>
+        <v>123549286</v>
       </c>
       <c r="B222" t="n">
-        <v>57503</v>
+        <v>56697</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -25793,25 +25788,25 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -25819,20 +25814,20 @@
       <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>459630</v>
+        <v>459241</v>
       </c>
       <c r="R222" t="n">
-        <v>6808926</v>
+        <v>6808793</v>
       </c>
       <c r="S222" t="n">
         <v>15</v>
@@ -25864,7 +25859,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -25874,7 +25869,12 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>Under betestall</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -26251,7 +26251,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>123547844</v>
+        <v>123564359</v>
       </c>
       <c r="B226" t="n">
         <v>78781</v>
@@ -26287,17 +26287,17 @@
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>459260</v>
+        <v>459743</v>
       </c>
       <c r="R226" t="n">
-        <v>6808804</v>
+        <v>6808927</v>
       </c>
       <c r="S226" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -26321,22 +26321,27 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>På Granstam</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -26351,22 +26356,22 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>123564359</v>
+        <v>123573008</v>
       </c>
       <c r="B227" t="n">
-        <v>78781</v>
+        <v>56697</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -26375,41 +26380,49 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>459743</v>
+        <v>459717</v>
       </c>
       <c r="R227" t="n">
-        <v>6808927</v>
+        <v>6808606</v>
       </c>
       <c r="S227" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -26438,7 +26451,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -26448,12 +26461,12 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>På Granstam</t>
+          <t>Under betestall</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -26468,22 +26481,22 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>123573008</v>
+        <v>123547844</v>
       </c>
       <c r="B228" t="n">
-        <v>56697</v>
+        <v>78781</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -26492,46 +26505,38 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>459717</v>
+        <v>459260</v>
       </c>
       <c r="R228" t="n">
-        <v>6808606</v>
+        <v>6808804</v>
       </c>
       <c r="S228" t="n">
         <v>15</v>
@@ -26558,27 +26563,22 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC228" t="inlineStr">
-        <is>
-          <t>Under betestall</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -26931,10 +26931,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>123725777</v>
+        <v>123727325</v>
       </c>
       <c r="B232" t="n">
-        <v>78781</v>
+        <v>78517</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -26947,21 +26947,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -26971,10 +26971,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>458901</v>
+        <v>458886</v>
       </c>
       <c r="R232" t="n">
-        <v>6808289</v>
+        <v>6808352</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -27033,10 +27033,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>123726070</v>
+        <v>123728287</v>
       </c>
       <c r="B233" t="n">
-        <v>57503</v>
+        <v>78781</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -27049,39 +27049,34 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P233" t="inlineStr">
         <is>
           <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>458944</v>
+        <v>458826</v>
       </c>
       <c r="R233" t="n">
-        <v>6808335</v>
+        <v>6808449</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -27114,6 +27109,11 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>Garnlav på samtliga träd,mer eller mindre, på bilden.</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -27140,10 +27140,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>123727325</v>
+        <v>123728532</v>
       </c>
       <c r="B234" t="n">
-        <v>78517</v>
+        <v>78518</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -27156,21 +27156,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -27180,10 +27180,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>458886</v>
+        <v>458798</v>
       </c>
       <c r="R234" t="n">
-        <v>6808352</v>
+        <v>6808499</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -27242,7 +27242,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>123728287</v>
+        <v>123732955</v>
       </c>
       <c r="B235" t="n">
         <v>78781</v>
@@ -27278,14 +27278,14 @@
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Dyvran, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>458826</v>
+        <v>458711</v>
       </c>
       <c r="R235" t="n">
-        <v>6808449</v>
+        <v>6808905</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27322,7 +27322,7 @@
       </c>
       <c r="AC235" t="inlineStr">
         <is>
-          <t>Garnlav på samtliga träd,mer eller mindre, på bilden.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -27349,10 +27349,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>123728532</v>
+        <v>123725777</v>
       </c>
       <c r="B236" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -27365,21 +27365,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -27389,10 +27389,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>458798</v>
+        <v>458901</v>
       </c>
       <c r="R236" t="n">
-        <v>6808499</v>
+        <v>6808289</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27451,10 +27451,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>123732955</v>
+        <v>123726070</v>
       </c>
       <c r="B237" t="n">
-        <v>78781</v>
+        <v>57503</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -27467,34 +27467,39 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>458711</v>
+        <v>458944</v>
       </c>
       <c r="R237" t="n">
-        <v>6808905</v>
+        <v>6808335</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27527,11 +27532,6 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -27976,7 +27976,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>123723313</v>
+        <v>123732682</v>
       </c>
       <c r="B242" t="n">
         <v>78781</v>
@@ -28012,14 +28012,14 @@
       <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Dyvran, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>458948</v>
+        <v>458711</v>
       </c>
       <c r="R242" t="n">
-        <v>6808276</v>
+        <v>6808858</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -28056,7 +28056,7 @@
       </c>
       <c r="AC242" t="inlineStr">
         <is>
-          <t>Garnlav med miljöbild.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -28083,7 +28083,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>123732682</v>
+        <v>123732746</v>
       </c>
       <c r="B243" t="n">
         <v>78781</v>
@@ -28123,10 +28123,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>458711</v>
+        <v>458699</v>
       </c>
       <c r="R243" t="n">
-        <v>6808858</v>
+        <v>6808863</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -28190,7 +28190,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>123732746</v>
+        <v>123723313</v>
       </c>
       <c r="B244" t="n">
         <v>78781</v>
@@ -28226,14 +28226,14 @@
       <c r="I244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>458699</v>
+        <v>458948</v>
       </c>
       <c r="R244" t="n">
-        <v>6808863</v>
+        <v>6808276</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -28270,7 +28270,7 @@
       </c>
       <c r="AC244" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -29561,10 +29561,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>123730266</v>
+        <v>123728918</v>
       </c>
       <c r="B257" t="n">
-        <v>78781</v>
+        <v>79399</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -29577,34 +29577,34 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>458694</v>
+        <v>458818</v>
       </c>
       <c r="R257" t="n">
-        <v>6808695</v>
+        <v>6808502</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29637,11 +29637,6 @@
       <c r="AA257" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC257" t="inlineStr">
-        <is>
-          <t>Garnlav i en radie av ca 50 meter. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -29668,10 +29663,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>123728918</v>
+        <v>123730266</v>
       </c>
       <c r="B258" t="n">
-        <v>79399</v>
+        <v>78781</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -29684,34 +29679,34 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Dyvran, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>458818</v>
+        <v>458694</v>
       </c>
       <c r="R258" t="n">
-        <v>6808502</v>
+        <v>6808695</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29744,6 +29739,11 @@
       <c r="AA258" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>Garnlav i en radie av ca 50 meter. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -29770,10 +29770,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>123728778</v>
+        <v>123725285</v>
       </c>
       <c r="B259" t="n">
-        <v>57503</v>
+        <v>78781</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -29786,21 +29786,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -29810,10 +29810,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>458798</v>
+        <v>458926</v>
       </c>
       <c r="R259" t="n">
-        <v>6808499</v>
+        <v>6808287</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -29846,11 +29846,6 @@
       <c r="AA259" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC259" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -29877,10 +29872,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>123725285</v>
+        <v>123728778</v>
       </c>
       <c r="B260" t="n">
-        <v>78781</v>
+        <v>57503</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -29893,21 +29888,21 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -29917,10 +29912,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>458926</v>
+        <v>458798</v>
       </c>
       <c r="R260" t="n">
-        <v>6808287</v>
+        <v>6808499</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -29953,6 +29948,11 @@
       <c r="AA260" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -30922,10 +30922,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>123733103</v>
+        <v>123729780</v>
       </c>
       <c r="B270" t="n">
-        <v>78781</v>
+        <v>78517</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -30938,21 +30938,21 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -30962,10 +30962,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>458738</v>
+        <v>458694</v>
       </c>
       <c r="R270" t="n">
-        <v>6808843</v>
+        <v>6808650</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -30998,6 +30998,11 @@
       <c r="AA270" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -31024,10 +31029,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>123729780</v>
+        <v>123730079</v>
       </c>
       <c r="B271" t="n">
-        <v>78517</v>
+        <v>57487</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -31040,34 +31045,39 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P271" t="inlineStr">
         <is>
           <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>458694</v>
+        <v>458669</v>
       </c>
       <c r="R271" t="n">
-        <v>6808650</v>
+        <v>6808687</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -31100,11 +31110,6 @@
       <c r="AA271" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC271" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -31131,10 +31136,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>123730079</v>
+        <v>123733103</v>
       </c>
       <c r="B272" t="n">
-        <v>57487</v>
+        <v>78781</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -31147,39 +31152,34 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P272" t="inlineStr">
         <is>
           <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>458669</v>
+        <v>458738</v>
       </c>
       <c r="R272" t="n">
-        <v>6808687</v>
+        <v>6808843</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>

--- a/artfynd/A 13728-2025 artfynd.xlsx
+++ b/artfynd/A 13728-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123544482</v>
+        <v>123549262</v>
       </c>
       <c r="B4" t="n">
         <v>78781</v>
@@ -928,17 +928,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459695</v>
+        <v>459241</v>
       </c>
       <c r="R4" t="n">
-        <v>6808940</v>
+        <v>6808793</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,19 +992,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123543271</v>
+        <v>123544027</v>
       </c>
       <c r="B5" t="n">
         <v>78781</v>
@@ -1040,17 +1040,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459704</v>
+        <v>459695</v>
       </c>
       <c r="R5" t="n">
-        <v>6808939</v>
+        <v>6808940</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1089,12 +1089,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På Gran blandat med skägglav</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,19 +1104,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123543936</v>
+        <v>123549170</v>
       </c>
       <c r="B6" t="n">
         <v>78781</v>
@@ -1157,17 +1152,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459520</v>
+        <v>459062</v>
       </c>
       <c r="R6" t="n">
-        <v>6808918</v>
+        <v>6808854</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1201,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,19 +1216,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123547534</v>
+        <v>123543271</v>
       </c>
       <c r="B7" t="n">
         <v>78781</v>
@@ -1269,17 +1264,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458871</v>
+        <v>459704</v>
       </c>
       <c r="R7" t="n">
-        <v>6809014</v>
+        <v>6808939</v>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,7 +1313,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På Gran blandat med skägglav</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,19 +1333,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123549262</v>
+        <v>123547534</v>
       </c>
       <c r="B8" t="n">
         <v>78781</v>
@@ -1381,17 +1381,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459241</v>
+        <v>458871</v>
       </c>
       <c r="R8" t="n">
-        <v>6808793</v>
+        <v>6809014</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,19 +1445,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123549170</v>
+        <v>123543936</v>
       </c>
       <c r="B9" t="n">
         <v>78781</v>
@@ -1493,17 +1493,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459062</v>
+        <v>459520</v>
       </c>
       <c r="R9" t="n">
-        <v>6808854</v>
+        <v>6808918</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,12 +1557,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -3175,10 +3175,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123548439</v>
+        <v>123548646</v>
       </c>
       <c r="B24" t="n">
-        <v>78781</v>
+        <v>78518</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3191,34 +3191,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459138</v>
+        <v>459185</v>
       </c>
       <c r="R24" t="n">
-        <v>6808765</v>
+        <v>6808785</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3287,7 +3287,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123549501</v>
+        <v>123548439</v>
       </c>
       <c r="B25" t="n">
         <v>78781</v>
@@ -3323,17 +3323,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459367</v>
+        <v>459138</v>
       </c>
       <c r="R25" t="n">
-        <v>6808792</v>
+        <v>6808765</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3387,22 +3387,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123548646</v>
+        <v>123549501</v>
       </c>
       <c r="B26" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3415,37 +3415,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459185</v>
+        <v>459367</v>
       </c>
       <c r="R26" t="n">
-        <v>6808785</v>
+        <v>6808792</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3499,12 +3499,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3959,10 +3959,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123545274</v>
+        <v>123546440</v>
       </c>
       <c r="B31" t="n">
-        <v>78781</v>
+        <v>78518</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3975,37 +3975,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459304</v>
+        <v>459563</v>
       </c>
       <c r="R31" t="n">
-        <v>6809019</v>
+        <v>6808917</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4059,12 +4059,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4183,7 +4183,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123548247</v>
+        <v>123545274</v>
       </c>
       <c r="B33" t="n">
         <v>78781</v>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459057</v>
+        <v>459304</v>
       </c>
       <c r="R33" t="n">
-        <v>6808867</v>
+        <v>6809019</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4283,22 +4283,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123546440</v>
+        <v>123548247</v>
       </c>
       <c r="B34" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4311,37 +4311,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459563</v>
+        <v>459057</v>
       </c>
       <c r="R34" t="n">
-        <v>6808917</v>
+        <v>6808867</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4395,12 +4395,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123545712</v>
+        <v>123547657</v>
       </c>
       <c r="B42" t="n">
-        <v>78876</v>
+        <v>56697</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5216,41 +5216,49 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>967</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459156</v>
+        <v>459003</v>
       </c>
       <c r="R42" t="n">
-        <v>6808985</v>
+        <v>6808929</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5279,7 +5287,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5289,7 +5297,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Betestall., spillning från höna</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5304,12 +5317,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5428,10 +5441,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123547657</v>
+        <v>123546479</v>
       </c>
       <c r="B44" t="n">
-        <v>56697</v>
+        <v>78518</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5440,46 +5453,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459003</v>
+        <v>459128</v>
       </c>
       <c r="R44" t="n">
-        <v>6808929</v>
+        <v>6808999</v>
       </c>
       <c r="S44" t="n">
         <v>9</v>
@@ -5511,7 +5516,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5521,12 +5526,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Betestall., spillning från höna</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5553,10 +5553,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123546479</v>
+        <v>123545712</v>
       </c>
       <c r="B45" t="n">
-        <v>78518</v>
+        <v>78876</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5569,21 +5569,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5593,13 +5593,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459128</v>
+        <v>459156</v>
       </c>
       <c r="R45" t="n">
-        <v>6808999</v>
+        <v>6808985</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5653,12 +5653,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -8290,10 +8290,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123549577</v>
+        <v>123549477</v>
       </c>
       <c r="B69" t="n">
-        <v>78781</v>
+        <v>78518</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8306,37 +8306,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>459420</v>
+        <v>459062</v>
       </c>
       <c r="R69" t="n">
-        <v>6808812</v>
+        <v>6808854</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8390,19 +8390,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123548371</v>
+        <v>123549577</v>
       </c>
       <c r="B70" t="n">
         <v>78781</v>
@@ -8438,17 +8438,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>459133</v>
+        <v>459420</v>
       </c>
       <c r="R70" t="n">
-        <v>6808760</v>
+        <v>6808812</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8502,19 +8502,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123549730</v>
+        <v>123548371</v>
       </c>
       <c r="B71" t="n">
         <v>78781</v>
@@ -8550,17 +8550,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>459461</v>
+        <v>459133</v>
       </c>
       <c r="R71" t="n">
-        <v>6808868</v>
+        <v>6808760</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8614,19 +8614,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123549689</v>
+        <v>123549730</v>
       </c>
       <c r="B72" t="n">
         <v>78781</v>
@@ -8666,10 +8666,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>459457</v>
+        <v>459461</v>
       </c>
       <c r="R72" t="n">
-        <v>6808865</v>
+        <v>6808868</v>
       </c>
       <c r="S72" t="n">
         <v>9</v>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8738,10 +8738,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123549477</v>
+        <v>123549689</v>
       </c>
       <c r="B73" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8754,37 +8754,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>459062</v>
+        <v>459457</v>
       </c>
       <c r="R73" t="n">
-        <v>6808854</v>
+        <v>6808865</v>
       </c>
       <c r="S73" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8838,22 +8838,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123548779</v>
+        <v>123548763</v>
       </c>
       <c r="B74" t="n">
-        <v>79370</v>
+        <v>78781</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8866,21 +8866,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8890,13 +8890,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>459073</v>
+        <v>459187</v>
       </c>
       <c r="R74" t="n">
-        <v>6808847</v>
+        <v>6808828</v>
       </c>
       <c r="S74" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8950,22 +8950,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123548763</v>
+        <v>123548779</v>
       </c>
       <c r="B75" t="n">
-        <v>78781</v>
+        <v>79370</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8978,21 +8978,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9002,13 +9002,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>459187</v>
+        <v>459073</v>
       </c>
       <c r="R75" t="n">
-        <v>6808828</v>
+        <v>6808847</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9062,12 +9062,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -14281,10 +14281,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123573174</v>
+        <v>123568223</v>
       </c>
       <c r="B122" t="n">
-        <v>78781</v>
+        <v>74875</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14297,21 +14297,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14321,13 +14321,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>459757</v>
+        <v>459796</v>
       </c>
       <c r="R122" t="n">
-        <v>6808589</v>
+        <v>6808830</v>
       </c>
       <c r="S122" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14381,22 +14381,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123574214</v>
+        <v>123567140</v>
       </c>
       <c r="B123" t="n">
-        <v>78781</v>
+        <v>74875</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14409,34 +14409,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>459645</v>
+        <v>459773</v>
       </c>
       <c r="R123" t="n">
-        <v>6808484</v>
+        <v>6808865</v>
       </c>
       <c r="S123" t="n">
         <v>9</v>
@@ -14468,7 +14468,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14478,12 +14478,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14510,7 +14505,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123573768</v>
+        <v>123573174</v>
       </c>
       <c r="B124" t="n">
         <v>78781</v>
@@ -14546,17 +14541,17 @@
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>459699</v>
+        <v>459757</v>
       </c>
       <c r="R124" t="n">
-        <v>6808517</v>
+        <v>6808589</v>
       </c>
       <c r="S124" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14585,7 +14580,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14595,12 +14590,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14615,19 +14605,19 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>123573228</v>
+        <v>123574214</v>
       </c>
       <c r="B125" t="n">
         <v>78781</v>
@@ -14667,10 +14657,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>459731</v>
+        <v>459645</v>
       </c>
       <c r="R125" t="n">
-        <v>6808589</v>
+        <v>6808484</v>
       </c>
       <c r="S125" t="n">
         <v>9</v>
@@ -14702,7 +14692,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14712,7 +14702,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
@@ -14744,7 +14734,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>123575052</v>
+        <v>123573768</v>
       </c>
       <c r="B126" t="n">
         <v>78781</v>
@@ -14784,13 +14774,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>459600</v>
+        <v>459699</v>
       </c>
       <c r="R126" t="n">
-        <v>6808513</v>
+        <v>6808517</v>
       </c>
       <c r="S126" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14819,7 +14809,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14829,7 +14819,12 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14844,19 +14839,19 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>123565290</v>
+        <v>123573228</v>
       </c>
       <c r="B127" t="n">
         <v>78781</v>
@@ -14892,17 +14887,17 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>459761</v>
+        <v>459731</v>
       </c>
       <c r="R127" t="n">
-        <v>6808736</v>
+        <v>6808589</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14931,7 +14926,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14941,7 +14936,12 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14956,19 +14956,19 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>123563725</v>
+        <v>123575052</v>
       </c>
       <c r="B128" t="n">
         <v>78781</v>
@@ -15004,17 +15004,17 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>459730</v>
+        <v>459600</v>
       </c>
       <c r="R128" t="n">
-        <v>6808890</v>
+        <v>6808513</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15053,7 +15053,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15068,22 +15068,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>123568223</v>
+        <v>123565290</v>
       </c>
       <c r="B129" t="n">
-        <v>74875</v>
+        <v>78781</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15096,21 +15096,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15120,13 +15120,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>459796</v>
+        <v>459761</v>
       </c>
       <c r="R129" t="n">
-        <v>6808830</v>
+        <v>6808736</v>
       </c>
       <c r="S129" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15180,22 +15180,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>123567140</v>
+        <v>123563725</v>
       </c>
       <c r="B130" t="n">
-        <v>74875</v>
+        <v>78781</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15208,21 +15208,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15232,13 +15232,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>459773</v>
+        <v>459730</v>
       </c>
       <c r="R130" t="n">
-        <v>6808865</v>
+        <v>6808890</v>
       </c>
       <c r="S130" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15277,7 +15277,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15292,12 +15292,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
@@ -15883,10 +15883,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>123563838</v>
+        <v>123566063</v>
       </c>
       <c r="B136" t="n">
-        <v>57487</v>
+        <v>82568</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15899,42 +15899,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>459731</v>
+        <v>459745</v>
       </c>
       <c r="R136" t="n">
-        <v>6808890</v>
+        <v>6808895</v>
       </c>
       <c r="S136" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15963,7 +15958,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15973,7 +15968,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15988,22 +15983,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>123575865</v>
+        <v>123567126</v>
       </c>
       <c r="B137" t="n">
-        <v>79370</v>
+        <v>78781</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16016,37 +16011,37 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>459707</v>
+        <v>459735</v>
       </c>
       <c r="R137" t="n">
-        <v>6808935</v>
+        <v>6808695</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16075,7 +16070,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16085,7 +16080,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16100,22 +16095,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>123566063</v>
+        <v>123577391</v>
       </c>
       <c r="B138" t="n">
-        <v>82568</v>
+        <v>78781</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16128,21 +16123,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -16152,13 +16147,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>459745</v>
+        <v>459446</v>
       </c>
       <c r="R138" t="n">
-        <v>6808895</v>
+        <v>6808812</v>
       </c>
       <c r="S138" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16187,7 +16182,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16197,7 +16192,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16212,19 +16207,19 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>123567126</v>
+        <v>123576513</v>
       </c>
       <c r="B139" t="n">
         <v>78781</v>
@@ -16260,17 +16255,17 @@
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>459735</v>
+        <v>459499</v>
       </c>
       <c r="R139" t="n">
-        <v>6808695</v>
+        <v>6808540</v>
       </c>
       <c r="S139" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16299,7 +16294,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16309,7 +16304,12 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>På Granar</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16324,22 +16324,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>123577391</v>
+        <v>123563838</v>
       </c>
       <c r="B140" t="n">
-        <v>78781</v>
+        <v>57487</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16352,34 +16352,39 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>459446</v>
+        <v>459731</v>
       </c>
       <c r="R140" t="n">
-        <v>6808812</v>
+        <v>6808890</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -16411,7 +16416,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16421,7 +16426,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16448,10 +16453,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>123576513</v>
+        <v>123575865</v>
       </c>
       <c r="B141" t="n">
-        <v>78781</v>
+        <v>79370</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16464,37 +16469,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>459499</v>
+        <v>459707</v>
       </c>
       <c r="R141" t="n">
-        <v>6808540</v>
+        <v>6808935</v>
       </c>
       <c r="S141" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16523,7 +16528,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16533,12 +16538,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>På Granar</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16553,12 +16553,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -21304,10 +21304,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>123575930</v>
+        <v>123576167</v>
       </c>
       <c r="B184" t="n">
-        <v>78517</v>
+        <v>78876</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21320,21 +21320,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -21344,13 +21344,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>459550</v>
+        <v>459499</v>
       </c>
       <c r="R184" t="n">
-        <v>6808474</v>
+        <v>6808603</v>
       </c>
       <c r="S184" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -21389,7 +21389,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21404,22 +21404,22 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>123576167</v>
+        <v>123564423</v>
       </c>
       <c r="B185" t="n">
-        <v>78876</v>
+        <v>78781</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21432,34 +21432,34 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>459499</v>
+        <v>459749</v>
       </c>
       <c r="R185" t="n">
-        <v>6808603</v>
+        <v>6808825</v>
       </c>
       <c r="S185" t="n">
         <v>15</v>
@@ -21491,7 +21491,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21528,7 +21528,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>123564423</v>
+        <v>123575662</v>
       </c>
       <c r="B186" t="n">
         <v>78781</v>
@@ -21564,17 +21564,17 @@
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>459749</v>
+        <v>459583</v>
       </c>
       <c r="R186" t="n">
-        <v>6808825</v>
+        <v>6808519</v>
       </c>
       <c r="S186" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -21613,7 +21613,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21628,19 +21628,19 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>123575662</v>
+        <v>123576411</v>
       </c>
       <c r="B187" t="n">
         <v>78781</v>
@@ -21680,13 +21680,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>459583</v>
+        <v>459499</v>
       </c>
       <c r="R187" t="n">
-        <v>6808519</v>
+        <v>6808603</v>
       </c>
       <c r="S187" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -21725,7 +21725,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21740,22 +21740,22 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>123576411</v>
+        <v>123575930</v>
       </c>
       <c r="B188" t="n">
-        <v>78781</v>
+        <v>78517</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21768,21 +21768,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -21792,13 +21792,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>459499</v>
+        <v>459550</v>
       </c>
       <c r="R188" t="n">
-        <v>6808603</v>
+        <v>6808474</v>
       </c>
       <c r="S188" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -21837,7 +21837,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21852,12 +21852,12 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
@@ -22093,10 +22093,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>123569178</v>
+        <v>123576076</v>
       </c>
       <c r="B191" t="n">
-        <v>78781</v>
+        <v>79370</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -22109,34 +22109,37 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>459776</v>
+        <v>459548</v>
       </c>
       <c r="R191" t="n">
-        <v>6808767</v>
+        <v>6808471</v>
       </c>
       <c r="S191" t="n">
         <v>9</v>
@@ -22168,7 +22171,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -22178,12 +22181,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22192,6 +22190,7 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
+      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
@@ -22210,7 +22209,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>123611803</v>
+        <v>123569178</v>
       </c>
       <c r="B192" t="n">
         <v>78781</v>
@@ -22244,22 +22243,19 @@
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Andjusbäcken, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>459326</v>
+        <v>459776</v>
       </c>
       <c r="R192" t="n">
-        <v>6808836</v>
+        <v>6808767</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -22286,18 +22282,32 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
+        </is>
+      </c>
       <c r="AD192" t="b">
         <v>0</v>
       </c>
       <c r="AE192" t="b">
         <v>0</v>
       </c>
-      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
@@ -22316,10 +22326,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>123576076</v>
+        <v>123611803</v>
       </c>
       <c r="B193" t="n">
-        <v>79370</v>
+        <v>78781</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -22332,21 +22342,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -22355,17 +22365,17 @@
       <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andjusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>459548</v>
+        <v>459326</v>
       </c>
       <c r="R193" t="n">
-        <v>6808471</v>
+        <v>6808836</v>
       </c>
       <c r="S193" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -22392,19 +22402,9 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>14:21</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -24007,10 +24007,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>123548240</v>
+        <v>123544600</v>
       </c>
       <c r="B207" t="n">
-        <v>56697</v>
+        <v>78165</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -24019,46 +24019,38 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100138</v>
+        <v>6437</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>459026</v>
+        <v>459426</v>
       </c>
       <c r="R207" t="n">
-        <v>6808873</v>
+        <v>6808964</v>
       </c>
       <c r="S207" t="n">
         <v>15</v>
@@ -24090,7 +24082,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -24100,12 +24092,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>Under betestall</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -24132,10 +24119,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>123568467</v>
+        <v>123543658</v>
       </c>
       <c r="B208" t="n">
-        <v>57487</v>
+        <v>91001</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -24148,39 +24135,34 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>459803</v>
+        <v>459656</v>
       </c>
       <c r="R208" t="n">
-        <v>6808817</v>
+        <v>6808959</v>
       </c>
       <c r="S208" t="n">
         <v>9</v>
@@ -24207,22 +24189,22 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -24249,10 +24231,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>123544600</v>
+        <v>123568467</v>
       </c>
       <c r="B209" t="n">
-        <v>78165</v>
+        <v>57487</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -24265,37 +24247,42 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>459426</v>
+        <v>459803</v>
       </c>
       <c r="R209" t="n">
-        <v>6808964</v>
+        <v>6808817</v>
       </c>
       <c r="S209" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -24319,22 +24306,22 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -24349,22 +24336,22 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>123543658</v>
+        <v>123577342</v>
       </c>
       <c r="B210" t="n">
-        <v>91001</v>
+        <v>56697</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -24373,41 +24360,49 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>459656</v>
+        <v>459446</v>
       </c>
       <c r="R210" t="n">
-        <v>6808959</v>
+        <v>6808812</v>
       </c>
       <c r="S210" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -24431,22 +24426,27 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>Under betestall</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24461,19 +24461,19 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>123577342</v>
+        <v>123548240</v>
       </c>
       <c r="B211" t="n">
         <v>56697</v>
@@ -24517,14 +24517,14 @@
       <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>459446</v>
+        <v>459026</v>
       </c>
       <c r="R211" t="n">
-        <v>6808812</v>
+        <v>6808873</v>
       </c>
       <c r="S211" t="n">
         <v>15</v>
@@ -24551,22 +24551,22 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC211" t="inlineStr">
@@ -25531,7 +25531,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>123567138</v>
+        <v>123549286</v>
       </c>
       <c r="B220" t="n">
         <v>56697</v>
@@ -25575,14 +25575,14 @@
       <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>459735</v>
+        <v>459241</v>
       </c>
       <c r="R220" t="n">
-        <v>6808695</v>
+        <v>6808793</v>
       </c>
       <c r="S220" t="n">
         <v>15</v>
@@ -25609,22 +25609,22 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC220" t="inlineStr">
@@ -25656,10 +25656,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>123543338</v>
+        <v>123567138</v>
       </c>
       <c r="B221" t="n">
-        <v>57503</v>
+        <v>56697</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -25668,25 +25668,25 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -25694,7 +25694,7 @@
       <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N221" t="inlineStr"/>
@@ -25704,10 +25704,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>459630</v>
+        <v>459735</v>
       </c>
       <c r="R221" t="n">
-        <v>6808926</v>
+        <v>6808695</v>
       </c>
       <c r="S221" t="n">
         <v>15</v>
@@ -25734,22 +25734,27 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>Under betestall</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -25776,10 +25781,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>123549286</v>
+        <v>123543338</v>
       </c>
       <c r="B222" t="n">
-        <v>56697</v>
+        <v>57503</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -25788,25 +25793,25 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -25814,20 +25819,20 @@
       <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>459241</v>
+        <v>459630</v>
       </c>
       <c r="R222" t="n">
-        <v>6808793</v>
+        <v>6808926</v>
       </c>
       <c r="S222" t="n">
         <v>15</v>
@@ -25859,7 +25864,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -25869,12 +25874,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>Under betestall</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -26931,10 +26931,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>123727325</v>
+        <v>123728287</v>
       </c>
       <c r="B232" t="n">
-        <v>78517</v>
+        <v>78781</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -26947,21 +26947,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -26971,10 +26971,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>458886</v>
+        <v>458826</v>
       </c>
       <c r="R232" t="n">
-        <v>6808352</v>
+        <v>6808449</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -27007,6 +27007,11 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Garnlav på samtliga träd,mer eller mindre, på bilden.</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -27033,10 +27038,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>123728287</v>
+        <v>123728532</v>
       </c>
       <c r="B233" t="n">
-        <v>78781</v>
+        <v>78518</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -27049,21 +27054,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -27073,10 +27078,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>458826</v>
+        <v>458798</v>
       </c>
       <c r="R233" t="n">
-        <v>6808449</v>
+        <v>6808499</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -27109,11 +27114,6 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>Garnlav på samtliga träd,mer eller mindre, på bilden.</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -27140,10 +27140,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>123728532</v>
+        <v>123732955</v>
       </c>
       <c r="B234" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -27156,34 +27156,34 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Dyvran, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>458798</v>
+        <v>458711</v>
       </c>
       <c r="R234" t="n">
-        <v>6808499</v>
+        <v>6808905</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -27216,6 +27216,11 @@
       <c r="AA234" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -27242,7 +27247,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>123732955</v>
+        <v>123725777</v>
       </c>
       <c r="B235" t="n">
         <v>78781</v>
@@ -27278,14 +27283,14 @@
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>458711</v>
+        <v>458901</v>
       </c>
       <c r="R235" t="n">
-        <v>6808905</v>
+        <v>6808289</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27318,11 +27323,6 @@
       <c r="AA235" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -27349,10 +27349,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>123725777</v>
+        <v>123726070</v>
       </c>
       <c r="B236" t="n">
-        <v>78781</v>
+        <v>57503</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -27365,34 +27365,39 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P236" t="inlineStr">
         <is>
           <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>458901</v>
+        <v>458944</v>
       </c>
       <c r="R236" t="n">
-        <v>6808289</v>
+        <v>6808335</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27451,10 +27456,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>123726070</v>
+        <v>123727325</v>
       </c>
       <c r="B237" t="n">
-        <v>57503</v>
+        <v>78517</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -27467,39 +27472,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P237" t="inlineStr">
         <is>
           <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>458944</v>
+        <v>458886</v>
       </c>
       <c r="R237" t="n">
-        <v>6808335</v>
+        <v>6808352</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27558,10 +27558,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>123728524</v>
+        <v>123728027</v>
       </c>
       <c r="B238" t="n">
-        <v>78517</v>
+        <v>78518</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -27574,21 +27574,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -27598,10 +27598,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>458826</v>
+        <v>458836</v>
       </c>
       <c r="R238" t="n">
-        <v>6808449</v>
+        <v>6808421</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -27634,11 +27634,6 @@
       <c r="AA238" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -27665,10 +27660,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>123732512</v>
+        <v>123725898</v>
       </c>
       <c r="B239" t="n">
-        <v>78517</v>
+        <v>78781</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -27681,34 +27676,34 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>458701</v>
+        <v>458927</v>
       </c>
       <c r="R239" t="n">
-        <v>6808812</v>
+        <v>6808307</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -27741,11 +27736,6 @@
       <c r="AA239" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC239" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -27772,10 +27762,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>123728027</v>
+        <v>123732512</v>
       </c>
       <c r="B240" t="n">
-        <v>78518</v>
+        <v>78517</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -27788,34 +27778,34 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Dyvran, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>458836</v>
+        <v>458701</v>
       </c>
       <c r="R240" t="n">
-        <v>6808421</v>
+        <v>6808812</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27848,6 +27838,11 @@
       <c r="AA240" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC240" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -27874,10 +27869,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>123725898</v>
+        <v>123728524</v>
       </c>
       <c r="B241" t="n">
-        <v>78781</v>
+        <v>78517</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -27890,21 +27885,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27914,10 +27909,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>458927</v>
+        <v>458826</v>
       </c>
       <c r="R241" t="n">
-        <v>6808307</v>
+        <v>6808449</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27950,6 +27945,11 @@
       <c r="AA241" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC241" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -27976,7 +27976,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>123732682</v>
+        <v>123723313</v>
       </c>
       <c r="B242" t="n">
         <v>78781</v>
@@ -28012,14 +28012,14 @@
       <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>458711</v>
+        <v>458948</v>
       </c>
       <c r="R242" t="n">
-        <v>6808858</v>
+        <v>6808276</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -28056,7 +28056,7 @@
       </c>
       <c r="AC242" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -28083,7 +28083,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>123732746</v>
+        <v>123732682</v>
       </c>
       <c r="B243" t="n">
         <v>78781</v>
@@ -28123,10 +28123,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>458699</v>
+        <v>458711</v>
       </c>
       <c r="R243" t="n">
-        <v>6808863</v>
+        <v>6808858</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -28190,7 +28190,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>123723313</v>
+        <v>123732746</v>
       </c>
       <c r="B244" t="n">
         <v>78781</v>
@@ -28226,14 +28226,14 @@
       <c r="I244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Dyvran, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>458948</v>
+        <v>458699</v>
       </c>
       <c r="R244" t="n">
-        <v>6808276</v>
+        <v>6808863</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -28270,7 +28270,7 @@
       </c>
       <c r="AC244" t="inlineStr">
         <is>
-          <t>Garnlav med miljöbild.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -29036,7 +29036,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>123729961</v>
+        <v>123733036</v>
       </c>
       <c r="B252" t="n">
         <v>78517</v>
@@ -29076,10 +29076,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>458680</v>
+        <v>458725</v>
       </c>
       <c r="R252" t="n">
-        <v>6808676</v>
+        <v>6808926</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -29116,7 +29116,7 @@
       </c>
       <c r="AC252" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -29143,7 +29143,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>123733036</v>
+        <v>123726510</v>
       </c>
       <c r="B253" t="n">
         <v>78517</v>
@@ -29179,14 +29179,14 @@
       <c r="I253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>458725</v>
+        <v>458940</v>
       </c>
       <c r="R253" t="n">
-        <v>6808926</v>
+        <v>6808345</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -29219,11 +29219,6 @@
       <c r="AA253" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -29250,7 +29245,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>123726510</v>
+        <v>123729961</v>
       </c>
       <c r="B254" t="n">
         <v>78517</v>
@@ -29286,14 +29281,14 @@
       <c r="I254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Dyvran, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>458940</v>
+        <v>458680</v>
       </c>
       <c r="R254" t="n">
-        <v>6808345</v>
+        <v>6808676</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -29326,6 +29321,11 @@
       <c r="AA254" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -30188,10 +30188,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>123731822</v>
+        <v>123723594</v>
       </c>
       <c r="B263" t="n">
-        <v>57487</v>
+        <v>78518</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -30204,39 +30204,34 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>458694</v>
+        <v>458948</v>
       </c>
       <c r="R263" t="n">
-        <v>6808720</v>
+        <v>6808276</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -30269,11 +30264,6 @@
       <c r="AA263" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC263" t="inlineStr">
-        <is>
-          <t>Troligt bo för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -30300,10 +30290,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>123723594</v>
+        <v>123731013</v>
       </c>
       <c r="B264" t="n">
-        <v>78518</v>
+        <v>79862</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -30316,34 +30306,34 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Dyvran, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>458948</v>
+        <v>458678</v>
       </c>
       <c r="R264" t="n">
-        <v>6808276</v>
+        <v>6808705</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -30402,10 +30392,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>123731013</v>
+        <v>123729221</v>
       </c>
       <c r="B265" t="n">
-        <v>79862</v>
+        <v>78781</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -30418,21 +30408,21 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -30442,10 +30432,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>458678</v>
+        <v>458783</v>
       </c>
       <c r="R265" t="n">
-        <v>6808705</v>
+        <v>6808546</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -30478,6 +30468,11 @@
       <c r="AA265" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>Garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -30504,10 +30499,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>123729221</v>
+        <v>123727363</v>
       </c>
       <c r="B266" t="n">
-        <v>78781</v>
+        <v>78518</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -30520,34 +30515,34 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>458783</v>
+        <v>458886</v>
       </c>
       <c r="R266" t="n">
-        <v>6808546</v>
+        <v>6808352</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -30580,11 +30575,6 @@
       <c r="AA266" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC266" t="inlineStr">
-        <is>
-          <t>Garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -30611,10 +30601,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>123727363</v>
+        <v>123727467</v>
       </c>
       <c r="B267" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -30627,21 +30617,21 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -30651,10 +30641,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>458886</v>
+        <v>458884</v>
       </c>
       <c r="R267" t="n">
-        <v>6808352</v>
+        <v>6808395</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -30687,6 +30677,11 @@
       <c r="AA267" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>Garnlav i en radie av ca 50 meter! Återkommande på speciellt tallstammar.</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -30713,7 +30708,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>123727467</v>
+        <v>123725953</v>
       </c>
       <c r="B268" t="n">
         <v>78781</v>
@@ -30753,10 +30748,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>458884</v>
+        <v>458928</v>
       </c>
       <c r="R268" t="n">
-        <v>6808395</v>
+        <v>6808305</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -30789,11 +30784,6 @@
       <c r="AA268" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>Garnlav i en radie av ca 50 meter! Återkommande på speciellt tallstammar.</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -30820,10 +30810,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>123725953</v>
+        <v>123729780</v>
       </c>
       <c r="B269" t="n">
-        <v>78781</v>
+        <v>78517</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -30836,34 +30826,34 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Dyvran, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>458928</v>
+        <v>458694</v>
       </c>
       <c r="R269" t="n">
-        <v>6808305</v>
+        <v>6808650</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -30896,6 +30886,11 @@
       <c r="AA269" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -30922,10 +30917,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>123729780</v>
+        <v>123730079</v>
       </c>
       <c r="B270" t="n">
-        <v>78517</v>
+        <v>57487</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -30938,34 +30933,39 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P270" t="inlineStr">
         <is>
           <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>458694</v>
+        <v>458669</v>
       </c>
       <c r="R270" t="n">
-        <v>6808650</v>
+        <v>6808687</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -30998,11 +30998,6 @@
       <c r="AA270" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC270" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -31029,10 +31024,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>123730079</v>
+        <v>123733103</v>
       </c>
       <c r="B271" t="n">
-        <v>57487</v>
+        <v>78781</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -31045,39 +31040,34 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P271" t="inlineStr">
         <is>
           <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>458669</v>
+        <v>458738</v>
       </c>
       <c r="R271" t="n">
-        <v>6808687</v>
+        <v>6808843</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -31136,7 +31126,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>123733103</v>
+        <v>123729517</v>
       </c>
       <c r="B272" t="n">
         <v>78781</v>
@@ -31176,10 +31166,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>458738</v>
+        <v>458715</v>
       </c>
       <c r="R272" t="n">
-        <v>6808843</v>
+        <v>6808620</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -31212,6 +31202,11 @@
       <c r="AA272" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>Garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -31238,7 +31233,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>123729517</v>
+        <v>123732178</v>
       </c>
       <c r="B273" t="n">
         <v>78781</v>
@@ -31278,10 +31273,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>458715</v>
+        <v>458742</v>
       </c>
       <c r="R273" t="n">
-        <v>6808620</v>
+        <v>6808732</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -31318,7 +31313,7 @@
       </c>
       <c r="AC273" t="inlineStr">
         <is>
-          <t>Garnlav i en radie av ca 50 meter.</t>
+          <t>Garnlav så långt jag ser, ca 50 meter i radie.</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -31345,10 +31340,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>123732178</v>
+        <v>123731822</v>
       </c>
       <c r="B274" t="n">
-        <v>78781</v>
+        <v>57487</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -31361,34 +31356,42 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
           <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>458742</v>
+        <v>458694</v>
       </c>
       <c r="R274" t="n">
-        <v>6808732</v>
+        <v>6808720</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -31425,7 +31428,7 @@
       </c>
       <c r="AC274" t="inlineStr">
         <is>
-          <t>Garnlav så långt jag ser, ca 50 meter i radie.</t>
+          <t>Troligt bo för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD274" t="b">

--- a/artfynd/A 13728-2025 artfynd.xlsx
+++ b/artfynd/A 13728-2025 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123548810</v>
+        <v>123542950</v>
       </c>
       <c r="B4" t="n">
-        <v>78525</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,37 +908,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459189</v>
+        <v>459697</v>
       </c>
       <c r="R4" t="n">
-        <v>6808830</v>
+        <v>6808925</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,12 +996,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1452,10 +1456,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123542950</v>
+        <v>123548810</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
+        <v>78525</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,41 +1472,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459697</v>
+        <v>459189</v>
       </c>
       <c r="R9" t="n">
-        <v>6808925</v>
+        <v>6808830</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,12 +1556,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1917,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123549501</v>
+        <v>123549559</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,41 +1929,49 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459367</v>
+        <v>459695</v>
       </c>
       <c r="R13" t="n">
-        <v>6808792</v>
+        <v>6808940</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1992,7 +2000,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2010,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Under betestall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,19 +2030,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123549549</v>
+        <v>123549501</v>
       </c>
       <c r="B14" t="n">
         <v>78788</v>
@@ -2069,10 +2082,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459415</v>
+        <v>459367</v>
       </c>
       <c r="R14" t="n">
-        <v>6808812</v>
+        <v>6808792</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2104,7 +2117,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2127,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,7 +2154,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123549709</v>
+        <v>123549549</v>
       </c>
       <c r="B15" t="n">
         <v>78788</v>
@@ -2181,10 +2194,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459458</v>
+        <v>459415</v>
       </c>
       <c r="R15" t="n">
-        <v>6808866</v>
+        <v>6808812</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2216,7 +2229,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,12 +2239,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:33</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På tallstammar flera</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,7 +2266,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123548510</v>
+        <v>123549709</v>
       </c>
       <c r="B16" t="n">
         <v>78788</v>
@@ -2294,17 +2302,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459172</v>
+        <v>459458</v>
       </c>
       <c r="R16" t="n">
-        <v>6808718</v>
+        <v>6808866</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2333,7 +2341,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2351,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På tallstammar flera</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,22 +2371,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123549559</v>
+        <v>123548510</v>
       </c>
       <c r="B17" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2382,49 +2395,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459695</v>
+        <v>459172</v>
       </c>
       <c r="R17" t="n">
-        <v>6808940</v>
+        <v>6808718</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2453,7 +2458,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2463,12 +2468,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Under betestall</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2483,22 +2483,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123549418</v>
+        <v>123549156</v>
       </c>
       <c r="B18" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2507,46 +2507,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459318</v>
+        <v>459240</v>
       </c>
       <c r="R18" t="n">
-        <v>6808809</v>
+        <v>6808794</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2575,7 +2570,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2585,12 +2580,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Under betestall</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2605,19 +2595,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123549156</v>
+        <v>123543987</v>
       </c>
       <c r="B19" t="n">
         <v>78788</v>
@@ -2657,10 +2647,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459240</v>
+        <v>459521</v>
       </c>
       <c r="R19" t="n">
-        <v>6808794</v>
+        <v>6808918</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2692,7 +2682,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2702,7 +2692,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2729,7 +2719,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123543987</v>
+        <v>123543499</v>
       </c>
       <c r="B20" t="n">
         <v>78788</v>
@@ -2769,13 +2759,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459521</v>
+        <v>459677</v>
       </c>
       <c r="R20" t="n">
-        <v>6808918</v>
+        <v>6808949</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2804,7 +2794,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2814,7 +2804,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På Gran blandat med skägglav</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2829,19 +2824,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123543499</v>
+        <v>123543842</v>
       </c>
       <c r="B21" t="n">
         <v>78788</v>
@@ -2881,10 +2876,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459677</v>
+        <v>459608</v>
       </c>
       <c r="R21" t="n">
-        <v>6808949</v>
+        <v>6809012</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2916,7 +2911,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2926,12 +2921,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På Gran blandat med skägglav</t>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2958,10 +2953,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123543842</v>
+        <v>123548636</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2974,37 +2969,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459608</v>
+        <v>459184</v>
       </c>
       <c r="R22" t="n">
-        <v>6809012</v>
+        <v>6808784</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3033,7 +3028,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3043,12 +3038,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På Gran</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3063,22 +3053,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123548636</v>
+        <v>123548196</v>
       </c>
       <c r="B23" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3091,34 +3081,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459184</v>
+        <v>459024</v>
       </c>
       <c r="R23" t="n">
-        <v>6808784</v>
+        <v>6808872</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3150,7 +3140,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3160,7 +3150,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3187,10 +3177,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123548196</v>
+        <v>123549418</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3199,41 +3189,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459024</v>
+        <v>459318</v>
       </c>
       <c r="R24" t="n">
-        <v>6808872</v>
+        <v>6808809</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3262,7 +3257,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3272,7 +3267,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Under betestall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3287,22 +3287,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123544364</v>
+        <v>123546440</v>
       </c>
       <c r="B25" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3315,21 +3315,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3345,7 +3345,7 @@
         <v>6808917</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3411,10 +3411,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123546440</v>
+        <v>123544364</v>
       </c>
       <c r="B26" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3427,21 +3427,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3457,7 +3457,7 @@
         <v>6808917</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3523,10 +3523,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123544485</v>
+        <v>123543850</v>
       </c>
       <c r="B27" t="n">
-        <v>5176</v>
+        <v>78788</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3535,46 +3535,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459504</v>
+        <v>459606</v>
       </c>
       <c r="R27" t="n">
-        <v>6809063</v>
+        <v>6808918</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3603,7 +3598,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3613,7 +3608,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3628,19 +3623,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123543850</v>
+        <v>123549200</v>
       </c>
       <c r="B28" t="n">
         <v>78788</v>
@@ -3680,13 +3675,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459606</v>
+        <v>459265</v>
       </c>
       <c r="R28" t="n">
-        <v>6808918</v>
+        <v>6808827</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3715,7 +3710,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3725,7 +3720,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3740,22 +3735,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123549200</v>
+        <v>123544485</v>
       </c>
       <c r="B29" t="n">
-        <v>78788</v>
+        <v>5176</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3764,38 +3759,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459265</v>
+        <v>459504</v>
       </c>
       <c r="R29" t="n">
-        <v>6808827</v>
+        <v>6809063</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4551,10 +4551,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123549137</v>
+        <v>123546049</v>
       </c>
       <c r="B36" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4567,37 +4567,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459240</v>
+        <v>459128</v>
       </c>
       <c r="R36" t="n">
-        <v>6808796</v>
+        <v>6809008</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4651,22 +4651,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123543087</v>
+        <v>123548646</v>
       </c>
       <c r="B37" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4679,34 +4679,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459627</v>
+        <v>459185</v>
       </c>
       <c r="R37" t="n">
-        <v>6808925</v>
+        <v>6808785</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4775,7 +4775,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123545274</v>
+        <v>123549137</v>
       </c>
       <c r="B38" t="n">
         <v>78788</v>
@@ -4811,14 +4811,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459304</v>
+        <v>459240</v>
       </c>
       <c r="R38" t="n">
-        <v>6809019</v>
+        <v>6808796</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4887,10 +4887,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123546049</v>
+        <v>123543087</v>
       </c>
       <c r="B39" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4903,37 +4903,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459128</v>
+        <v>459627</v>
       </c>
       <c r="R39" t="n">
-        <v>6809008</v>
+        <v>6808925</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4987,22 +4987,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123548646</v>
+        <v>123545274</v>
       </c>
       <c r="B40" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5015,34 +5015,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459185</v>
+        <v>459304</v>
       </c>
       <c r="R40" t="n">
-        <v>6808785</v>
+        <v>6809019</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -10662,10 +10662,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123566723</v>
+        <v>123566063</v>
       </c>
       <c r="B90" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10678,21 +10678,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10702,10 +10702,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>459751</v>
+        <v>459745</v>
       </c>
       <c r="R90" t="n">
-        <v>6808886</v>
+        <v>6808895</v>
       </c>
       <c r="S90" t="n">
         <v>9</v>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10774,10 +10774,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123564558</v>
+        <v>123577141</v>
       </c>
       <c r="B91" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10790,37 +10790,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>459732</v>
+        <v>459462</v>
       </c>
       <c r="R91" t="n">
-        <v>6808815</v>
+        <v>6808627</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10874,19 +10874,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123566087</v>
+        <v>123566723</v>
       </c>
       <c r="B92" t="n">
         <v>78788</v>
@@ -10926,13 +10926,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>459733</v>
+        <v>459751</v>
       </c>
       <c r="R92" t="n">
-        <v>6808745</v>
+        <v>6808886</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10986,19 +10986,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123575662</v>
+        <v>123564558</v>
       </c>
       <c r="B93" t="n">
         <v>78788</v>
@@ -11034,17 +11034,17 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>459583</v>
+        <v>459732</v>
       </c>
       <c r="R93" t="n">
-        <v>6808519</v>
+        <v>6808815</v>
       </c>
       <c r="S93" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11098,19 +11098,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123576104</v>
+        <v>123566087</v>
       </c>
       <c r="B94" t="n">
         <v>78788</v>
@@ -11146,17 +11146,17 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>459515</v>
+        <v>459733</v>
       </c>
       <c r="R94" t="n">
-        <v>6808562</v>
+        <v>6808745</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11195,7 +11195,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11222,7 +11222,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123564616</v>
+        <v>123575662</v>
       </c>
       <c r="B95" t="n">
         <v>78788</v>
@@ -11258,17 +11258,17 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>459687</v>
+        <v>459583</v>
       </c>
       <c r="R95" t="n">
-        <v>6808829</v>
+        <v>6808519</v>
       </c>
       <c r="S95" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11334,10 +11334,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123566063</v>
+        <v>123576104</v>
       </c>
       <c r="B96" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11350,37 +11350,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>459745</v>
+        <v>459515</v>
       </c>
       <c r="R96" t="n">
-        <v>6808895</v>
+        <v>6808562</v>
       </c>
       <c r="S96" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11434,22 +11434,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123577141</v>
+        <v>123564616</v>
       </c>
       <c r="B97" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11462,37 +11462,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>459462</v>
+        <v>459687</v>
       </c>
       <c r="R97" t="n">
-        <v>6808627</v>
+        <v>6808829</v>
       </c>
       <c r="S97" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11546,12 +11546,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -16311,10 +16311,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>123577149</v>
+        <v>123566355</v>
       </c>
       <c r="B140" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16327,37 +16327,37 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>459571</v>
+        <v>459762</v>
       </c>
       <c r="R140" t="n">
-        <v>6808546</v>
+        <v>6808880</v>
       </c>
       <c r="S140" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16396,7 +16396,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16411,22 +16411,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>123577066</v>
+        <v>123564834</v>
       </c>
       <c r="B141" t="n">
-        <v>56700</v>
+        <v>79406</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16435,46 +16435,41 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>459565</v>
+        <v>459734</v>
       </c>
       <c r="R141" t="n">
-        <v>6808543</v>
+        <v>6808814</v>
       </c>
       <c r="S141" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16503,7 +16498,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16513,7 +16508,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16528,19 +16523,19 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>123566355</v>
+        <v>123565429</v>
       </c>
       <c r="B142" t="n">
         <v>78788</v>
@@ -16580,10 +16575,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>459762</v>
+        <v>459753</v>
       </c>
       <c r="R142" t="n">
-        <v>6808880</v>
+        <v>6808887</v>
       </c>
       <c r="S142" t="n">
         <v>9</v>
@@ -16615,7 +16610,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16625,7 +16620,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16652,10 +16647,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>123564834</v>
+        <v>123563857</v>
       </c>
       <c r="B143" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16668,21 +16663,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16692,10 +16687,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>459734</v>
+        <v>459731</v>
       </c>
       <c r="R143" t="n">
-        <v>6808814</v>
+        <v>6808890</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -16727,7 +16722,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16737,7 +16732,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16764,7 +16759,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>123565429</v>
+        <v>123573297</v>
       </c>
       <c r="B144" t="n">
         <v>78788</v>
@@ -16800,14 +16795,14 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>459753</v>
+        <v>459736</v>
       </c>
       <c r="R144" t="n">
-        <v>6808887</v>
+        <v>6808577</v>
       </c>
       <c r="S144" t="n">
         <v>9</v>
@@ -16839,7 +16834,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16849,7 +16844,12 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16876,10 +16876,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>123563857</v>
+        <v>123577066</v>
       </c>
       <c r="B145" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16888,41 +16888,46 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>459731</v>
+        <v>459565</v>
       </c>
       <c r="R145" t="n">
-        <v>6808890</v>
+        <v>6808543</v>
       </c>
       <c r="S145" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16951,7 +16956,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16961,7 +16966,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16976,22 +16981,22 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>123573297</v>
+        <v>123577149</v>
       </c>
       <c r="B146" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -17004,21 +17009,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -17028,13 +17033,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>459736</v>
+        <v>459571</v>
       </c>
       <c r="R146" t="n">
-        <v>6808577</v>
+        <v>6808546</v>
       </c>
       <c r="S146" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -17063,7 +17068,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17073,12 +17078,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17093,12 +17093,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -17329,10 +17329,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>123575257</v>
+        <v>123576740</v>
       </c>
       <c r="B149" t="n">
-        <v>78525</v>
+        <v>79377</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17345,21 +17345,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17369,13 +17369,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>459595</v>
+        <v>459565</v>
       </c>
       <c r="R149" t="n">
-        <v>6808516</v>
+        <v>6808543</v>
       </c>
       <c r="S149" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17414,7 +17414,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17441,10 +17441,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>123576740</v>
+        <v>123575257</v>
       </c>
       <c r="B150" t="n">
-        <v>79377</v>
+        <v>78525</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17457,21 +17457,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17481,13 +17481,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>459565</v>
+        <v>459595</v>
       </c>
       <c r="R150" t="n">
-        <v>6808543</v>
+        <v>6808516</v>
       </c>
       <c r="S150" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17894,10 +17894,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>123575865</v>
+        <v>123577363</v>
       </c>
       <c r="B154" t="n">
-        <v>79377</v>
+        <v>78525</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17910,37 +17910,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>459707</v>
+        <v>459424</v>
       </c>
       <c r="R154" t="n">
-        <v>6808935</v>
+        <v>6808673</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17979,7 +17979,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17994,22 +17994,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>123577363</v>
+        <v>123575486</v>
       </c>
       <c r="B155" t="n">
-        <v>78525</v>
+        <v>79377</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18022,21 +18022,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -18046,13 +18046,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>459424</v>
+        <v>459595</v>
       </c>
       <c r="R155" t="n">
-        <v>6808673</v>
+        <v>6808516</v>
       </c>
       <c r="S155" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18091,7 +18091,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18106,19 +18106,19 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>123575486</v>
+        <v>123575865</v>
       </c>
       <c r="B156" t="n">
         <v>79377</v>
@@ -18154,17 +18154,17 @@
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>459595</v>
+        <v>459707</v>
       </c>
       <c r="R156" t="n">
-        <v>6808516</v>
+        <v>6808935</v>
       </c>
       <c r="S156" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18203,7 +18203,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18218,12 +18218,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -27874,10 +27874,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>123732682</v>
+        <v>123727583</v>
       </c>
       <c r="B241" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -27886,38 +27886,38 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>458711</v>
+        <v>458880</v>
       </c>
       <c r="R241" t="n">
-        <v>6808858</v>
+        <v>6808416</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27954,7 +27954,7 @@
       </c>
       <c r="AC241" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Tjäderspillning under tjädertall med garnlav.</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -27981,10 +27981,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>123727583</v>
+        <v>123730079</v>
       </c>
       <c r="B242" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -27993,38 +27993,43 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Dyvran, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>458880</v>
+        <v>458669</v>
       </c>
       <c r="R242" t="n">
-        <v>6808416</v>
+        <v>6808687</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -28057,11 +28062,6 @@
       <c r="AA242" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC242" t="inlineStr">
-        <is>
-          <t>Tjäderspillning under tjädertall med garnlav.</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -28088,10 +28088,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>123730079</v>
+        <v>123732682</v>
       </c>
       <c r="B243" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -28104,39 +28104,34 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P243" t="inlineStr">
         <is>
           <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>458669</v>
+        <v>458711</v>
       </c>
       <c r="R243" t="n">
-        <v>6808687</v>
+        <v>6808858</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -28169,6 +28164,11 @@
       <c r="AA243" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -32383,10 +32383,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>123822130</v>
+        <v>123834650</v>
       </c>
       <c r="B284" t="n">
-        <v>56700</v>
+        <v>78525</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -32395,43 +32395,38 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
-      <c r="M284" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P284" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>458948</v>
+        <v>459399</v>
       </c>
       <c r="R284" t="n">
-        <v>6808785</v>
+        <v>6808189</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -32461,19 +32456,14 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="Z284" t="inlineStr">
-        <is>
-          <t>09:09</t>
-        </is>
-      </c>
       <c r="AA284" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AB284" t="inlineStr">
-        <is>
-          <t>09:09</t>
+      <c r="AC284" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD284" t="b">
@@ -32488,12 +32478,12 @@
       <c r="AT284" t="inlineStr"/>
       <c r="AW284" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
@@ -33550,10 +33540,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>123834650</v>
+        <v>123822130</v>
       </c>
       <c r="B295" t="n">
-        <v>78525</v>
+        <v>56700</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -33562,38 +33552,43 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>459399</v>
+        <v>458948</v>
       </c>
       <c r="R295" t="n">
-        <v>6808189</v>
+        <v>6808785</v>
       </c>
       <c r="S295" t="n">
         <v>10</v>
@@ -33623,14 +33618,19 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="Z295" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
       <c r="AA295" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC295" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
+      <c r="AB295" t="inlineStr">
+        <is>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD295" t="b">
@@ -33645,12 +33645,12 @@
       <c r="AT295" t="inlineStr"/>
       <c r="AW295" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX295" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
@@ -35140,10 +35140,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>123829121</v>
+        <v>123827321</v>
       </c>
       <c r="B310" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -35156,34 +35156,34 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
       <c r="P310" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>459641</v>
+        <v>458750</v>
       </c>
       <c r="R310" t="n">
-        <v>6807971</v>
+        <v>6808601</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -35218,11 +35218,6 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC310" t="inlineStr">
-        <is>
-          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD310" t="b">
         <v>0</v>
       </c>
@@ -35235,22 +35230,22 @@
       <c r="AT310" t="inlineStr"/>
       <c r="AW310" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>123827329</v>
+        <v>123828892</v>
       </c>
       <c r="B311" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -35263,37 +35258,37 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
       <c r="P311" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>459664</v>
+        <v>459465</v>
       </c>
       <c r="R311" t="n">
-        <v>6808159</v>
+        <v>6808411</v>
       </c>
       <c r="S311" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T311" t="inlineStr">
         <is>
@@ -35337,22 +35332,22 @@
       <c r="AT311" t="inlineStr"/>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>123834034</v>
+        <v>123834998</v>
       </c>
       <c r="B312" t="n">
-        <v>57507</v>
+        <v>79377</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -35365,42 +35360,37 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I312" t="inlineStr"/>
-      <c r="M312" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P312" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>459325</v>
+        <v>459437</v>
       </c>
       <c r="R312" t="n">
-        <v>6808176</v>
+        <v>6808171</v>
       </c>
       <c r="S312" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T312" t="inlineStr">
         <is>
@@ -35430,11 +35420,6 @@
       <c r="AA312" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC312" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD312" t="b">
@@ -35449,22 +35434,22 @@
       <c r="AT312" t="inlineStr"/>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>123827321</v>
+        <v>123829121</v>
       </c>
       <c r="B313" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -35477,34 +35462,34 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I313" t="inlineStr"/>
       <c r="P313" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>458750</v>
+        <v>459641</v>
       </c>
       <c r="R313" t="n">
-        <v>6808601</v>
+        <v>6807971</v>
       </c>
       <c r="S313" t="n">
         <v>10</v>
@@ -35539,6 +35524,11 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AC313" t="inlineStr">
+        <is>
+          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD313" t="b">
         <v>0</v>
       </c>
@@ -35551,22 +35541,22 @@
       <c r="AT313" t="inlineStr"/>
       <c r="AW313" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX313" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>123828892</v>
+        <v>123827329</v>
       </c>
       <c r="B314" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -35579,37 +35569,37 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
       <c r="P314" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>459465</v>
+        <v>459664</v>
       </c>
       <c r="R314" t="n">
-        <v>6808411</v>
+        <v>6808159</v>
       </c>
       <c r="S314" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T314" t="inlineStr">
         <is>
@@ -35653,22 +35643,22 @@
       <c r="AT314" t="inlineStr"/>
       <c r="AW314" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX314" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>123834998</v>
+        <v>123834034</v>
       </c>
       <c r="B315" t="n">
-        <v>79377</v>
+        <v>57507</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -35681,37 +35671,42 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I315" t="inlineStr"/>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>459437</v>
+        <v>459325</v>
       </c>
       <c r="R315" t="n">
-        <v>6808171</v>
+        <v>6808176</v>
       </c>
       <c r="S315" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T315" t="inlineStr">
         <is>
@@ -35741,6 +35736,11 @@
       <c r="AA315" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC315" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD315" t="b">
@@ -35755,12 +35755,12 @@
       <c r="AT315" t="inlineStr"/>
       <c r="AW315" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
@@ -36491,10 +36491,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>123831244</v>
+        <v>123833814</v>
       </c>
       <c r="B323" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -36507,37 +36507,37 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
       <c r="P323" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>459393</v>
+        <v>459293</v>
       </c>
       <c r="R323" t="n">
-        <v>6808027</v>
+        <v>6808123</v>
       </c>
       <c r="S323" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T323" t="inlineStr">
         <is>
@@ -36581,19 +36581,19 @@
       <c r="AT323" t="inlineStr"/>
       <c r="AW323" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX323" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>123833814</v>
+        <v>123829438</v>
       </c>
       <c r="B324" t="n">
         <v>78525</v>
@@ -36633,10 +36633,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>459293</v>
+        <v>459113</v>
       </c>
       <c r="R324" t="n">
-        <v>6808123</v>
+        <v>6808380</v>
       </c>
       <c r="S324" t="n">
         <v>15</v>
@@ -36695,10 +36695,10 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>123829348</v>
+        <v>123831244</v>
       </c>
       <c r="B325" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -36711,37 +36711,37 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I325" t="inlineStr"/>
       <c r="P325" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>459230</v>
+        <v>459393</v>
       </c>
       <c r="R325" t="n">
-        <v>6808362</v>
+        <v>6808027</v>
       </c>
       <c r="S325" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T325" t="inlineStr">
         <is>
@@ -36785,19 +36785,19 @@
       <c r="AT325" t="inlineStr"/>
       <c r="AW325" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX325" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>123829438</v>
+        <v>123829348</v>
       </c>
       <c r="B326" t="n">
         <v>78525</v>
@@ -36837,10 +36837,10 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>459113</v>
+        <v>459230</v>
       </c>
       <c r="R326" t="n">
-        <v>6808380</v>
+        <v>6808362</v>
       </c>
       <c r="S326" t="n">
         <v>15</v>
@@ -39432,10 +39432,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>123827028</v>
+        <v>123820832</v>
       </c>
       <c r="B351" t="n">
-        <v>78788</v>
+        <v>56703</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -39444,41 +39444,55 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I351" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P351" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>459725</v>
+        <v>459400</v>
       </c>
       <c r="R351" t="n">
-        <v>6808300</v>
+        <v>6809033</v>
       </c>
       <c r="S351" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T351" t="inlineStr">
         <is>
@@ -39505,9 +39519,19 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="Z351" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
       <c r="AA351" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB351" t="inlineStr">
+        <is>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AD351" t="b">
@@ -39522,22 +39546,22 @@
       <c r="AT351" t="inlineStr"/>
       <c r="AW351" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX351" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>123827325</v>
+        <v>123827028</v>
       </c>
       <c r="B352" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
@@ -39550,37 +39574,37 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I352" t="inlineStr"/>
       <c r="P352" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>458750</v>
+        <v>459725</v>
       </c>
       <c r="R352" t="n">
-        <v>6808601</v>
+        <v>6808300</v>
       </c>
       <c r="S352" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T352" t="inlineStr">
         <is>
@@ -39624,22 +39648,22 @@
       <c r="AT352" t="inlineStr"/>
       <c r="AW352" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX352" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>123820832</v>
+        <v>123827325</v>
       </c>
       <c r="B353" t="n">
-        <v>56703</v>
+        <v>78524</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -39648,55 +39672,41 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>102613</v>
+        <v>6446</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I353" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L353" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M353" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr"/>
       <c r="P353" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>459400</v>
+        <v>458750</v>
       </c>
       <c r="R353" t="n">
-        <v>6809033</v>
+        <v>6808601</v>
       </c>
       <c r="S353" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T353" t="inlineStr">
         <is>
@@ -39723,19 +39733,9 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="Z353" t="inlineStr">
-        <is>
-          <t>07:52</t>
-        </is>
-      </c>
       <c r="AA353" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AB353" t="inlineStr">
-        <is>
-          <t>07:52</t>
         </is>
       </c>
       <c r="AD353" t="b">
@@ -40720,10 +40720,10 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>123828476</v>
+        <v>123829889</v>
       </c>
       <c r="B363" t="n">
-        <v>79869</v>
+        <v>78525</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -40736,37 +40736,37 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I363" t="inlineStr"/>
       <c r="P363" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>459649</v>
+        <v>459494</v>
       </c>
       <c r="R363" t="n">
-        <v>6808146</v>
+        <v>6807997</v>
       </c>
       <c r="S363" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T363" t="inlineStr">
         <is>
@@ -40796,6 +40796,11 @@
       <c r="AA363" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC363" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD363" t="b">
@@ -40810,22 +40815,22 @@
       <c r="AT363" t="inlineStr"/>
       <c r="AW363" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX363" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>123828981</v>
+        <v>123828476</v>
       </c>
       <c r="B364" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
@@ -40838,37 +40843,37 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I364" t="inlineStr"/>
       <c r="P364" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q364" t="n">
-        <v>459275</v>
+        <v>459649</v>
       </c>
       <c r="R364" t="n">
-        <v>6808519</v>
+        <v>6808146</v>
       </c>
       <c r="S364" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T364" t="inlineStr">
         <is>
@@ -40912,19 +40917,19 @@
       <c r="AT364" t="inlineStr"/>
       <c r="AW364" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX364" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>123835322</v>
+        <v>123828981</v>
       </c>
       <c r="B365" t="n">
         <v>78788</v>
@@ -40964,10 +40969,10 @@
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>459636</v>
+        <v>459275</v>
       </c>
       <c r="R365" t="n">
-        <v>6808203</v>
+        <v>6808519</v>
       </c>
       <c r="S365" t="n">
         <v>10</v>
@@ -41014,22 +41019,22 @@
       <c r="AT365" t="inlineStr"/>
       <c r="AW365" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX365" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>123829889</v>
+        <v>123835322</v>
       </c>
       <c r="B366" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
@@ -41042,34 +41047,34 @@
         </is>
       </c>
       <c r="E366" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I366" t="inlineStr"/>
       <c r="P366" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q366" t="n">
-        <v>459494</v>
+        <v>459636</v>
       </c>
       <c r="R366" t="n">
-        <v>6807997</v>
+        <v>6808203</v>
       </c>
       <c r="S366" t="n">
         <v>10</v>
@@ -41104,11 +41109,6 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC366" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD366" t="b">
         <v>0</v>
       </c>
@@ -41121,12 +41121,12 @@
       <c r="AT366" t="inlineStr"/>
       <c r="AW366" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX366" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY366" t="inlineStr"/>
@@ -43243,10 +43243,10 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>123834966</v>
+        <v>123829197</v>
       </c>
       <c r="B387" t="n">
-        <v>57512</v>
+        <v>78525</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -43255,46 +43255,41 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>100110</v>
+        <v>228912</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I387" t="inlineStr"/>
-      <c r="M387" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P387" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>459399</v>
+        <v>459611</v>
       </c>
       <c r="R387" t="n">
-        <v>6808189</v>
+        <v>6807987</v>
       </c>
       <c r="S387" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T387" t="inlineStr">
         <is>
@@ -43324,11 +43319,6 @@
       <c r="AA387" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC387" t="inlineStr">
-        <is>
-          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD387" t="b">
@@ -43343,19 +43333,19 @@
       <c r="AT387" t="inlineStr"/>
       <c r="AW387" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX387" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>123833917</v>
+        <v>123826342</v>
       </c>
       <c r="B388" t="n">
         <v>78525</v>
@@ -43391,17 +43381,17 @@
       <c r="I388" t="inlineStr"/>
       <c r="P388" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>459292</v>
+        <v>458975</v>
       </c>
       <c r="R388" t="n">
-        <v>6808184</v>
+        <v>6808922</v>
       </c>
       <c r="S388" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T388" t="inlineStr">
         <is>
@@ -43428,9 +43418,19 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="Z388" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA388" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB388" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD388" t="b">
@@ -43445,19 +43445,19 @@
       <c r="AT388" t="inlineStr"/>
       <c r="AW388" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX388" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>123829197</v>
+        <v>123833917</v>
       </c>
       <c r="B389" t="n">
         <v>78525</v>
@@ -43497,10 +43497,10 @@
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>459611</v>
+        <v>459292</v>
       </c>
       <c r="R389" t="n">
-        <v>6807987</v>
+        <v>6808184</v>
       </c>
       <c r="S389" t="n">
         <v>20</v>
@@ -43559,10 +43559,10 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>123826342</v>
+        <v>123834966</v>
       </c>
       <c r="B390" t="n">
-        <v>78525</v>
+        <v>57512</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
@@ -43571,38 +43571,43 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E390" t="n">
-        <v>228912</v>
+        <v>100110</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I390" t="inlineStr"/>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P390" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>458975</v>
+        <v>459399</v>
       </c>
       <c r="R390" t="n">
-        <v>6808922</v>
+        <v>6808189</v>
       </c>
       <c r="S390" t="n">
         <v>10</v>
@@ -43632,19 +43637,14 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="Z390" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA390" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AB390" t="inlineStr">
-        <is>
-          <t>11:53</t>
+      <c r="AC390" t="inlineStr">
+        <is>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD390" t="b">
@@ -43659,12 +43659,12 @@
       <c r="AT390" t="inlineStr"/>
       <c r="AW390" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX390" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY390" t="inlineStr"/>
@@ -43773,10 +43773,10 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>123822771</v>
+        <v>123822912</v>
       </c>
       <c r="B392" t="n">
-        <v>56700</v>
+        <v>57644</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
@@ -43785,31 +43785,31 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E392" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I392" t="inlineStr"/>
       <c r="M392" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P392" t="inlineStr">
@@ -43818,10 +43818,10 @@
         </is>
       </c>
       <c r="Q392" t="n">
-        <v>459307</v>
+        <v>459118</v>
       </c>
       <c r="R392" t="n">
-        <v>6808524</v>
+        <v>6808615</v>
       </c>
       <c r="S392" t="n">
         <v>10</v>
@@ -43853,7 +43853,7 @@
       </c>
       <c r="Z392" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA392" t="inlineStr">
@@ -43863,7 +43863,7 @@
       </c>
       <c r="AB392" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD392" t="b">
@@ -43890,10 +43890,10 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>123822912</v>
+        <v>123828044</v>
       </c>
       <c r="B393" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C393" t="inlineStr">
         <is>
@@ -43906,39 +43906,34 @@
         </is>
       </c>
       <c r="E393" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I393" t="inlineStr"/>
-      <c r="M393" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P393" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q393" t="n">
-        <v>459118</v>
+        <v>459681</v>
       </c>
       <c r="R393" t="n">
-        <v>6808615</v>
+        <v>6808072</v>
       </c>
       <c r="S393" t="n">
         <v>10</v>
@@ -43968,19 +43963,14 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="Z393" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AA393" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AB393" t="inlineStr">
-        <is>
-          <t>09:56</t>
+      <c r="AC393" t="inlineStr">
+        <is>
+          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD393" t="b">
@@ -43995,19 +43985,19 @@
       <c r="AT393" t="inlineStr"/>
       <c r="AW393" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX393" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>123828044</v>
+        <v>123834641</v>
       </c>
       <c r="B394" t="n">
         <v>78788</v>
@@ -44043,17 +44033,17 @@
       <c r="I394" t="inlineStr"/>
       <c r="P394" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q394" t="n">
-        <v>459681</v>
+        <v>459405</v>
       </c>
       <c r="R394" t="n">
-        <v>6808072</v>
+        <v>6808172</v>
       </c>
       <c r="S394" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T394" t="inlineStr">
         <is>
@@ -44083,11 +44073,6 @@
       <c r="AA394" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC394" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD394" t="b">
@@ -44102,22 +44087,22 @@
       <c r="AT394" t="inlineStr"/>
       <c r="AW394" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX394" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>123834641</v>
+        <v>123822771</v>
       </c>
       <c r="B395" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
@@ -44126,41 +44111,46 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E395" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I395" t="inlineStr"/>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P395" t="inlineStr">
         <is>
           <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q395" t="n">
-        <v>459405</v>
+        <v>459307</v>
       </c>
       <c r="R395" t="n">
-        <v>6808172</v>
+        <v>6808524</v>
       </c>
       <c r="S395" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T395" t="inlineStr">
         <is>
@@ -44187,9 +44177,19 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="Z395" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA395" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB395" t="inlineStr">
+        <is>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD395" t="b">
@@ -44204,12 +44204,12 @@
       <c r="AT395" t="inlineStr"/>
       <c r="AW395" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX395" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY395" t="inlineStr"/>
@@ -44532,10 +44532,10 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>123829270</v>
+        <v>123829275</v>
       </c>
       <c r="B399" t="n">
-        <v>78883</v>
+        <v>78525</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
@@ -44548,37 +44548,37 @@
         </is>
       </c>
       <c r="E399" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I399" t="inlineStr"/>
       <c r="P399" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q399" t="n">
-        <v>459310</v>
+        <v>459544</v>
       </c>
       <c r="R399" t="n">
-        <v>6808409</v>
+        <v>6807989</v>
       </c>
       <c r="S399" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T399" t="inlineStr">
         <is>
@@ -44622,22 +44622,22 @@
       <c r="AT399" t="inlineStr"/>
       <c r="AW399" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX399" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>123834890</v>
+        <v>123829270</v>
       </c>
       <c r="B400" t="n">
-        <v>78867</v>
+        <v>78883</v>
       </c>
       <c r="C400" t="inlineStr">
         <is>
@@ -44650,21 +44650,21 @@
         </is>
       </c>
       <c r="E400" t="n">
-        <v>864</v>
+        <v>967</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I400" t="inlineStr"/>
@@ -44674,13 +44674,13 @@
         </is>
       </c>
       <c r="Q400" t="n">
-        <v>459427</v>
+        <v>459310</v>
       </c>
       <c r="R400" t="n">
-        <v>6808130</v>
+        <v>6808409</v>
       </c>
       <c r="S400" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T400" t="inlineStr">
         <is>
@@ -44724,22 +44724,22 @@
       <c r="AT400" t="inlineStr"/>
       <c r="AW400" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX400" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>123829684</v>
+        <v>123834890</v>
       </c>
       <c r="B401" t="n">
-        <v>78788</v>
+        <v>78867</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
@@ -44752,21 +44752,21 @@
         </is>
       </c>
       <c r="E401" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I401" t="inlineStr"/>
@@ -44776,13 +44776,13 @@
         </is>
       </c>
       <c r="Q401" t="n">
-        <v>458980</v>
+        <v>459427</v>
       </c>
       <c r="R401" t="n">
-        <v>6808290</v>
+        <v>6808130</v>
       </c>
       <c r="S401" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T401" t="inlineStr">
         <is>
@@ -44826,22 +44826,22 @@
       <c r="AT401" t="inlineStr"/>
       <c r="AW401" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX401" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>123829275</v>
+        <v>123829684</v>
       </c>
       <c r="B402" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
@@ -44854,37 +44854,37 @@
         </is>
       </c>
       <c r="E402" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I402" t="inlineStr"/>
       <c r="P402" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q402" t="n">
-        <v>459544</v>
+        <v>458980</v>
       </c>
       <c r="R402" t="n">
-        <v>6807989</v>
+        <v>6808290</v>
       </c>
       <c r="S402" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T402" t="inlineStr">
         <is>
@@ -44928,12 +44928,12 @@
       <c r="AT402" t="inlineStr"/>
       <c r="AW402" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX402" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY402" t="inlineStr"/>
@@ -47371,10 +47371,10 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>123866301</v>
+        <v>123866513</v>
       </c>
       <c r="B426" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
@@ -47387,37 +47387,37 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I426" t="inlineStr"/>
       <c r="P426" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q426" t="n">
-        <v>459260</v>
+        <v>459177</v>
       </c>
       <c r="R426" t="n">
-        <v>6808646</v>
+        <v>6808709</v>
       </c>
       <c r="S426" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T426" t="inlineStr">
         <is>
@@ -47461,19 +47461,19 @@
       <c r="AT426" t="inlineStr"/>
       <c r="AW426" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX426" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>123866613</v>
+        <v>123866301</v>
       </c>
       <c r="B427" t="n">
         <v>79377</v>
@@ -47513,13 +47513,13 @@
         </is>
       </c>
       <c r="Q427" t="n">
-        <v>459110</v>
+        <v>459260</v>
       </c>
       <c r="R427" t="n">
-        <v>6808718</v>
+        <v>6808646</v>
       </c>
       <c r="S427" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T427" t="inlineStr">
         <is>
@@ -47575,10 +47575,10 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>123866513</v>
+        <v>123866613</v>
       </c>
       <c r="B428" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
@@ -47591,37 +47591,37 @@
         </is>
       </c>
       <c r="E428" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I428" t="inlineStr"/>
       <c r="P428" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q428" t="n">
-        <v>459177</v>
+        <v>459110</v>
       </c>
       <c r="R428" t="n">
-        <v>6808709</v>
+        <v>6808718</v>
       </c>
       <c r="S428" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T428" t="inlineStr">
         <is>
@@ -47665,12 +47665,12 @@
       <c r="AT428" t="inlineStr"/>
       <c r="AW428" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX428" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY428" t="inlineStr"/>
@@ -48105,10 +48105,10 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>123865793</v>
+        <v>123866998</v>
       </c>
       <c r="B433" t="n">
-        <v>56700</v>
+        <v>79377</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
@@ -48117,46 +48117,41 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E433" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I433" t="inlineStr"/>
-      <c r="M433" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P433" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q433" t="n">
-        <v>459341</v>
+        <v>458925</v>
       </c>
       <c r="R433" t="n">
-        <v>6808761</v>
+        <v>6808789</v>
       </c>
       <c r="S433" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T433" t="inlineStr">
         <is>
@@ -48200,22 +48195,22 @@
       <c r="AT433" t="inlineStr"/>
       <c r="AW433" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX433" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>123868751</v>
+        <v>123865793</v>
       </c>
       <c r="B434" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
@@ -48224,41 +48219,46 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E434" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I434" t="inlineStr"/>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P434" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q434" t="n">
-        <v>459228</v>
+        <v>459341</v>
       </c>
       <c r="R434" t="n">
-        <v>6808886</v>
+        <v>6808761</v>
       </c>
       <c r="S434" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T434" t="inlineStr">
         <is>
@@ -48302,19 +48302,19 @@
       <c r="AT434" t="inlineStr"/>
       <c r="AW434" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX434" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>123868109</v>
+        <v>123868751</v>
       </c>
       <c r="B435" t="n">
         <v>78788</v>
@@ -48354,13 +48354,13 @@
         </is>
       </c>
       <c r="Q435" t="n">
-        <v>458928</v>
+        <v>459228</v>
       </c>
       <c r="R435" t="n">
-        <v>6808926</v>
+        <v>6808886</v>
       </c>
       <c r="S435" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T435" t="inlineStr">
         <is>
@@ -48416,10 +48416,10 @@
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>123866998</v>
+        <v>123868109</v>
       </c>
       <c r="B436" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
@@ -48432,37 +48432,37 @@
         </is>
       </c>
       <c r="E436" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I436" t="inlineStr"/>
       <c r="P436" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q436" t="n">
-        <v>458925</v>
+        <v>458928</v>
       </c>
       <c r="R436" t="n">
-        <v>6808789</v>
+        <v>6808926</v>
       </c>
       <c r="S436" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T436" t="inlineStr">
         <is>
@@ -48506,12 +48506,12 @@
       <c r="AT436" t="inlineStr"/>
       <c r="AW436" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX436" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY436" t="inlineStr"/>
@@ -48620,10 +48620,10 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>123869983</v>
+        <v>123867031</v>
       </c>
       <c r="B438" t="n">
-        <v>57491</v>
+        <v>78525</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
@@ -48636,42 +48636,37 @@
         </is>
       </c>
       <c r="E438" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I438" t="inlineStr"/>
-      <c r="M438" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P438" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q438" t="n">
-        <v>459708</v>
+        <v>458879</v>
       </c>
       <c r="R438" t="n">
-        <v>6808890</v>
+        <v>6808768</v>
       </c>
       <c r="S438" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T438" t="inlineStr">
         <is>
@@ -48715,22 +48710,22 @@
       <c r="AT438" t="inlineStr"/>
       <c r="AW438" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX438" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>123866711</v>
+        <v>123869983</v>
       </c>
       <c r="B439" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
@@ -48739,43 +48734,43 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E439" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I439" t="inlineStr"/>
       <c r="M439" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P439" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q439" t="n">
-        <v>459001</v>
+        <v>459708</v>
       </c>
       <c r="R439" t="n">
-        <v>6808842</v>
+        <v>6808890</v>
       </c>
       <c r="S439" t="n">
         <v>10</v>
@@ -48822,22 +48817,22 @@
       <c r="AT439" t="inlineStr"/>
       <c r="AW439" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX439" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>123867031</v>
+        <v>123866711</v>
       </c>
       <c r="B440" t="n">
-        <v>78525</v>
+        <v>56700</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
@@ -48846,41 +48841,46 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E440" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I440" t="inlineStr"/>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P440" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q440" t="n">
-        <v>458879</v>
+        <v>459001</v>
       </c>
       <c r="R440" t="n">
-        <v>6808768</v>
+        <v>6808842</v>
       </c>
       <c r="S440" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T440" t="inlineStr">
         <is>
@@ -48936,10 +48936,10 @@
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>123863610</v>
+        <v>123865731</v>
       </c>
       <c r="B441" t="n">
-        <v>57861</v>
+        <v>57507</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
@@ -48948,20 +48948,20 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E441" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -48972,19 +48972,19 @@
       <c r="I441" t="inlineStr"/>
       <c r="M441" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P441" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q441" t="n">
-        <v>459773</v>
+        <v>459340</v>
       </c>
       <c r="R441" t="n">
-        <v>6808678</v>
+        <v>6808753</v>
       </c>
       <c r="S441" t="n">
         <v>10</v>
@@ -49043,10 +49043,10 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>123868528</v>
+        <v>123863610</v>
       </c>
       <c r="B442" t="n">
-        <v>79377</v>
+        <v>57861</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
@@ -49055,38 +49055,43 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E442" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I442" t="inlineStr"/>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P442" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q442" t="n">
-        <v>459168</v>
+        <v>459773</v>
       </c>
       <c r="R442" t="n">
-        <v>6808988</v>
+        <v>6808678</v>
       </c>
       <c r="S442" t="n">
         <v>10</v>
@@ -49133,22 +49138,22 @@
       <c r="AT442" t="inlineStr"/>
       <c r="AW442" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX442" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>123865731</v>
+        <v>123868528</v>
       </c>
       <c r="B443" t="n">
-        <v>57507</v>
+        <v>79377</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
@@ -49161,39 +49166,34 @@
         </is>
       </c>
       <c r="E443" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I443" t="inlineStr"/>
-      <c r="M443" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P443" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q443" t="n">
-        <v>459340</v>
+        <v>459168</v>
       </c>
       <c r="R443" t="n">
-        <v>6808753</v>
+        <v>6808988</v>
       </c>
       <c r="S443" t="n">
         <v>10</v>
@@ -49240,22 +49240,22 @@
       <c r="AT443" t="inlineStr"/>
       <c r="AW443" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX443" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>123868052</v>
+        <v>123868217</v>
       </c>
       <c r="B444" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
@@ -49268,21 +49268,21 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I444" t="inlineStr"/>
@@ -49292,13 +49292,13 @@
         </is>
       </c>
       <c r="Q444" t="n">
-        <v>458921</v>
+        <v>459029</v>
       </c>
       <c r="R444" t="n">
-        <v>6808961</v>
+        <v>6808959</v>
       </c>
       <c r="S444" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T444" t="inlineStr">
         <is>
@@ -49354,10 +49354,10 @@
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>123866561</v>
+        <v>123866559</v>
       </c>
       <c r="B445" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
@@ -49370,37 +49370,37 @@
         </is>
       </c>
       <c r="E445" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I445" t="inlineStr"/>
       <c r="P445" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q445" t="n">
-        <v>459159</v>
+        <v>459128</v>
       </c>
       <c r="R445" t="n">
-        <v>6808628</v>
+        <v>6808639</v>
       </c>
       <c r="S445" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T445" t="inlineStr">
         <is>
@@ -49430,11 +49430,6 @@
       <c r="AA445" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC445" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD445" t="b">
@@ -49449,22 +49444,22 @@
       <c r="AT445" t="inlineStr"/>
       <c r="AW445" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX445" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>123865783</v>
+        <v>123863675</v>
       </c>
       <c r="B446" t="n">
-        <v>56700</v>
+        <v>77716</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
@@ -49473,25 +49468,25 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E446" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I446" t="inlineStr"/>
@@ -49501,10 +49496,10 @@
         </is>
       </c>
       <c r="Q446" t="n">
-        <v>459326</v>
+        <v>459743</v>
       </c>
       <c r="R446" t="n">
-        <v>6808793</v>
+        <v>6808691</v>
       </c>
       <c r="S446" t="n">
         <v>20</v>
@@ -49537,11 +49532,6 @@
       <c r="AA446" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC446" t="inlineStr">
-        <is>
-          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD446" t="b">
@@ -49568,10 +49558,10 @@
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>123864050</v>
+        <v>123863840</v>
       </c>
       <c r="B447" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
@@ -49580,43 +49570,38 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E447" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I447" t="inlineStr"/>
-      <c r="M447" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P447" t="inlineStr">
         <is>
           <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q447" t="n">
-        <v>459647</v>
+        <v>459689</v>
       </c>
       <c r="R447" t="n">
-        <v>6808642</v>
+        <v>6808558</v>
       </c>
       <c r="S447" t="n">
         <v>20</v>
@@ -49659,11 +49644,6 @@
       </c>
       <c r="AG447" t="b">
         <v>0</v>
-      </c>
-      <c r="AH447" t="inlineStr">
-        <is>
-          <t>Öppen fastmark - med eller utan enstaka träd</t>
-        </is>
       </c>
       <c r="AT447" t="inlineStr"/>
       <c r="AW447" t="inlineStr">
@@ -49680,10 +49660,10 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>123868217</v>
+        <v>123865783</v>
       </c>
       <c r="B448" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C448" t="inlineStr">
         <is>
@@ -49692,25 +49672,25 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E448" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I448" t="inlineStr"/>
@@ -49720,13 +49700,13 @@
         </is>
       </c>
       <c r="Q448" t="n">
-        <v>459029</v>
+        <v>459326</v>
       </c>
       <c r="R448" t="n">
-        <v>6808959</v>
+        <v>6808793</v>
       </c>
       <c r="S448" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T448" t="inlineStr">
         <is>
@@ -49756,6 +49736,11 @@
       <c r="AA448" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC448" t="inlineStr">
+        <is>
+          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD448" t="b">
@@ -49782,10 +49767,10 @@
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>123866559</v>
+        <v>123864050</v>
       </c>
       <c r="B449" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
@@ -49794,38 +49779,43 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E449" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I449" t="inlineStr"/>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P449" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q449" t="n">
-        <v>459128</v>
+        <v>459647</v>
       </c>
       <c r="R449" t="n">
-        <v>6808639</v>
+        <v>6808642</v>
       </c>
       <c r="S449" t="n">
         <v>20</v>
@@ -49869,25 +49859,30 @@
       <c r="AG449" t="b">
         <v>0</v>
       </c>
+      <c r="AH449" t="inlineStr">
+        <is>
+          <t>Öppen fastmark - med eller utan enstaka träd</t>
+        </is>
+      </c>
       <c r="AT449" t="inlineStr"/>
       <c r="AW449" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX449" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>123863675</v>
+        <v>123868052</v>
       </c>
       <c r="B450" t="n">
-        <v>77716</v>
+        <v>79377</v>
       </c>
       <c r="C450" t="inlineStr">
         <is>
@@ -49900,21 +49895,21 @@
         </is>
       </c>
       <c r="E450" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I450" t="inlineStr"/>
@@ -49924,10 +49919,10 @@
         </is>
       </c>
       <c r="Q450" t="n">
-        <v>459743</v>
+        <v>458921</v>
       </c>
       <c r="R450" t="n">
-        <v>6808691</v>
+        <v>6808961</v>
       </c>
       <c r="S450" t="n">
         <v>20</v>
@@ -49986,10 +49981,10 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>123863840</v>
+        <v>123866561</v>
       </c>
       <c r="B451" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
@@ -50002,37 +49997,37 @@
         </is>
       </c>
       <c r="E451" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I451" t="inlineStr"/>
       <c r="P451" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q451" t="n">
-        <v>459689</v>
+        <v>459159</v>
       </c>
       <c r="R451" t="n">
-        <v>6808558</v>
+        <v>6808628</v>
       </c>
       <c r="S451" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T451" t="inlineStr">
         <is>
@@ -50062,6 +50057,11 @@
       <c r="AA451" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC451" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD451" t="b">
@@ -50076,12 +50076,12 @@
       <c r="AT451" t="inlineStr"/>
       <c r="AW451" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX451" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY451" t="inlineStr"/>
@@ -50302,10 +50302,10 @@
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>123864080</v>
+        <v>123866153</v>
       </c>
       <c r="B454" t="n">
-        <v>77716</v>
+        <v>56700</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
@@ -50314,41 +50314,51 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E454" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I454" t="inlineStr"/>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P454" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q454" t="n">
-        <v>459555</v>
+        <v>459211</v>
       </c>
       <c r="R454" t="n">
-        <v>6808660</v>
+        <v>6808724</v>
       </c>
       <c r="S454" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T454" t="inlineStr">
         <is>
@@ -50392,22 +50402,22 @@
       <c r="AT454" t="inlineStr"/>
       <c r="AW454" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX454" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>123866153</v>
+        <v>123864080</v>
       </c>
       <c r="B455" t="n">
-        <v>56700</v>
+        <v>77716</v>
       </c>
       <c r="C455" t="inlineStr">
         <is>
@@ -50416,51 +50426,41 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E455" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I455" t="inlineStr"/>
-      <c r="L455" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M455" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P455" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q455" t="n">
-        <v>459211</v>
+        <v>459555</v>
       </c>
       <c r="R455" t="n">
-        <v>6808724</v>
+        <v>6808660</v>
       </c>
       <c r="S455" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T455" t="inlineStr">
         <is>
@@ -50504,12 +50504,12 @@
       <c r="AT455" t="inlineStr"/>
       <c r="AW455" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX455" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY455" t="inlineStr"/>
@@ -52447,7 +52447,7 @@
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>123864359</v>
+        <v>123866920</v>
       </c>
       <c r="B474" t="n">
         <v>78788</v>
@@ -52483,17 +52483,17 @@
       <c r="I474" t="inlineStr"/>
       <c r="P474" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q474" t="n">
-        <v>459500</v>
+        <v>458966</v>
       </c>
       <c r="R474" t="n">
-        <v>6808604</v>
+        <v>6808788</v>
       </c>
       <c r="S474" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T474" t="inlineStr">
         <is>
@@ -52523,11 +52523,6 @@
       <c r="AA474" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC474" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter.  Miljöbild på bland annat torraka/silvertall.</t>
         </is>
       </c>
       <c r="AD474" t="b">
@@ -52542,19 +52537,19 @@
       <c r="AT474" t="inlineStr"/>
       <c r="AW474" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX474" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>123866920</v>
+        <v>123864359</v>
       </c>
       <c r="B475" t="n">
         <v>78788</v>
@@ -52590,17 +52585,17 @@
       <c r="I475" t="inlineStr"/>
       <c r="P475" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q475" t="n">
-        <v>458966</v>
+        <v>459500</v>
       </c>
       <c r="R475" t="n">
-        <v>6808788</v>
+        <v>6808604</v>
       </c>
       <c r="S475" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T475" t="inlineStr">
         <is>
@@ -52630,6 +52625,11 @@
       <c r="AA475" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC475" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter.  Miljöbild på bland annat torraka/silvertall.</t>
         </is>
       </c>
       <c r="AD475" t="b">
@@ -52644,12 +52644,12 @@
       <c r="AT475" t="inlineStr"/>
       <c r="AW475" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX475" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY475" t="inlineStr"/>
@@ -53701,10 +53701,10 @@
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>123864015</v>
+        <v>123864326</v>
       </c>
       <c r="B486" t="n">
-        <v>79377</v>
+        <v>78433</v>
       </c>
       <c r="C486" t="inlineStr">
         <is>
@@ -53717,21 +53717,21 @@
         </is>
       </c>
       <c r="E486" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I486" t="inlineStr"/>
@@ -53741,13 +53741,13 @@
         </is>
       </c>
       <c r="Q486" t="n">
-        <v>459594</v>
+        <v>459507</v>
       </c>
       <c r="R486" t="n">
-        <v>6808664</v>
+        <v>6808603</v>
       </c>
       <c r="S486" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T486" t="inlineStr">
         <is>
@@ -53803,10 +53803,10 @@
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>123864326</v>
+        <v>123866750</v>
       </c>
       <c r="B487" t="n">
-        <v>78433</v>
+        <v>78788</v>
       </c>
       <c r="C487" t="inlineStr">
         <is>
@@ -53819,37 +53819,37 @@
         </is>
       </c>
       <c r="E487" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I487" t="inlineStr"/>
       <c r="P487" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q487" t="n">
-        <v>459507</v>
+        <v>459080</v>
       </c>
       <c r="R487" t="n">
-        <v>6808603</v>
+        <v>6808643</v>
       </c>
       <c r="S487" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T487" t="inlineStr">
         <is>
@@ -53879,6 +53879,11 @@
       <c r="AA487" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC487" t="inlineStr">
+        <is>
+          <t>I en radie av ca 50 meter, garnlav. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD487" t="b">
@@ -53893,22 +53898,22 @@
       <c r="AT487" t="inlineStr"/>
       <c r="AW487" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX487" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>123866750</v>
+        <v>123869316</v>
       </c>
       <c r="B488" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C488" t="inlineStr">
         <is>
@@ -53917,41 +53922,46 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E488" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I488" t="inlineStr"/>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P488" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q488" t="n">
-        <v>459080</v>
+        <v>459292</v>
       </c>
       <c r="R488" t="n">
-        <v>6808643</v>
+        <v>6808848</v>
       </c>
       <c r="S488" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T488" t="inlineStr">
         <is>
@@ -53981,11 +53991,6 @@
       <c r="AA488" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC488" t="inlineStr">
-        <is>
-          <t>I en radie av ca 50 meter, garnlav. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD488" t="b">
@@ -54000,22 +54005,22 @@
       <c r="AT488" t="inlineStr"/>
       <c r="AW488" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX488" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>123869316</v>
+        <v>123864015</v>
       </c>
       <c r="B489" t="n">
-        <v>56700</v>
+        <v>79377</v>
       </c>
       <c r="C489" t="inlineStr">
         <is>
@@ -54024,46 +54029,41 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E489" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I489" t="inlineStr"/>
-      <c r="M489" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P489" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q489" t="n">
-        <v>459292</v>
+        <v>459594</v>
       </c>
       <c r="R489" t="n">
-        <v>6808848</v>
+        <v>6808664</v>
       </c>
       <c r="S489" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T489" t="inlineStr">
         <is>
@@ -54107,12 +54107,12 @@
       <c r="AT489" t="inlineStr"/>
       <c r="AW489" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX489" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY489" t="inlineStr"/>
@@ -73264,10 +73264,10 @@
     </row>
     <row r="676">
       <c r="A676" t="n">
-        <v>123920448</v>
+        <v>123920315</v>
       </c>
       <c r="B676" t="n">
-        <v>56700</v>
+        <v>79406</v>
       </c>
       <c r="C676" t="inlineStr">
         <is>
@@ -73276,43 +73276,38 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E676" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I676" t="inlineStr"/>
-      <c r="M676" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P676" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q676" t="n">
-        <v>458790</v>
+        <v>459450</v>
       </c>
       <c r="R676" t="n">
-        <v>6808708</v>
+        <v>6808625</v>
       </c>
       <c r="S676" t="n">
         <v>10</v>
@@ -73371,10 +73366,10 @@
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>123920402</v>
+        <v>123920795</v>
       </c>
       <c r="B677" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C677" t="inlineStr">
         <is>
@@ -73387,21 +73382,21 @@
         </is>
       </c>
       <c r="E677" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I677" t="inlineStr"/>
@@ -73411,10 +73406,10 @@
         </is>
       </c>
       <c r="Q677" t="n">
-        <v>459222</v>
+        <v>458927</v>
       </c>
       <c r="R677" t="n">
-        <v>6807998</v>
+        <v>6808282</v>
       </c>
       <c r="S677" t="n">
         <v>10</v>
@@ -73466,17 +73461,17 @@
       </c>
       <c r="AX677" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY677" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" t="n">
-        <v>123920318</v>
+        <v>123920396</v>
       </c>
       <c r="B678" t="n">
-        <v>79406</v>
+        <v>79377</v>
       </c>
       <c r="C678" t="inlineStr">
         <is>
@@ -73489,21 +73484,21 @@
         </is>
       </c>
       <c r="E678" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I678" t="inlineStr"/>
@@ -73513,10 +73508,10 @@
         </is>
       </c>
       <c r="Q678" t="n">
-        <v>459568</v>
+        <v>459516</v>
       </c>
       <c r="R678" t="n">
-        <v>6808641</v>
+        <v>6808647</v>
       </c>
       <c r="S678" t="n">
         <v>10</v>
@@ -73575,7 +73570,7 @@
     </row>
     <row r="679">
       <c r="A679" t="n">
-        <v>123920807</v>
+        <v>123920799</v>
       </c>
       <c r="B679" t="n">
         <v>78788</v>
@@ -73615,10 +73610,10 @@
         </is>
       </c>
       <c r="Q679" t="n">
-        <v>459115</v>
+        <v>459007</v>
       </c>
       <c r="R679" t="n">
-        <v>6808339</v>
+        <v>6808305</v>
       </c>
       <c r="S679" t="n">
         <v>10</v>
@@ -73677,10 +73672,10 @@
     </row>
     <row r="680">
       <c r="A680" t="n">
-        <v>123920691</v>
+        <v>123920448</v>
       </c>
       <c r="B680" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C680" t="inlineStr">
         <is>
@@ -73689,38 +73684,43 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E680" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I680" t="inlineStr"/>
+      <c r="M680" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P680" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q680" t="n">
-        <v>459688</v>
+        <v>458790</v>
       </c>
       <c r="R680" t="n">
-        <v>6808555</v>
+        <v>6808708</v>
       </c>
       <c r="S680" t="n">
         <v>10</v>
@@ -73779,10 +73779,10 @@
     </row>
     <row r="681">
       <c r="A681" t="n">
-        <v>123920695</v>
+        <v>123920402</v>
       </c>
       <c r="B681" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C681" t="inlineStr">
         <is>
@@ -73795,21 +73795,21 @@
         </is>
       </c>
       <c r="E681" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I681" t="inlineStr"/>
@@ -73819,10 +73819,10 @@
         </is>
       </c>
       <c r="Q681" t="n">
-        <v>459733</v>
+        <v>459222</v>
       </c>
       <c r="R681" t="n">
-        <v>6808671</v>
+        <v>6807998</v>
       </c>
       <c r="S681" t="n">
         <v>10</v>
@@ -73849,12 +73849,12 @@
       </c>
       <c r="Y681" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA681" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD681" t="b">
@@ -73874,17 +73874,17 @@
       </c>
       <c r="AX681" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY681" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" t="n">
-        <v>123920439</v>
+        <v>123920318</v>
       </c>
       <c r="B682" t="n">
-        <v>56700</v>
+        <v>79406</v>
       </c>
       <c r="C682" t="inlineStr">
         <is>
@@ -73893,43 +73893,38 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E682" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I682" t="inlineStr"/>
-      <c r="M682" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P682" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q682" t="n">
-        <v>459700</v>
+        <v>459568</v>
       </c>
       <c r="R682" t="n">
-        <v>6808234</v>
+        <v>6808641</v>
       </c>
       <c r="S682" t="n">
         <v>10</v>
@@ -73956,12 +73951,12 @@
       </c>
       <c r="Y682" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA682" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD682" t="b">
@@ -73981,17 +73976,17 @@
       </c>
       <c r="AX682" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY682" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" t="n">
-        <v>123920316</v>
+        <v>123920807</v>
       </c>
       <c r="B683" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C683" t="inlineStr">
         <is>
@@ -74004,21 +73999,21 @@
         </is>
       </c>
       <c r="E683" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I683" t="inlineStr"/>
@@ -74028,10 +74023,10 @@
         </is>
       </c>
       <c r="Q683" t="n">
-        <v>459455</v>
+        <v>459115</v>
       </c>
       <c r="R683" t="n">
-        <v>6808627</v>
+        <v>6808339</v>
       </c>
       <c r="S683" t="n">
         <v>10</v>
@@ -74058,12 +74053,12 @@
       </c>
       <c r="Y683" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA683" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD683" t="b">
@@ -74083,17 +74078,17 @@
       </c>
       <c r="AX683" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY683" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" t="n">
-        <v>123920929</v>
+        <v>123920691</v>
       </c>
       <c r="B684" t="n">
-        <v>78433</v>
+        <v>78788</v>
       </c>
       <c r="C684" t="inlineStr">
         <is>
@@ -74106,21 +74101,21 @@
         </is>
       </c>
       <c r="E684" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I684" t="inlineStr"/>
@@ -74130,10 +74125,10 @@
         </is>
       </c>
       <c r="Q684" t="n">
-        <v>459707</v>
+        <v>459688</v>
       </c>
       <c r="R684" t="n">
-        <v>6808606</v>
+        <v>6808555</v>
       </c>
       <c r="S684" t="n">
         <v>10</v>
@@ -74192,7 +74187,7 @@
     </row>
     <row r="685">
       <c r="A685" t="n">
-        <v>123920810</v>
+        <v>123920695</v>
       </c>
       <c r="B685" t="n">
         <v>78788</v>
@@ -74232,10 +74227,10 @@
         </is>
       </c>
       <c r="Q685" t="n">
-        <v>459205</v>
+        <v>459733</v>
       </c>
       <c r="R685" t="n">
-        <v>6808378</v>
+        <v>6808671</v>
       </c>
       <c r="S685" t="n">
         <v>10</v>
@@ -74262,12 +74257,12 @@
       </c>
       <c r="Y685" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA685" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD685" t="b">
@@ -74287,17 +74282,17 @@
       </c>
       <c r="AX685" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY685" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" t="n">
-        <v>123920826</v>
+        <v>123920439</v>
       </c>
       <c r="B686" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C686" t="inlineStr">
         <is>
@@ -74306,38 +74301,43 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E686" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I686" t="inlineStr"/>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P686" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q686" t="n">
-        <v>459573</v>
+        <v>459700</v>
       </c>
       <c r="R686" t="n">
-        <v>6808265</v>
+        <v>6808234</v>
       </c>
       <c r="S686" t="n">
         <v>10</v>
@@ -74389,17 +74389,17 @@
       </c>
       <c r="AX686" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY686" t="inlineStr"/>
     </row>
     <row r="687">
       <c r="A687" t="n">
-        <v>123920735</v>
+        <v>123920316</v>
       </c>
       <c r="B687" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C687" t="inlineStr">
         <is>
@@ -74412,21 +74412,21 @@
         </is>
       </c>
       <c r="E687" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I687" t="inlineStr"/>
@@ -74436,10 +74436,10 @@
         </is>
       </c>
       <c r="Q687" t="n">
-        <v>459602</v>
+        <v>459455</v>
       </c>
       <c r="R687" t="n">
-        <v>6807938</v>
+        <v>6808627</v>
       </c>
       <c r="S687" t="n">
         <v>10</v>
@@ -74466,12 +74466,12 @@
       </c>
       <c r="Y687" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA687" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD687" t="b">
@@ -74491,17 +74491,17 @@
       </c>
       <c r="AX687" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY687" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" t="n">
-        <v>123920315</v>
+        <v>123920929</v>
       </c>
       <c r="B688" t="n">
-        <v>79406</v>
+        <v>78433</v>
       </c>
       <c r="C688" t="inlineStr">
         <is>
@@ -74514,21 +74514,21 @@
         </is>
       </c>
       <c r="E688" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I688" t="inlineStr"/>
@@ -74538,10 +74538,10 @@
         </is>
       </c>
       <c r="Q688" t="n">
-        <v>459450</v>
+        <v>459707</v>
       </c>
       <c r="R688" t="n">
-        <v>6808625</v>
+        <v>6808606</v>
       </c>
       <c r="S688" t="n">
         <v>10</v>
@@ -74600,7 +74600,7 @@
     </row>
     <row r="689">
       <c r="A689" t="n">
-        <v>123920795</v>
+        <v>123920810</v>
       </c>
       <c r="B689" t="n">
         <v>78788</v>
@@ -74640,10 +74640,10 @@
         </is>
       </c>
       <c r="Q689" t="n">
-        <v>458927</v>
+        <v>459205</v>
       </c>
       <c r="R689" t="n">
-        <v>6808282</v>
+        <v>6808378</v>
       </c>
       <c r="S689" t="n">
         <v>10</v>
@@ -74702,10 +74702,10 @@
     </row>
     <row r="690">
       <c r="A690" t="n">
-        <v>123920396</v>
+        <v>123920826</v>
       </c>
       <c r="B690" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C690" t="inlineStr">
         <is>
@@ -74718,21 +74718,21 @@
         </is>
       </c>
       <c r="E690" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I690" t="inlineStr"/>
@@ -74742,10 +74742,10 @@
         </is>
       </c>
       <c r="Q690" t="n">
-        <v>459516</v>
+        <v>459573</v>
       </c>
       <c r="R690" t="n">
-        <v>6808647</v>
+        <v>6808265</v>
       </c>
       <c r="S690" t="n">
         <v>10</v>
@@ -74772,12 +74772,12 @@
       </c>
       <c r="Y690" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA690" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD690" t="b">
@@ -74797,14 +74797,14 @@
       </c>
       <c r="AX690" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY690" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" t="n">
-        <v>123920799</v>
+        <v>123920735</v>
       </c>
       <c r="B691" t="n">
         <v>78788</v>
@@ -74844,10 +74844,10 @@
         </is>
       </c>
       <c r="Q691" t="n">
-        <v>459007</v>
+        <v>459602</v>
       </c>
       <c r="R691" t="n">
-        <v>6808305</v>
+        <v>6807938</v>
       </c>
       <c r="S691" t="n">
         <v>10</v>
@@ -77573,10 +77573,10 @@
     </row>
     <row r="718">
       <c r="A718" t="n">
-        <v>123920662</v>
+        <v>123920380</v>
       </c>
       <c r="B718" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C718" t="inlineStr">
         <is>
@@ -77589,21 +77589,21 @@
         </is>
       </c>
       <c r="E718" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I718" t="inlineStr"/>
@@ -77613,10 +77613,10 @@
         </is>
       </c>
       <c r="Q718" t="n">
-        <v>458749</v>
+        <v>459217</v>
       </c>
       <c r="R718" t="n">
-        <v>6808795</v>
+        <v>6808383</v>
       </c>
       <c r="S718" t="n">
         <v>10</v>
@@ -77643,12 +77643,12 @@
       </c>
       <c r="Y718" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA718" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD718" t="b">
@@ -77668,17 +77668,17 @@
       </c>
       <c r="AX718" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY718" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" t="n">
-        <v>123920476</v>
+        <v>123920573</v>
       </c>
       <c r="B719" t="n">
-        <v>79898</v>
+        <v>80741</v>
       </c>
       <c r="C719" t="inlineStr">
         <is>
@@ -77687,25 +77687,25 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E719" t="n">
-        <v>6462</v>
+        <v>1049</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I719" t="inlineStr"/>
@@ -77715,10 +77715,10 @@
         </is>
       </c>
       <c r="Q719" t="n">
-        <v>459568</v>
+        <v>458988</v>
       </c>
       <c r="R719" t="n">
-        <v>6808142</v>
+        <v>6808278</v>
       </c>
       <c r="S719" t="n">
         <v>10</v>
@@ -77777,10 +77777,10 @@
     </row>
     <row r="720">
       <c r="A720" t="n">
-        <v>123920727</v>
+        <v>123920452</v>
       </c>
       <c r="B720" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C720" t="inlineStr">
         <is>
@@ -77789,38 +77789,43 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E720" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I720" t="inlineStr"/>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P720" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q720" t="n">
-        <v>459542</v>
+        <v>459281</v>
       </c>
       <c r="R720" t="n">
-        <v>6808123</v>
+        <v>6808708</v>
       </c>
       <c r="S720" t="n">
         <v>10</v>
@@ -77847,12 +77852,12 @@
       </c>
       <c r="Y720" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA720" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD720" t="b">
@@ -77872,14 +77877,14 @@
       </c>
       <c r="AX720" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY720" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" t="n">
-        <v>123920730</v>
+        <v>123920813</v>
       </c>
       <c r="B721" t="n">
         <v>78788</v>
@@ -77919,10 +77924,10 @@
         </is>
       </c>
       <c r="Q721" t="n">
-        <v>459590</v>
+        <v>459237</v>
       </c>
       <c r="R721" t="n">
-        <v>6808062</v>
+        <v>6808364</v>
       </c>
       <c r="S721" t="n">
         <v>10</v>
@@ -77981,10 +77986,10 @@
     </row>
     <row r="722">
       <c r="A722" t="n">
-        <v>123920457</v>
+        <v>123920794</v>
       </c>
       <c r="B722" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C722" t="inlineStr">
         <is>
@@ -77993,43 +77998,38 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E722" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I722" t="inlineStr"/>
-      <c r="M722" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P722" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q722" t="n">
-        <v>458767</v>
+        <v>458919</v>
       </c>
       <c r="R722" t="n">
-        <v>6808746</v>
+        <v>6808281</v>
       </c>
       <c r="S722" t="n">
         <v>10</v>
@@ -78056,12 +78056,12 @@
       </c>
       <c r="Y722" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA722" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD722" t="b">
@@ -78081,17 +78081,17 @@
       </c>
       <c r="AX722" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY722" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" t="n">
-        <v>123920336</v>
+        <v>123920463</v>
       </c>
       <c r="B723" t="n">
-        <v>79406</v>
+        <v>56700</v>
       </c>
       <c r="C723" t="inlineStr">
         <is>
@@ -78100,38 +78100,43 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E723" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I723" t="inlineStr"/>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P723" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q723" t="n">
-        <v>459520</v>
+        <v>459717</v>
       </c>
       <c r="R723" t="n">
-        <v>6808387</v>
+        <v>6808604</v>
       </c>
       <c r="S723" t="n">
         <v>10</v>
@@ -78158,12 +78163,12 @@
       </c>
       <c r="Y723" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA723" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD723" t="b">
@@ -78183,14 +78188,14 @@
       </c>
       <c r="AX723" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY723" t="inlineStr"/>
     </row>
     <row r="724">
       <c r="A724" t="n">
-        <v>123920668</v>
+        <v>123920812</v>
       </c>
       <c r="B724" t="n">
         <v>78788</v>
@@ -78230,10 +78235,10 @@
         </is>
       </c>
       <c r="Q724" t="n">
-        <v>458876</v>
+        <v>459239</v>
       </c>
       <c r="R724" t="n">
-        <v>6808749</v>
+        <v>6808359</v>
       </c>
       <c r="S724" t="n">
         <v>10</v>
@@ -78260,12 +78265,12 @@
       </c>
       <c r="Y724" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA724" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD724" t="b">
@@ -78285,17 +78290,17 @@
       </c>
       <c r="AX724" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY724" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" t="n">
-        <v>123920380</v>
+        <v>123920662</v>
       </c>
       <c r="B725" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C725" t="inlineStr">
         <is>
@@ -78308,21 +78313,21 @@
         </is>
       </c>
       <c r="E725" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I725" t="inlineStr"/>
@@ -78332,10 +78337,10 @@
         </is>
       </c>
       <c r="Q725" t="n">
-        <v>459217</v>
+        <v>458749</v>
       </c>
       <c r="R725" t="n">
-        <v>6808383</v>
+        <v>6808795</v>
       </c>
       <c r="S725" t="n">
         <v>10</v>
@@ -78362,12 +78367,12 @@
       </c>
       <c r="Y725" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA725" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD725" t="b">
@@ -78387,17 +78392,17 @@
       </c>
       <c r="AX725" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY725" t="inlineStr"/>
     </row>
     <row r="726">
       <c r="A726" t="n">
-        <v>123920573</v>
+        <v>123920476</v>
       </c>
       <c r="B726" t="n">
-        <v>80741</v>
+        <v>79898</v>
       </c>
       <c r="C726" t="inlineStr">
         <is>
@@ -78406,25 +78411,25 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E726" t="n">
-        <v>1049</v>
+        <v>6462</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I726" t="inlineStr"/>
@@ -78434,10 +78439,10 @@
         </is>
       </c>
       <c r="Q726" t="n">
-        <v>458988</v>
+        <v>459568</v>
       </c>
       <c r="R726" t="n">
-        <v>6808278</v>
+        <v>6808142</v>
       </c>
       <c r="S726" t="n">
         <v>10</v>
@@ -78496,10 +78501,10 @@
     </row>
     <row r="727">
       <c r="A727" t="n">
-        <v>123920452</v>
+        <v>123920727</v>
       </c>
       <c r="B727" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C727" t="inlineStr">
         <is>
@@ -78508,43 +78513,38 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E727" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I727" t="inlineStr"/>
-      <c r="M727" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P727" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q727" t="n">
-        <v>459281</v>
+        <v>459542</v>
       </c>
       <c r="R727" t="n">
-        <v>6808708</v>
+        <v>6808123</v>
       </c>
       <c r="S727" t="n">
         <v>10</v>
@@ -78571,12 +78571,12 @@
       </c>
       <c r="Y727" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA727" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD727" t="b">
@@ -78596,14 +78596,14 @@
       </c>
       <c r="AX727" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY727" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" t="n">
-        <v>123920813</v>
+        <v>123920730</v>
       </c>
       <c r="B728" t="n">
         <v>78788</v>
@@ -78643,10 +78643,10 @@
         </is>
       </c>
       <c r="Q728" t="n">
-        <v>459237</v>
+        <v>459590</v>
       </c>
       <c r="R728" t="n">
-        <v>6808364</v>
+        <v>6808062</v>
       </c>
       <c r="S728" t="n">
         <v>10</v>
@@ -78705,10 +78705,10 @@
     </row>
     <row r="729">
       <c r="A729" t="n">
-        <v>123920794</v>
+        <v>123920457</v>
       </c>
       <c r="B729" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C729" t="inlineStr">
         <is>
@@ -78717,38 +78717,43 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E729" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I729" t="inlineStr"/>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P729" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q729" t="n">
-        <v>458919</v>
+        <v>458767</v>
       </c>
       <c r="R729" t="n">
-        <v>6808281</v>
+        <v>6808746</v>
       </c>
       <c r="S729" t="n">
         <v>10</v>
@@ -78775,12 +78780,12 @@
       </c>
       <c r="Y729" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA729" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD729" t="b">
@@ -78800,17 +78805,17 @@
       </c>
       <c r="AX729" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY729" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" t="n">
-        <v>123920463</v>
+        <v>123920336</v>
       </c>
       <c r="B730" t="n">
-        <v>56700</v>
+        <v>79406</v>
       </c>
       <c r="C730" t="inlineStr">
         <is>
@@ -78819,43 +78824,38 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E730" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I730" t="inlineStr"/>
-      <c r="M730" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P730" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q730" t="n">
-        <v>459717</v>
+        <v>459520</v>
       </c>
       <c r="R730" t="n">
-        <v>6808604</v>
+        <v>6808387</v>
       </c>
       <c r="S730" t="n">
         <v>10</v>
@@ -78882,12 +78882,12 @@
       </c>
       <c r="Y730" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA730" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD730" t="b">
@@ -78907,14 +78907,14 @@
       </c>
       <c r="AX730" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY730" t="inlineStr"/>
     </row>
     <row r="731">
       <c r="A731" t="n">
-        <v>123920812</v>
+        <v>123920668</v>
       </c>
       <c r="B731" t="n">
         <v>78788</v>
@@ -78954,10 +78954,10 @@
         </is>
       </c>
       <c r="Q731" t="n">
-        <v>459239</v>
+        <v>458876</v>
       </c>
       <c r="R731" t="n">
-        <v>6808359</v>
+        <v>6808749</v>
       </c>
       <c r="S731" t="n">
         <v>10</v>
@@ -78984,12 +78984,12 @@
       </c>
       <c r="Y731" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA731" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD731" t="b">
@@ -79009,7 +79009,7 @@
       </c>
       <c r="AX731" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY731" t="inlineStr"/>

--- a/artfynd/A 13728-2025 artfynd.xlsx
+++ b/artfynd/A 13728-2025 artfynd.xlsx
@@ -1917,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123549559</v>
+        <v>123549501</v>
       </c>
       <c r="B13" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,49 +1929,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459695</v>
+        <v>459367</v>
       </c>
       <c r="R13" t="n">
-        <v>6808940</v>
+        <v>6808792</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2000,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2010,12 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Under betestall</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,19 +2017,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123549501</v>
+        <v>123549549</v>
       </c>
       <c r="B14" t="n">
         <v>78788</v>
@@ -2082,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459367</v>
+        <v>459415</v>
       </c>
       <c r="R14" t="n">
-        <v>6808792</v>
+        <v>6808812</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2117,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2127,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,7 +2141,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123549549</v>
+        <v>123549709</v>
       </c>
       <c r="B15" t="n">
         <v>78788</v>
@@ -2194,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459415</v>
+        <v>459458</v>
       </c>
       <c r="R15" t="n">
-        <v>6808812</v>
+        <v>6808866</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2229,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2239,7 +2226,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På tallstammar flera</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2266,7 +2258,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123549709</v>
+        <v>123548510</v>
       </c>
       <c r="B16" t="n">
         <v>78788</v>
@@ -2302,17 +2294,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459458</v>
+        <v>459172</v>
       </c>
       <c r="R16" t="n">
-        <v>6808866</v>
+        <v>6808718</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2341,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2351,12 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:33</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På tallstammar flera</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,22 +2358,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123548510</v>
+        <v>123549559</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2395,41 +2382,49 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459172</v>
+        <v>459695</v>
       </c>
       <c r="R17" t="n">
-        <v>6808718</v>
+        <v>6808940</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2458,7 +2453,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2468,7 +2463,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Under betestall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2483,22 +2483,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123549156</v>
+        <v>123549418</v>
       </c>
       <c r="B18" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2507,41 +2507,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459240</v>
+        <v>459318</v>
       </c>
       <c r="R18" t="n">
-        <v>6808794</v>
+        <v>6808809</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2570,7 +2575,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2580,7 +2585,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Under betestall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2595,19 +2605,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123543987</v>
+        <v>123549156</v>
       </c>
       <c r="B19" t="n">
         <v>78788</v>
@@ -2647,10 +2657,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459521</v>
+        <v>459240</v>
       </c>
       <c r="R19" t="n">
-        <v>6808918</v>
+        <v>6808794</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2682,7 +2692,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2692,7 +2702,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2719,7 +2729,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123543499</v>
+        <v>123543987</v>
       </c>
       <c r="B20" t="n">
         <v>78788</v>
@@ -2759,13 +2769,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459677</v>
+        <v>459521</v>
       </c>
       <c r="R20" t="n">
-        <v>6808949</v>
+        <v>6808918</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2794,7 +2804,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2804,12 +2814,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På Gran blandat med skägglav</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2824,19 +2829,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123543842</v>
+        <v>123543499</v>
       </c>
       <c r="B21" t="n">
         <v>78788</v>
@@ -2876,10 +2881,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459608</v>
+        <v>459677</v>
       </c>
       <c r="R21" t="n">
-        <v>6809012</v>
+        <v>6808949</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2911,7 +2916,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2921,12 +2926,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På Gran</t>
+          <t>På Gran blandat med skägglav</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2953,10 +2958,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123548636</v>
+        <v>123543842</v>
       </c>
       <c r="B22" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2969,37 +2974,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459184</v>
+        <v>459608</v>
       </c>
       <c r="R22" t="n">
-        <v>6808784</v>
+        <v>6809012</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3028,7 +3033,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3038,7 +3043,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3053,22 +3063,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123548196</v>
+        <v>123548636</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3081,34 +3091,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459024</v>
+        <v>459184</v>
       </c>
       <c r="R23" t="n">
-        <v>6808872</v>
+        <v>6808784</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3140,7 +3150,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3150,7 +3160,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3177,10 +3187,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123549418</v>
+        <v>123548196</v>
       </c>
       <c r="B24" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3189,46 +3199,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459318</v>
+        <v>459024</v>
       </c>
       <c r="R24" t="n">
-        <v>6808809</v>
+        <v>6808872</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3257,7 +3262,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3267,12 +3272,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Under betestall</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3287,12 +3287,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -6811,10 +6811,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123545712</v>
+        <v>123549248</v>
       </c>
       <c r="B56" t="n">
-        <v>78883</v>
+        <v>78788</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6827,37 +6827,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459156</v>
+        <v>459268</v>
       </c>
       <c r="R56" t="n">
-        <v>6808985</v>
+        <v>6808828</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6911,22 +6911,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123549248</v>
+        <v>123545712</v>
       </c>
       <c r="B57" t="n">
-        <v>78788</v>
+        <v>78883</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6939,37 +6939,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459268</v>
+        <v>459156</v>
       </c>
       <c r="R57" t="n">
-        <v>6808828</v>
+        <v>6808985</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7023,22 +7023,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123548439</v>
+        <v>123549476</v>
       </c>
       <c r="B58" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7047,41 +7047,46 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459138</v>
+        <v>459369</v>
       </c>
       <c r="R58" t="n">
-        <v>6808765</v>
+        <v>6808793</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7110,7 +7115,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7120,7 +7125,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Under betestall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7135,19 +7145,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123543936</v>
+        <v>123548439</v>
       </c>
       <c r="B59" t="n">
         <v>78788</v>
@@ -7183,14 +7193,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459520</v>
+        <v>459138</v>
       </c>
       <c r="R59" t="n">
-        <v>6808918</v>
+        <v>6808765</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7222,7 +7232,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7232,7 +7242,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7259,7 +7269,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123548548</v>
+        <v>123543936</v>
       </c>
       <c r="B60" t="n">
         <v>78788</v>
@@ -7295,14 +7305,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459181</v>
+        <v>459520</v>
       </c>
       <c r="R60" t="n">
-        <v>6808783</v>
+        <v>6808918</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7334,7 +7344,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7344,7 +7354,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7371,7 +7381,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123549630</v>
+        <v>123548548</v>
       </c>
       <c r="B61" t="n">
         <v>78788</v>
@@ -7407,17 +7417,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459421</v>
+        <v>459181</v>
       </c>
       <c r="R61" t="n">
-        <v>6808816</v>
+        <v>6808783</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7446,7 +7456,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7456,7 +7466,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7471,22 +7481,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123549476</v>
+        <v>123549630</v>
       </c>
       <c r="B62" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7495,43 +7505,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459369</v>
+        <v>459421</v>
       </c>
       <c r="R62" t="n">
-        <v>6808793</v>
+        <v>6808816</v>
       </c>
       <c r="S62" t="n">
         <v>9</v>
@@ -7563,7 +7568,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7573,12 +7578,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Under betestall</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7941,10 +7941,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123547657</v>
+        <v>123549662</v>
       </c>
       <c r="B66" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7953,49 +7953,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>459003</v>
+        <v>459479</v>
       </c>
       <c r="R66" t="n">
-        <v>6808929</v>
+        <v>6808853</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8024,7 +8016,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8034,12 +8026,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Betestall., spillning från höna</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8054,22 +8041,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123548779</v>
+        <v>123548763</v>
       </c>
       <c r="B67" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8082,21 +8069,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8106,13 +8093,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>459073</v>
+        <v>459187</v>
       </c>
       <c r="R67" t="n">
-        <v>6808847</v>
+        <v>6808828</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8166,19 +8153,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123549662</v>
+        <v>123549171</v>
       </c>
       <c r="B68" t="n">
         <v>78788</v>
@@ -8218,13 +8205,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>459479</v>
+        <v>459253</v>
       </c>
       <c r="R68" t="n">
-        <v>6808853</v>
+        <v>6808807</v>
       </c>
       <c r="S68" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8253,7 +8240,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8263,7 +8250,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8278,22 +8265,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123548763</v>
+        <v>123547657</v>
       </c>
       <c r="B69" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8302,41 +8289,49 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>459187</v>
+        <v>459003</v>
       </c>
       <c r="R69" t="n">
-        <v>6808828</v>
+        <v>6808929</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8365,7 +8360,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8375,7 +8370,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Betestall., spillning från höna</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8390,22 +8390,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123549171</v>
+        <v>123548779</v>
       </c>
       <c r="B70" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8418,34 +8418,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>459253</v>
+        <v>459073</v>
       </c>
       <c r="R70" t="n">
-        <v>6808807</v>
+        <v>6808847</v>
       </c>
       <c r="S70" t="n">
         <v>9</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -10321,10 +10321,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123575827</v>
+        <v>123575142</v>
       </c>
       <c r="B87" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10337,37 +10337,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>459707</v>
+        <v>459609</v>
       </c>
       <c r="R87" t="n">
-        <v>6808935</v>
+        <v>6808467</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10406,7 +10406,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10421,19 +10426,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123575142</v>
+        <v>123564034</v>
       </c>
       <c r="B88" t="n">
         <v>78788</v>
@@ -10469,14 +10474,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>459609</v>
+        <v>459721</v>
       </c>
       <c r="R88" t="n">
-        <v>6808467</v>
+        <v>6808937</v>
       </c>
       <c r="S88" t="n">
         <v>9</v>
@@ -10508,7 +10513,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10518,12 +10523,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10550,10 +10550,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123564034</v>
+        <v>123575827</v>
       </c>
       <c r="B89" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10566,37 +10566,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>459721</v>
+        <v>459707</v>
       </c>
       <c r="R89" t="n">
-        <v>6808937</v>
+        <v>6808935</v>
       </c>
       <c r="S89" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10635,7 +10635,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10650,12 +10650,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -11558,10 +11558,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123573487</v>
+        <v>123563838</v>
       </c>
       <c r="B98" t="n">
-        <v>78525</v>
+        <v>57491</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11574,37 +11574,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>459764</v>
+        <v>459731</v>
       </c>
       <c r="R98" t="n">
-        <v>6808549</v>
+        <v>6808890</v>
       </c>
       <c r="S98" t="n">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11633,7 +11638,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11643,7 +11648,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11658,12 +11663,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -11782,10 +11787,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123563838</v>
+        <v>123573487</v>
       </c>
       <c r="B100" t="n">
-        <v>57491</v>
+        <v>78525</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11798,42 +11803,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>459731</v>
+        <v>459764</v>
       </c>
       <c r="R100" t="n">
-        <v>6808890</v>
+        <v>6808549</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11887,12 +11887,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -12581,10 +12581,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123566816</v>
+        <v>123567356</v>
       </c>
       <c r="B107" t="n">
-        <v>79870</v>
+        <v>78525</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12597,21 +12597,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>459735</v>
+        <v>459560</v>
       </c>
       <c r="R107" t="n">
-        <v>6808695</v>
+        <v>6808986</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12666,7 +12666,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12681,22 +12681,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123575074</v>
+        <v>123566816</v>
       </c>
       <c r="B108" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12709,37 +12709,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>459619</v>
+        <v>459735</v>
       </c>
       <c r="R108" t="n">
-        <v>6808506</v>
+        <v>6808695</v>
       </c>
       <c r="S108" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12793,22 +12793,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123566397</v>
+        <v>123575074</v>
       </c>
       <c r="B109" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12821,37 +12821,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>459735</v>
+        <v>459619</v>
       </c>
       <c r="R109" t="n">
-        <v>6808695</v>
+        <v>6808506</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12890,7 +12890,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12905,22 +12905,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123572080</v>
+        <v>123566397</v>
       </c>
       <c r="B110" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12933,21 +12933,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12957,10 +12957,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>459645</v>
+        <v>459735</v>
       </c>
       <c r="R110" t="n">
-        <v>6808629</v>
+        <v>6808695</v>
       </c>
       <c r="S110" t="n">
         <v>15</v>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13017,19 +13017,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123575052</v>
+        <v>123572080</v>
       </c>
       <c r="B111" t="n">
         <v>78788</v>
@@ -13065,17 +13065,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>459600</v>
+        <v>459645</v>
       </c>
       <c r="R111" t="n">
-        <v>6808513</v>
+        <v>6808629</v>
       </c>
       <c r="S111" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13141,10 +13141,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123575930</v>
+        <v>123575052</v>
       </c>
       <c r="B112" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13157,21 +13157,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13181,13 +13181,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>459550</v>
+        <v>459600</v>
       </c>
       <c r="R112" t="n">
-        <v>6808474</v>
+        <v>6808513</v>
       </c>
       <c r="S112" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13226,7 +13226,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13241,22 +13241,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123567356</v>
+        <v>123575930</v>
       </c>
       <c r="B113" t="n">
-        <v>78525</v>
+        <v>78524</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13269,37 +13269,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>459560</v>
+        <v>459550</v>
       </c>
       <c r="R113" t="n">
-        <v>6808986</v>
+        <v>6808474</v>
       </c>
       <c r="S113" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13353,12 +13353,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -19365,10 +19365,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>123574629</v>
+        <v>123574181</v>
       </c>
       <c r="B167" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -19381,21 +19381,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -19405,10 +19405,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>459648</v>
+        <v>459652</v>
       </c>
       <c r="R167" t="n">
-        <v>6808494</v>
+        <v>6808496</v>
       </c>
       <c r="S167" t="n">
         <v>9</v>
@@ -19440,7 +19440,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -19450,7 +19450,12 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19477,10 +19482,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>123573282</v>
+        <v>123566313</v>
       </c>
       <c r="B168" t="n">
-        <v>78525</v>
+        <v>74879</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19493,21 +19498,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -19517,13 +19522,13 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>459757</v>
+        <v>459762</v>
       </c>
       <c r="R168" t="n">
-        <v>6808589</v>
+        <v>6808880</v>
       </c>
       <c r="S168" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -19552,7 +19557,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -19562,7 +19567,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19577,19 +19582,19 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>123574181</v>
+        <v>123573959</v>
       </c>
       <c r="B169" t="n">
         <v>78788</v>
@@ -19629,10 +19634,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>459652</v>
+        <v>459676</v>
       </c>
       <c r="R169" t="n">
-        <v>6808496</v>
+        <v>6808503</v>
       </c>
       <c r="S169" t="n">
         <v>9</v>
@@ -19664,7 +19669,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -19674,7 +19679,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC169" t="inlineStr">
@@ -19706,10 +19711,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>123566313</v>
+        <v>123575210</v>
       </c>
       <c r="B170" t="n">
-        <v>74879</v>
+        <v>78524</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19722,34 +19727,34 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>459762</v>
+        <v>459619</v>
       </c>
       <c r="R170" t="n">
-        <v>6808880</v>
+        <v>6808506</v>
       </c>
       <c r="S170" t="n">
         <v>9</v>
@@ -19781,7 +19786,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -19791,7 +19796,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19806,19 +19811,19 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>123573959</v>
+        <v>123575835</v>
       </c>
       <c r="B171" t="n">
         <v>78788</v>
@@ -19858,10 +19863,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>459676</v>
+        <v>459553</v>
       </c>
       <c r="R171" t="n">
-        <v>6808503</v>
+        <v>6808474</v>
       </c>
       <c r="S171" t="n">
         <v>9</v>
@@ -19893,7 +19898,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19903,12 +19908,12 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>På tallstammar</t>
+          <t>På tallstammar 7st</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19935,10 +19940,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>123575210</v>
+        <v>123574629</v>
       </c>
       <c r="B172" t="n">
-        <v>78524</v>
+        <v>79377</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19951,21 +19956,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -19975,10 +19980,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>459619</v>
+        <v>459648</v>
       </c>
       <c r="R172" t="n">
-        <v>6808506</v>
+        <v>6808494</v>
       </c>
       <c r="S172" t="n">
         <v>9</v>
@@ -20010,7 +20015,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -20020,7 +20025,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20035,22 +20040,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>123575835</v>
+        <v>123573282</v>
       </c>
       <c r="B173" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -20063,37 +20068,37 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>459553</v>
+        <v>459757</v>
       </c>
       <c r="R173" t="n">
-        <v>6808474</v>
+        <v>6808589</v>
       </c>
       <c r="S173" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -20122,7 +20127,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -20132,12 +20137,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>På tallstammar 7st</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20152,22 +20152,22 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>123574214</v>
+        <v>123574293</v>
       </c>
       <c r="B174" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -20180,21 +20180,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -20204,10 +20204,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>459645</v>
+        <v>459648</v>
       </c>
       <c r="R174" t="n">
-        <v>6808484</v>
+        <v>6808494</v>
       </c>
       <c r="S174" t="n">
         <v>9</v>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -20249,12 +20249,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20281,10 +20276,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>123568043</v>
+        <v>123565752</v>
       </c>
       <c r="B175" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -20297,21 +20292,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -20321,13 +20316,13 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>459728</v>
+        <v>459733</v>
       </c>
       <c r="R175" t="n">
-        <v>6808677</v>
+        <v>6808745</v>
       </c>
       <c r="S175" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -20356,7 +20351,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -20366,7 +20361,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20381,22 +20376,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>123573067</v>
+        <v>123573086</v>
       </c>
       <c r="B176" t="n">
-        <v>78524</v>
+        <v>56700</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -20405,41 +20400,41 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>459717</v>
+        <v>459718</v>
       </c>
       <c r="R176" t="n">
-        <v>6808606</v>
+        <v>6808594</v>
       </c>
       <c r="S176" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -20493,22 +20488,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>123573086</v>
+        <v>123574214</v>
       </c>
       <c r="B177" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20517,25 +20512,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -20545,13 +20540,13 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>459718</v>
+        <v>459645</v>
       </c>
       <c r="R177" t="n">
-        <v>6808594</v>
+        <v>6808484</v>
       </c>
       <c r="S177" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -20580,7 +20575,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -20590,7 +20585,12 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20605,22 +20605,22 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>123565513</v>
+        <v>123568043</v>
       </c>
       <c r="B178" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20629,46 +20629,41 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>459753</v>
+        <v>459728</v>
       </c>
       <c r="R178" t="n">
-        <v>6808887</v>
+        <v>6808677</v>
       </c>
       <c r="S178" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -20697,7 +20692,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -20707,7 +20702,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20722,22 +20717,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>123574293</v>
+        <v>123573067</v>
       </c>
       <c r="B179" t="n">
-        <v>78525</v>
+        <v>78524</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20750,37 +20745,37 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>459648</v>
+        <v>459717</v>
       </c>
       <c r="R179" t="n">
-        <v>6808494</v>
+        <v>6808606</v>
       </c>
       <c r="S179" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -20809,7 +20804,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -20819,7 +20814,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20834,22 +20829,22 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>123565752</v>
+        <v>123565513</v>
       </c>
       <c r="B180" t="n">
-        <v>78525</v>
+        <v>57861</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20858,41 +20853,46 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>459733</v>
+        <v>459753</v>
       </c>
       <c r="R180" t="n">
-        <v>6808745</v>
+        <v>6808887</v>
       </c>
       <c r="S180" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -20931,7 +20931,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20946,12 +20946,12 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
@@ -22441,7 +22441,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>123573621</v>
+        <v>123546845</v>
       </c>
       <c r="B194" t="n">
         <v>56700</v>
@@ -22485,17 +22485,17 @@
       <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>459707</v>
+        <v>459131</v>
       </c>
       <c r="R194" t="n">
-        <v>6808935</v>
+        <v>6808992</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -22519,27 +22519,27 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>under betad tall</t>
+          <t>Under betestall</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22554,19 +22554,19 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>123546845</v>
+        <v>123573621</v>
       </c>
       <c r="B195" t="n">
         <v>56700</v>
@@ -22610,17 +22610,17 @@
       <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>459131</v>
+        <v>459707</v>
       </c>
       <c r="R195" t="n">
-        <v>6808992</v>
+        <v>6808935</v>
       </c>
       <c r="S195" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -22644,27 +22644,27 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Under betestall</t>
+          <t>under betad tall</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22679,12 +22679,12 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
@@ -23769,7 +23769,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>123567138</v>
+        <v>123576549</v>
       </c>
       <c r="B205" t="n">
         <v>56700</v>
@@ -23813,14 +23813,14 @@
       <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>459735</v>
+        <v>459499</v>
       </c>
       <c r="R205" t="n">
-        <v>6808695</v>
+        <v>6808603</v>
       </c>
       <c r="S205" t="n">
         <v>15</v>
@@ -23852,7 +23852,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -23862,7 +23862,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC205" t="inlineStr">
@@ -23894,7 +23894,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>123576549</v>
+        <v>123567138</v>
       </c>
       <c r="B206" t="n">
         <v>56700</v>
@@ -23938,14 +23938,14 @@
       <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>459499</v>
+        <v>459735</v>
       </c>
       <c r="R206" t="n">
-        <v>6808603</v>
+        <v>6808695</v>
       </c>
       <c r="S206" t="n">
         <v>15</v>
@@ -23977,7 +23977,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -23987,7 +23987,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC206" t="inlineStr">
@@ -25767,10 +25767,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>123544600</v>
+        <v>123568467</v>
       </c>
       <c r="B222" t="n">
-        <v>78172</v>
+        <v>57491</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -25783,37 +25783,42 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>459426</v>
+        <v>459803</v>
       </c>
       <c r="R222" t="n">
-        <v>6808964</v>
+        <v>6808817</v>
       </c>
       <c r="S222" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -25837,22 +25842,22 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -25867,22 +25872,22 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>123543338</v>
+        <v>123544600</v>
       </c>
       <c r="B223" t="n">
-        <v>57507</v>
+        <v>78172</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -25895,42 +25900,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>459630</v>
+        <v>459426</v>
       </c>
       <c r="R223" t="n">
-        <v>6808926</v>
+        <v>6808964</v>
       </c>
       <c r="S223" t="n">
         <v>15</v>
@@ -25962,7 +25959,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -25972,7 +25969,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25999,10 +25996,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>123568467</v>
+        <v>123543338</v>
       </c>
       <c r="B224" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -26015,16 +26012,16 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -26033,24 +26030,27 @@
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>459803</v>
+        <v>459630</v>
       </c>
       <c r="R224" t="n">
-        <v>6808817</v>
+        <v>6808926</v>
       </c>
       <c r="S224" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -26074,22 +26074,22 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -26104,12 +26104,12 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
@@ -26829,10 +26829,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>123728918</v>
+        <v>123725898</v>
       </c>
       <c r="B231" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -26845,21 +26845,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -26869,10 +26869,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>458818</v>
+        <v>458927</v>
       </c>
       <c r="R231" t="n">
-        <v>6808502</v>
+        <v>6808307</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26931,7 +26931,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>123725898</v>
+        <v>123725805</v>
       </c>
       <c r="B232" t="n">
         <v>78788</v>
@@ -26971,10 +26971,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>458927</v>
+        <v>458901</v>
       </c>
       <c r="R232" t="n">
-        <v>6808307</v>
+        <v>6808289</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -27033,7 +27033,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>123725805</v>
+        <v>123728287</v>
       </c>
       <c r="B233" t="n">
         <v>78788</v>
@@ -27073,10 +27073,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>458901</v>
+        <v>458826</v>
       </c>
       <c r="R233" t="n">
-        <v>6808289</v>
+        <v>6808449</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -27109,6 +27109,11 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>Garnlav på samtliga träd,mer eller mindre, på bilden.</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -27135,10 +27140,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>123728287</v>
+        <v>123728918</v>
       </c>
       <c r="B234" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -27151,21 +27156,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -27175,10 +27180,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>458826</v>
+        <v>458818</v>
       </c>
       <c r="R234" t="n">
-        <v>6808449</v>
+        <v>6808502</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -27211,11 +27216,6 @@
       <c r="AA234" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>Garnlav på samtliga träd,mer eller mindre, på bilden.</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -30927,10 +30927,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>123729517</v>
+        <v>123728549</v>
       </c>
       <c r="B270" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -30943,34 +30943,34 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>458715</v>
+        <v>458798</v>
       </c>
       <c r="R270" t="n">
-        <v>6808620</v>
+        <v>6808499</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -31003,11 +31003,6 @@
       <c r="AA270" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC270" t="inlineStr">
-        <is>
-          <t>Garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -31034,10 +31029,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>123728549</v>
+        <v>123729517</v>
       </c>
       <c r="B271" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -31050,34 +31045,34 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Dyvran, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>458798</v>
+        <v>458715</v>
       </c>
       <c r="R271" t="n">
-        <v>6808499</v>
+        <v>6808620</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -31110,6 +31105,11 @@
       <c r="AA271" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>Garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -31136,7 +31136,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>123723594</v>
+        <v>123727363</v>
       </c>
       <c r="B272" t="n">
         <v>78525</v>
@@ -31176,10 +31176,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>458948</v>
+        <v>458886</v>
       </c>
       <c r="R272" t="n">
-        <v>6808276</v>
+        <v>6808352</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -31238,7 +31238,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>123727363</v>
+        <v>123723594</v>
       </c>
       <c r="B273" t="n">
         <v>78525</v>
@@ -31278,10 +31278,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>458886</v>
+        <v>458948</v>
       </c>
       <c r="R273" t="n">
-        <v>6808352</v>
+        <v>6808276</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -36491,10 +36491,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>123833814</v>
+        <v>123831244</v>
       </c>
       <c r="B323" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -36507,37 +36507,37 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
       <c r="P323" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>459293</v>
+        <v>459393</v>
       </c>
       <c r="R323" t="n">
-        <v>6808123</v>
+        <v>6808027</v>
       </c>
       <c r="S323" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T323" t="inlineStr">
         <is>
@@ -36581,19 +36581,19 @@
       <c r="AT323" t="inlineStr"/>
       <c r="AW323" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX323" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>123829438</v>
+        <v>123833814</v>
       </c>
       <c r="B324" t="n">
         <v>78525</v>
@@ -36633,10 +36633,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>459113</v>
+        <v>459293</v>
       </c>
       <c r="R324" t="n">
-        <v>6808380</v>
+        <v>6808123</v>
       </c>
       <c r="S324" t="n">
         <v>15</v>
@@ -36695,10 +36695,10 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>123831244</v>
+        <v>123829348</v>
       </c>
       <c r="B325" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -36711,37 +36711,37 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I325" t="inlineStr"/>
       <c r="P325" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>459393</v>
+        <v>459230</v>
       </c>
       <c r="R325" t="n">
-        <v>6808027</v>
+        <v>6808362</v>
       </c>
       <c r="S325" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T325" t="inlineStr">
         <is>
@@ -36785,19 +36785,19 @@
       <c r="AT325" t="inlineStr"/>
       <c r="AW325" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX325" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>123829348</v>
+        <v>123829438</v>
       </c>
       <c r="B326" t="n">
         <v>78525</v>
@@ -36837,10 +36837,10 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>459230</v>
+        <v>459113</v>
       </c>
       <c r="R326" t="n">
-        <v>6808362</v>
+        <v>6808380</v>
       </c>
       <c r="S326" t="n">
         <v>15</v>
@@ -43773,10 +43773,10 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>123822912</v>
+        <v>123822771</v>
       </c>
       <c r="B392" t="n">
-        <v>57644</v>
+        <v>56700</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
@@ -43785,31 +43785,31 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E392" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I392" t="inlineStr"/>
       <c r="M392" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P392" t="inlineStr">
@@ -43818,10 +43818,10 @@
         </is>
       </c>
       <c r="Q392" t="n">
-        <v>459118</v>
+        <v>459307</v>
       </c>
       <c r="R392" t="n">
-        <v>6808615</v>
+        <v>6808524</v>
       </c>
       <c r="S392" t="n">
         <v>10</v>
@@ -43853,7 +43853,7 @@
       </c>
       <c r="Z392" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA392" t="inlineStr">
@@ -43863,7 +43863,7 @@
       </c>
       <c r="AB392" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD392" t="b">
@@ -43890,10 +43890,10 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>123828044</v>
+        <v>123822912</v>
       </c>
       <c r="B393" t="n">
-        <v>78788</v>
+        <v>57644</v>
       </c>
       <c r="C393" t="inlineStr">
         <is>
@@ -43906,34 +43906,39 @@
         </is>
       </c>
       <c r="E393" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I393" t="inlineStr"/>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P393" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q393" t="n">
-        <v>459681</v>
+        <v>459118</v>
       </c>
       <c r="R393" t="n">
-        <v>6808072</v>
+        <v>6808615</v>
       </c>
       <c r="S393" t="n">
         <v>10</v>
@@ -43963,14 +43968,19 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="Z393" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
       <c r="AA393" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC393" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
+      <c r="AB393" t="inlineStr">
+        <is>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD393" t="b">
@@ -43985,19 +43995,19 @@
       <c r="AT393" t="inlineStr"/>
       <c r="AW393" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX393" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>123834641</v>
+        <v>123828044</v>
       </c>
       <c r="B394" t="n">
         <v>78788</v>
@@ -44033,17 +44043,17 @@
       <c r="I394" t="inlineStr"/>
       <c r="P394" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q394" t="n">
-        <v>459405</v>
+        <v>459681</v>
       </c>
       <c r="R394" t="n">
-        <v>6808172</v>
+        <v>6808072</v>
       </c>
       <c r="S394" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T394" t="inlineStr">
         <is>
@@ -44073,6 +44083,11 @@
       <c r="AA394" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC394" t="inlineStr">
+        <is>
+          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD394" t="b">
@@ -44087,22 +44102,22 @@
       <c r="AT394" t="inlineStr"/>
       <c r="AW394" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX394" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>123822771</v>
+        <v>123834641</v>
       </c>
       <c r="B395" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
@@ -44111,46 +44126,41 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E395" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I395" t="inlineStr"/>
-      <c r="M395" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P395" t="inlineStr">
         <is>
           <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q395" t="n">
-        <v>459307</v>
+        <v>459405</v>
       </c>
       <c r="R395" t="n">
-        <v>6808524</v>
+        <v>6808172</v>
       </c>
       <c r="S395" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T395" t="inlineStr">
         <is>
@@ -44177,19 +44187,9 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="Z395" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA395" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AB395" t="inlineStr">
-        <is>
-          <t>09:48</t>
         </is>
       </c>
       <c r="AD395" t="b">
@@ -44204,12 +44204,12 @@
       <c r="AT395" t="inlineStr"/>
       <c r="AW395" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX395" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY395" t="inlineStr"/>
@@ -47371,10 +47371,10 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>123866513</v>
+        <v>123866301</v>
       </c>
       <c r="B426" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
@@ -47387,37 +47387,37 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I426" t="inlineStr"/>
       <c r="P426" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q426" t="n">
-        <v>459177</v>
+        <v>459260</v>
       </c>
       <c r="R426" t="n">
-        <v>6808709</v>
+        <v>6808646</v>
       </c>
       <c r="S426" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T426" t="inlineStr">
         <is>
@@ -47461,19 +47461,19 @@
       <c r="AT426" t="inlineStr"/>
       <c r="AW426" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX426" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>123866301</v>
+        <v>123866613</v>
       </c>
       <c r="B427" t="n">
         <v>79377</v>
@@ -47513,13 +47513,13 @@
         </is>
       </c>
       <c r="Q427" t="n">
-        <v>459260</v>
+        <v>459110</v>
       </c>
       <c r="R427" t="n">
-        <v>6808646</v>
+        <v>6808718</v>
       </c>
       <c r="S427" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T427" t="inlineStr">
         <is>
@@ -47575,10 +47575,10 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>123866613</v>
+        <v>123866513</v>
       </c>
       <c r="B428" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
@@ -47591,37 +47591,37 @@
         </is>
       </c>
       <c r="E428" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I428" t="inlineStr"/>
       <c r="P428" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q428" t="n">
-        <v>459110</v>
+        <v>459177</v>
       </c>
       <c r="R428" t="n">
-        <v>6808718</v>
+        <v>6808709</v>
       </c>
       <c r="S428" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T428" t="inlineStr">
         <is>
@@ -47665,12 +47665,12 @@
       <c r="AT428" t="inlineStr"/>
       <c r="AW428" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX428" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY428" t="inlineStr"/>
@@ -48936,10 +48936,10 @@
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>123865731</v>
+        <v>123863610</v>
       </c>
       <c r="B441" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
@@ -48948,20 +48948,20 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E441" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -48972,19 +48972,19 @@
       <c r="I441" t="inlineStr"/>
       <c r="M441" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P441" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q441" t="n">
-        <v>459340</v>
+        <v>459773</v>
       </c>
       <c r="R441" t="n">
-        <v>6808753</v>
+        <v>6808678</v>
       </c>
       <c r="S441" t="n">
         <v>10</v>
@@ -49043,10 +49043,10 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>123863610</v>
+        <v>123868528</v>
       </c>
       <c r="B442" t="n">
-        <v>57861</v>
+        <v>79377</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
@@ -49055,43 +49055,38 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E442" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I442" t="inlineStr"/>
-      <c r="M442" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P442" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q442" t="n">
-        <v>459773</v>
+        <v>459168</v>
       </c>
       <c r="R442" t="n">
-        <v>6808678</v>
+        <v>6808988</v>
       </c>
       <c r="S442" t="n">
         <v>10</v>
@@ -49138,22 +49133,22 @@
       <c r="AT442" t="inlineStr"/>
       <c r="AW442" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX442" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>123868528</v>
+        <v>123865731</v>
       </c>
       <c r="B443" t="n">
-        <v>79377</v>
+        <v>57507</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
@@ -49166,34 +49161,39 @@
         </is>
       </c>
       <c r="E443" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I443" t="inlineStr"/>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P443" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q443" t="n">
-        <v>459168</v>
+        <v>459340</v>
       </c>
       <c r="R443" t="n">
-        <v>6808988</v>
+        <v>6808753</v>
       </c>
       <c r="S443" t="n">
         <v>10</v>
@@ -49240,22 +49240,22 @@
       <c r="AT443" t="inlineStr"/>
       <c r="AW443" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX443" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>123868217</v>
+        <v>123868052</v>
       </c>
       <c r="B444" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
@@ -49268,21 +49268,21 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I444" t="inlineStr"/>
@@ -49292,13 +49292,13 @@
         </is>
       </c>
       <c r="Q444" t="n">
-        <v>459029</v>
+        <v>458921</v>
       </c>
       <c r="R444" t="n">
-        <v>6808959</v>
+        <v>6808961</v>
       </c>
       <c r="S444" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T444" t="inlineStr">
         <is>
@@ -49354,10 +49354,10 @@
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>123866559</v>
+        <v>123866561</v>
       </c>
       <c r="B445" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
@@ -49370,37 +49370,37 @@
         </is>
       </c>
       <c r="E445" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I445" t="inlineStr"/>
       <c r="P445" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q445" t="n">
-        <v>459128</v>
+        <v>459159</v>
       </c>
       <c r="R445" t="n">
-        <v>6808639</v>
+        <v>6808628</v>
       </c>
       <c r="S445" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T445" t="inlineStr">
         <is>
@@ -49430,6 +49430,11 @@
       <c r="AA445" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC445" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD445" t="b">
@@ -49444,22 +49449,22 @@
       <c r="AT445" t="inlineStr"/>
       <c r="AW445" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX445" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>123863675</v>
+        <v>123865783</v>
       </c>
       <c r="B446" t="n">
-        <v>77716</v>
+        <v>56700</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
@@ -49468,25 +49473,25 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E446" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I446" t="inlineStr"/>
@@ -49496,10 +49501,10 @@
         </is>
       </c>
       <c r="Q446" t="n">
-        <v>459743</v>
+        <v>459326</v>
       </c>
       <c r="R446" t="n">
-        <v>6808691</v>
+        <v>6808793</v>
       </c>
       <c r="S446" t="n">
         <v>20</v>
@@ -49532,6 +49537,11 @@
       <c r="AA446" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC446" t="inlineStr">
+        <is>
+          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD446" t="b">
@@ -49558,10 +49568,10 @@
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>123863840</v>
+        <v>123864050</v>
       </c>
       <c r="B447" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
@@ -49570,38 +49580,43 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E447" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I447" t="inlineStr"/>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P447" t="inlineStr">
         <is>
           <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q447" t="n">
-        <v>459689</v>
+        <v>459647</v>
       </c>
       <c r="R447" t="n">
-        <v>6808558</v>
+        <v>6808642</v>
       </c>
       <c r="S447" t="n">
         <v>20</v>
@@ -49644,6 +49659,11 @@
       </c>
       <c r="AG447" t="b">
         <v>0</v>
+      </c>
+      <c r="AH447" t="inlineStr">
+        <is>
+          <t>Öppen fastmark - med eller utan enstaka träd</t>
+        </is>
       </c>
       <c r="AT447" t="inlineStr"/>
       <c r="AW447" t="inlineStr">
@@ -49660,10 +49680,10 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>123865783</v>
+        <v>123868217</v>
       </c>
       <c r="B448" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C448" t="inlineStr">
         <is>
@@ -49672,25 +49692,25 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E448" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I448" t="inlineStr"/>
@@ -49700,13 +49720,13 @@
         </is>
       </c>
       <c r="Q448" t="n">
-        <v>459326</v>
+        <v>459029</v>
       </c>
       <c r="R448" t="n">
-        <v>6808793</v>
+        <v>6808959</v>
       </c>
       <c r="S448" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T448" t="inlineStr">
         <is>
@@ -49736,11 +49756,6 @@
       <c r="AA448" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC448" t="inlineStr">
-        <is>
-          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD448" t="b">
@@ -49767,10 +49782,10 @@
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>123864050</v>
+        <v>123866559</v>
       </c>
       <c r="B449" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
@@ -49779,43 +49794,38 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E449" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I449" t="inlineStr"/>
-      <c r="M449" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P449" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q449" t="n">
-        <v>459647</v>
+        <v>459128</v>
       </c>
       <c r="R449" t="n">
-        <v>6808642</v>
+        <v>6808639</v>
       </c>
       <c r="S449" t="n">
         <v>20</v>
@@ -49859,30 +49869,25 @@
       <c r="AG449" t="b">
         <v>0</v>
       </c>
-      <c r="AH449" t="inlineStr">
-        <is>
-          <t>Öppen fastmark - med eller utan enstaka träd</t>
-        </is>
-      </c>
       <c r="AT449" t="inlineStr"/>
       <c r="AW449" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX449" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>123868052</v>
+        <v>123863675</v>
       </c>
       <c r="B450" t="n">
-        <v>79377</v>
+        <v>77716</v>
       </c>
       <c r="C450" t="inlineStr">
         <is>
@@ -49895,21 +49900,21 @@
         </is>
       </c>
       <c r="E450" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I450" t="inlineStr"/>
@@ -49919,10 +49924,10 @@
         </is>
       </c>
       <c r="Q450" t="n">
-        <v>458921</v>
+        <v>459743</v>
       </c>
       <c r="R450" t="n">
-        <v>6808961</v>
+        <v>6808691</v>
       </c>
       <c r="S450" t="n">
         <v>20</v>
@@ -49981,10 +49986,10 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>123866561</v>
+        <v>123863840</v>
       </c>
       <c r="B451" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
@@ -49997,37 +50002,37 @@
         </is>
       </c>
       <c r="E451" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I451" t="inlineStr"/>
       <c r="P451" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q451" t="n">
-        <v>459159</v>
+        <v>459689</v>
       </c>
       <c r="R451" t="n">
-        <v>6808628</v>
+        <v>6808558</v>
       </c>
       <c r="S451" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T451" t="inlineStr">
         <is>
@@ -50057,11 +50062,6 @@
       <c r="AA451" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC451" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD451" t="b">
@@ -50076,12 +50076,12 @@
       <c r="AT451" t="inlineStr"/>
       <c r="AW451" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX451" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY451" t="inlineStr"/>
@@ -50516,10 +50516,10 @@
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>123866815</v>
+        <v>123868755</v>
       </c>
       <c r="B456" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C456" t="inlineStr">
         <is>
@@ -50532,37 +50532,37 @@
         </is>
       </c>
       <c r="E456" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I456" t="inlineStr"/>
       <c r="P456" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q456" t="n">
-        <v>458928</v>
+        <v>459291</v>
       </c>
       <c r="R456" t="n">
-        <v>6808783</v>
+        <v>6809040</v>
       </c>
       <c r="S456" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T456" t="inlineStr">
         <is>
@@ -50606,22 +50606,22 @@
       <c r="AT456" t="inlineStr"/>
       <c r="AW456" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX456" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>123869277</v>
+        <v>123864718</v>
       </c>
       <c r="B457" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C457" t="inlineStr">
         <is>
@@ -50634,37 +50634,37 @@
         </is>
       </c>
       <c r="E457" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I457" t="inlineStr"/>
       <c r="P457" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q457" t="n">
-        <v>459300</v>
+        <v>459500</v>
       </c>
       <c r="R457" t="n">
-        <v>6808875</v>
+        <v>6808604</v>
       </c>
       <c r="S457" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T457" t="inlineStr">
         <is>
@@ -50694,6 +50694,11 @@
       <c r="AA457" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC457" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD457" t="b">
@@ -50708,22 +50713,22 @@
       <c r="AT457" t="inlineStr"/>
       <c r="AW457" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX457" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>123868318</v>
+        <v>123866815</v>
       </c>
       <c r="B458" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
@@ -50732,53 +50737,38 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E458" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I458" t="inlineStr"/>
-      <c r="K458" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L458" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M458" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P458" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q458" t="n">
-        <v>459035</v>
+        <v>458928</v>
       </c>
       <c r="R458" t="n">
-        <v>6808931</v>
+        <v>6808783</v>
       </c>
       <c r="S458" t="n">
         <v>15</v>
@@ -50837,10 +50827,10 @@
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>123868755</v>
+        <v>123869277</v>
       </c>
       <c r="B459" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
@@ -50853,37 +50843,37 @@
         </is>
       </c>
       <c r="E459" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I459" t="inlineStr"/>
       <c r="P459" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q459" t="n">
-        <v>459291</v>
+        <v>459300</v>
       </c>
       <c r="R459" t="n">
-        <v>6809040</v>
+        <v>6808875</v>
       </c>
       <c r="S459" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T459" t="inlineStr">
         <is>
@@ -50927,22 +50917,22 @@
       <c r="AT459" t="inlineStr"/>
       <c r="AW459" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX459" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>123864718</v>
+        <v>123868318</v>
       </c>
       <c r="B460" t="n">
-        <v>78525</v>
+        <v>56700</v>
       </c>
       <c r="C460" t="inlineStr">
         <is>
@@ -50951,41 +50941,56 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E460" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P460" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q460" t="n">
-        <v>459500</v>
+        <v>459035</v>
       </c>
       <c r="R460" t="n">
-        <v>6808604</v>
+        <v>6808931</v>
       </c>
       <c r="S460" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T460" t="inlineStr">
         <is>
@@ -51015,11 +51020,6 @@
       <c r="AA460" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC460" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD460" t="b">
@@ -51034,12 +51034,12 @@
       <c r="AT460" t="inlineStr"/>
       <c r="AW460" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX460" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY460" t="inlineStr"/>
@@ -51917,10 +51917,10 @@
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>123864022</v>
+        <v>123866962</v>
       </c>
       <c r="B469" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C469" t="inlineStr">
         <is>
@@ -51933,34 +51933,34 @@
         </is>
       </c>
       <c r="E469" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I469" t="inlineStr"/>
       <c r="P469" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q469" t="n">
-        <v>459582</v>
+        <v>459041</v>
       </c>
       <c r="R469" t="n">
-        <v>6808669</v>
+        <v>6808701</v>
       </c>
       <c r="S469" t="n">
         <v>10</v>
@@ -51995,6 +51995,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC469" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD469" t="b">
         <v>0</v>
       </c>
@@ -52007,19 +52012,19 @@
       <c r="AT469" t="inlineStr"/>
       <c r="AW469" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX469" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>123868597</v>
+        <v>123864022</v>
       </c>
       <c r="B470" t="n">
         <v>78788</v>
@@ -52055,14 +52060,14 @@
       <c r="I470" t="inlineStr"/>
       <c r="P470" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q470" t="n">
-        <v>458836</v>
+        <v>459582</v>
       </c>
       <c r="R470" t="n">
-        <v>6809057</v>
+        <v>6808669</v>
       </c>
       <c r="S470" t="n">
         <v>10</v>
@@ -52097,11 +52102,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC470" t="inlineStr">
-        <is>
-          <t>Garnlav i en radie av ca 50 meter, synfältet. Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD470" t="b">
         <v>0</v>
       </c>
@@ -52114,19 +52114,19 @@
       <c r="AT470" t="inlineStr"/>
       <c r="AW470" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX470" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>123864392</v>
+        <v>123868597</v>
       </c>
       <c r="B471" t="n">
         <v>78788</v>
@@ -52162,14 +52162,14 @@
       <c r="I471" t="inlineStr"/>
       <c r="P471" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q471" t="n">
-        <v>459501</v>
+        <v>458836</v>
       </c>
       <c r="R471" t="n">
-        <v>6808620</v>
+        <v>6809057</v>
       </c>
       <c r="S471" t="n">
         <v>10</v>
@@ -52204,6 +52204,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC471" t="inlineStr">
+        <is>
+          <t>Garnlav i en radie av ca 50 meter, synfältet. Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD471" t="b">
         <v>0</v>
       </c>
@@ -52216,22 +52221,22 @@
       <c r="AT471" t="inlineStr"/>
       <c r="AW471" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX471" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>123864194</v>
+        <v>123864392</v>
       </c>
       <c r="B472" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C472" t="inlineStr">
         <is>
@@ -52240,43 +52245,38 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E472" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I472" t="inlineStr"/>
-      <c r="M472" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P472" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q472" t="n">
-        <v>459570</v>
+        <v>459501</v>
       </c>
       <c r="R472" t="n">
-        <v>6808616</v>
+        <v>6808620</v>
       </c>
       <c r="S472" t="n">
         <v>10</v>
@@ -52311,11 +52311,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC472" t="inlineStr">
-        <is>
-          <t>Spillning på 7 platser i närområdet. Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD472" t="b">
         <v>0</v>
       </c>
@@ -52328,22 +52323,22 @@
       <c r="AT472" t="inlineStr"/>
       <c r="AW472" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX472" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>123866962</v>
+        <v>123864194</v>
       </c>
       <c r="B473" t="n">
-        <v>79377</v>
+        <v>56700</v>
       </c>
       <c r="C473" t="inlineStr">
         <is>
@@ -52352,38 +52347,43 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E473" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I473" t="inlineStr"/>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P473" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q473" t="n">
-        <v>459041</v>
+        <v>459570</v>
       </c>
       <c r="R473" t="n">
-        <v>6808701</v>
+        <v>6808616</v>
       </c>
       <c r="S473" t="n">
         <v>10</v>
@@ -52420,7 +52420,7 @@
       </c>
       <c r="AC473" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Spillning på 7 platser i närområdet. Miljöbild.</t>
         </is>
       </c>
       <c r="AD473" t="b">
@@ -78297,10 +78297,10 @@
     </row>
     <row r="725">
       <c r="A725" t="n">
-        <v>123920662</v>
+        <v>123866170</v>
       </c>
       <c r="B725" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C725" t="inlineStr">
         <is>
@@ -78309,38 +78309,46 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E725" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I725" t="inlineStr"/>
+      <c r="K725" t="inlineStr"/>
+      <c r="L725" t="inlineStr"/>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N725" t="inlineStr"/>
       <c r="P725" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q725" t="n">
-        <v>458749</v>
+        <v>459236</v>
       </c>
       <c r="R725" t="n">
-        <v>6808795</v>
+        <v>6808707</v>
       </c>
       <c r="S725" t="n">
         <v>10</v>
@@ -78375,6 +78383,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC725" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD725" t="b">
         <v>0</v>
       </c>
@@ -78387,22 +78400,22 @@
       <c r="AT725" t="inlineStr"/>
       <c r="AW725" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX725" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY725" t="inlineStr"/>
     </row>
     <row r="726">
       <c r="A726" t="n">
-        <v>123920476</v>
+        <v>123920662</v>
       </c>
       <c r="B726" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C726" t="inlineStr">
         <is>
@@ -78411,25 +78424,25 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E726" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I726" t="inlineStr"/>
@@ -78439,10 +78452,10 @@
         </is>
       </c>
       <c r="Q726" t="n">
-        <v>459568</v>
+        <v>458749</v>
       </c>
       <c r="R726" t="n">
-        <v>6808142</v>
+        <v>6808795</v>
       </c>
       <c r="S726" t="n">
         <v>10</v>
@@ -78469,12 +78482,12 @@
       </c>
       <c r="Y726" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA726" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD726" t="b">
@@ -78494,17 +78507,17 @@
       </c>
       <c r="AX726" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY726" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" t="n">
-        <v>123920727</v>
+        <v>123920476</v>
       </c>
       <c r="B727" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C727" t="inlineStr">
         <is>
@@ -78513,25 +78526,25 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E727" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I727" t="inlineStr"/>
@@ -78541,10 +78554,10 @@
         </is>
       </c>
       <c r="Q727" t="n">
-        <v>459542</v>
+        <v>459568</v>
       </c>
       <c r="R727" t="n">
-        <v>6808123</v>
+        <v>6808142</v>
       </c>
       <c r="S727" t="n">
         <v>10</v>
@@ -78603,7 +78616,7 @@
     </row>
     <row r="728">
       <c r="A728" t="n">
-        <v>123920730</v>
+        <v>123920727</v>
       </c>
       <c r="B728" t="n">
         <v>78788</v>
@@ -78643,10 +78656,10 @@
         </is>
       </c>
       <c r="Q728" t="n">
-        <v>459590</v>
+        <v>459542</v>
       </c>
       <c r="R728" t="n">
-        <v>6808062</v>
+        <v>6808123</v>
       </c>
       <c r="S728" t="n">
         <v>10</v>
@@ -78705,10 +78718,10 @@
     </row>
     <row r="729">
       <c r="A729" t="n">
-        <v>123920457</v>
+        <v>123920730</v>
       </c>
       <c r="B729" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C729" t="inlineStr">
         <is>
@@ -78717,43 +78730,38 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E729" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I729" t="inlineStr"/>
-      <c r="M729" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P729" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q729" t="n">
-        <v>458767</v>
+        <v>459590</v>
       </c>
       <c r="R729" t="n">
-        <v>6808746</v>
+        <v>6808062</v>
       </c>
       <c r="S729" t="n">
         <v>10</v>
@@ -78780,12 +78788,12 @@
       </c>
       <c r="Y729" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA729" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD729" t="b">
@@ -78805,17 +78813,17 @@
       </c>
       <c r="AX729" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY729" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" t="n">
-        <v>123920336</v>
+        <v>123920457</v>
       </c>
       <c r="B730" t="n">
-        <v>79406</v>
+        <v>56700</v>
       </c>
       <c r="C730" t="inlineStr">
         <is>
@@ -78824,38 +78832,43 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E730" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I730" t="inlineStr"/>
+      <c r="M730" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P730" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q730" t="n">
-        <v>459520</v>
+        <v>458767</v>
       </c>
       <c r="R730" t="n">
-        <v>6808387</v>
+        <v>6808746</v>
       </c>
       <c r="S730" t="n">
         <v>10</v>
@@ -78882,12 +78895,12 @@
       </c>
       <c r="Y730" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA730" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD730" t="b">
@@ -78907,17 +78920,17 @@
       </c>
       <c r="AX730" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY730" t="inlineStr"/>
     </row>
     <row r="731">
       <c r="A731" t="n">
-        <v>123920668</v>
+        <v>123920336</v>
       </c>
       <c r="B731" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C731" t="inlineStr">
         <is>
@@ -78930,21 +78943,21 @@
         </is>
       </c>
       <c r="E731" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I731" t="inlineStr"/>
@@ -78954,10 +78967,10 @@
         </is>
       </c>
       <c r="Q731" t="n">
-        <v>458876</v>
+        <v>459520</v>
       </c>
       <c r="R731" t="n">
-        <v>6808749</v>
+        <v>6808387</v>
       </c>
       <c r="S731" t="n">
         <v>10</v>
@@ -78984,12 +78997,12 @@
       </c>
       <c r="Y731" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA731" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD731" t="b">
@@ -79009,17 +79022,17 @@
       </c>
       <c r="AX731" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY731" t="inlineStr"/>
     </row>
     <row r="732">
       <c r="A732" t="n">
-        <v>123866170</v>
+        <v>123920668</v>
       </c>
       <c r="B732" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C732" t="inlineStr">
         <is>
@@ -79028,46 +79041,38 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E732" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I732" t="inlineStr"/>
-      <c r="K732" t="inlineStr"/>
-      <c r="L732" t="inlineStr"/>
-      <c r="M732" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N732" t="inlineStr"/>
       <c r="P732" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q732" t="n">
-        <v>459236</v>
+        <v>458876</v>
       </c>
       <c r="R732" t="n">
-        <v>6808707</v>
+        <v>6808749</v>
       </c>
       <c r="S732" t="n">
         <v>10</v>
@@ -79102,11 +79107,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC732" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD732" t="b">
         <v>0</v>
       </c>
@@ -79119,12 +79119,12 @@
       <c r="AT732" t="inlineStr"/>
       <c r="AW732" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX732" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY732" t="inlineStr"/>

--- a/artfynd/A 13728-2025 artfynd.xlsx
+++ b/artfynd/A 13728-2025 artfynd.xlsx
@@ -54119,10 +54119,10 @@
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>123920598</v>
+        <v>123920448</v>
       </c>
       <c r="B490" t="n">
-        <v>78546</v>
+        <v>56722</v>
       </c>
       <c r="C490" t="inlineStr">
         <is>
@@ -54131,38 +54131,43 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E490" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I490" t="inlineStr"/>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P490" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q490" t="n">
-        <v>459727</v>
+        <v>458790</v>
       </c>
       <c r="R490" t="n">
-        <v>6808344</v>
+        <v>6808708</v>
       </c>
       <c r="S490" t="n">
         <v>10</v>
@@ -54189,12 +54194,12 @@
       </c>
       <c r="Y490" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA490" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD490" t="b">
@@ -54214,17 +54219,17 @@
       </c>
       <c r="AX490" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>123920798</v>
+        <v>123920451</v>
       </c>
       <c r="B491" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C491" t="inlineStr">
         <is>
@@ -54233,38 +54238,43 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E491" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I491" t="inlineStr"/>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P491" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q491" t="n">
-        <v>458998</v>
+        <v>459257</v>
       </c>
       <c r="R491" t="n">
-        <v>6808288</v>
+        <v>6808663</v>
       </c>
       <c r="S491" t="n">
         <v>10</v>
@@ -54291,12 +54301,12 @@
       </c>
       <c r="Y491" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA491" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD491" t="b">
@@ -54316,17 +54326,17 @@
       </c>
       <c r="AX491" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>123920658</v>
+        <v>123920602</v>
       </c>
       <c r="B492" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C492" t="inlineStr">
         <is>
@@ -54339,34 +54349,42 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I492" t="inlineStr"/>
+      <c r="K492" t="inlineStr"/>
+      <c r="L492" t="inlineStr"/>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr"/>
       <c r="P492" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q492" t="n">
-        <v>458778</v>
+        <v>459098</v>
       </c>
       <c r="R492" t="n">
-        <v>6808585</v>
+        <v>6808349</v>
       </c>
       <c r="S492" t="n">
         <v>10</v>
@@ -54393,12 +54411,12 @@
       </c>
       <c r="Y492" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA492" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD492" t="b">
@@ -54418,14 +54436,14 @@
       </c>
       <c r="AX492" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>123920656</v>
+        <v>123920679</v>
       </c>
       <c r="B493" t="n">
         <v>78810</v>
@@ -54465,10 +54483,10 @@
         </is>
       </c>
       <c r="Q493" t="n">
-        <v>458721</v>
+        <v>459257</v>
       </c>
       <c r="R493" t="n">
-        <v>6808571</v>
+        <v>6808663</v>
       </c>
       <c r="S493" t="n">
         <v>10</v>
@@ -54527,10 +54545,10 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>123920602</v>
+        <v>123920306</v>
       </c>
       <c r="B494" t="n">
-        <v>56714</v>
+        <v>79428</v>
       </c>
       <c r="C494" t="inlineStr">
         <is>
@@ -54543,42 +54561,34 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>102612</v>
+        <v>6453</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I494" t="inlineStr"/>
-      <c r="K494" t="inlineStr"/>
-      <c r="L494" t="inlineStr"/>
-      <c r="M494" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N494" t="inlineStr"/>
       <c r="P494" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q494" t="n">
-        <v>459098</v>
+        <v>458976</v>
       </c>
       <c r="R494" t="n">
-        <v>6808349</v>
+        <v>6808671</v>
       </c>
       <c r="S494" t="n">
         <v>10</v>
@@ -54605,12 +54615,12 @@
       </c>
       <c r="Y494" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA494" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD494" t="b">
@@ -54630,17 +54640,17 @@
       </c>
       <c r="AX494" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>123920387</v>
+        <v>123920798</v>
       </c>
       <c r="B495" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C495" t="inlineStr">
         <is>
@@ -54653,21 +54663,21 @@
         </is>
       </c>
       <c r="E495" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I495" t="inlineStr"/>
@@ -54677,10 +54687,10 @@
         </is>
       </c>
       <c r="Q495" t="n">
-        <v>459177</v>
+        <v>458998</v>
       </c>
       <c r="R495" t="n">
-        <v>6808653</v>
+        <v>6808288</v>
       </c>
       <c r="S495" t="n">
         <v>10</v>
@@ -54707,12 +54717,12 @@
       </c>
       <c r="Y495" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA495" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD495" t="b">
@@ -54732,17 +54742,17 @@
       </c>
       <c r="AX495" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>123920393</v>
+        <v>123920658</v>
       </c>
       <c r="B496" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C496" t="inlineStr">
         <is>
@@ -54755,21 +54765,21 @@
         </is>
       </c>
       <c r="E496" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I496" t="inlineStr"/>
@@ -54779,10 +54789,10 @@
         </is>
       </c>
       <c r="Q496" t="n">
-        <v>459347</v>
+        <v>458778</v>
       </c>
       <c r="R496" t="n">
-        <v>6808645</v>
+        <v>6808585</v>
       </c>
       <c r="S496" t="n">
         <v>10</v>
@@ -54841,7 +54851,7 @@
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>123920679</v>
+        <v>123920656</v>
       </c>
       <c r="B497" t="n">
         <v>78810</v>
@@ -54881,10 +54891,10 @@
         </is>
       </c>
       <c r="Q497" t="n">
-        <v>459257</v>
+        <v>458721</v>
       </c>
       <c r="R497" t="n">
-        <v>6808663</v>
+        <v>6808571</v>
       </c>
       <c r="S497" t="n">
         <v>10</v>
@@ -54943,10 +54953,10 @@
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>123920306</v>
+        <v>123920598</v>
       </c>
       <c r="B498" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C498" t="inlineStr">
         <is>
@@ -54959,21 +54969,21 @@
         </is>
       </c>
       <c r="E498" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I498" t="inlineStr"/>
@@ -54983,10 +54993,10 @@
         </is>
       </c>
       <c r="Q498" t="n">
-        <v>458976</v>
+        <v>459727</v>
       </c>
       <c r="R498" t="n">
-        <v>6808671</v>
+        <v>6808344</v>
       </c>
       <c r="S498" t="n">
         <v>10</v>
@@ -55013,12 +55023,12 @@
       </c>
       <c r="Y498" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA498" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD498" t="b">
@@ -55038,17 +55048,17 @@
       </c>
       <c r="AX498" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>123920448</v>
+        <v>123920387</v>
       </c>
       <c r="B499" t="n">
-        <v>56722</v>
+        <v>79399</v>
       </c>
       <c r="C499" t="inlineStr">
         <is>
@@ -55057,43 +55067,38 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E499" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I499" t="inlineStr"/>
-      <c r="M499" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P499" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q499" t="n">
-        <v>458790</v>
+        <v>459177</v>
       </c>
       <c r="R499" t="n">
-        <v>6808708</v>
+        <v>6808653</v>
       </c>
       <c r="S499" t="n">
         <v>10</v>
@@ -55152,10 +55157,10 @@
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>123920451</v>
+        <v>123920393</v>
       </c>
       <c r="B500" t="n">
-        <v>56722</v>
+        <v>79399</v>
       </c>
       <c r="C500" t="inlineStr">
         <is>
@@ -55164,43 +55169,38 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E500" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I500" t="inlineStr"/>
-      <c r="M500" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P500" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q500" t="n">
-        <v>459257</v>
+        <v>459347</v>
       </c>
       <c r="R500" t="n">
-        <v>6808663</v>
+        <v>6808645</v>
       </c>
       <c r="S500" t="n">
         <v>10</v>
@@ -56196,10 +56196,10 @@
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>123920910</v>
+        <v>123920334</v>
       </c>
       <c r="B510" t="n">
-        <v>92293</v>
+        <v>79428</v>
       </c>
       <c r="C510" t="inlineStr">
         <is>
@@ -56208,25 +56208,25 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E510" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I510" t="inlineStr"/>
@@ -56236,10 +56236,10 @@
         </is>
       </c>
       <c r="Q510" t="n">
-        <v>458914</v>
+        <v>459343</v>
       </c>
       <c r="R510" t="n">
-        <v>6808283</v>
+        <v>6808423</v>
       </c>
       <c r="S510" t="n">
         <v>10</v>
@@ -56291,17 +56291,17 @@
       </c>
       <c r="AX510" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Niklas Rehn, Håkan Thenander, lennart karlsson, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>123920484</v>
+        <v>123920315</v>
       </c>
       <c r="B511" t="n">
-        <v>79892</v>
+        <v>79428</v>
       </c>
       <c r="C511" t="inlineStr">
         <is>
@@ -56314,21 +56314,21 @@
         </is>
       </c>
       <c r="E511" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I511" t="inlineStr"/>
@@ -56338,10 +56338,10 @@
         </is>
       </c>
       <c r="Q511" t="n">
-        <v>459592</v>
+        <v>459450</v>
       </c>
       <c r="R511" t="n">
-        <v>6808153</v>
+        <v>6808625</v>
       </c>
       <c r="S511" t="n">
         <v>10</v>
@@ -56368,12 +56368,12 @@
       </c>
       <c r="Y511" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA511" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD511" t="b">
@@ -56393,17 +56393,17 @@
       </c>
       <c r="AX511" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>123920918</v>
+        <v>123920662</v>
       </c>
       <c r="B512" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C512" t="inlineStr">
         <is>
@@ -56416,21 +56416,21 @@
         </is>
       </c>
       <c r="E512" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I512" t="inlineStr"/>
@@ -56440,10 +56440,10 @@
         </is>
       </c>
       <c r="Q512" t="n">
-        <v>459805</v>
+        <v>458749</v>
       </c>
       <c r="R512" t="n">
-        <v>6808635</v>
+        <v>6808795</v>
       </c>
       <c r="S512" t="n">
         <v>10</v>
@@ -56502,10 +56502,10 @@
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>123920334</v>
+        <v>123920815</v>
       </c>
       <c r="B513" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C513" t="inlineStr">
         <is>
@@ -56518,21 +56518,21 @@
         </is>
       </c>
       <c r="E513" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I513" t="inlineStr"/>
@@ -56542,10 +56542,10 @@
         </is>
       </c>
       <c r="Q513" t="n">
-        <v>459343</v>
+        <v>459280</v>
       </c>
       <c r="R513" t="n">
-        <v>6808423</v>
+        <v>6808403</v>
       </c>
       <c r="S513" t="n">
         <v>10</v>
@@ -56597,17 +56597,17 @@
       </c>
       <c r="AX513" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>123920315</v>
+        <v>123920910</v>
       </c>
       <c r="B514" t="n">
-        <v>79428</v>
+        <v>92293</v>
       </c>
       <c r="C514" t="inlineStr">
         <is>
@@ -56616,25 +56616,25 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E514" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I514" t="inlineStr"/>
@@ -56644,10 +56644,10 @@
         </is>
       </c>
       <c r="Q514" t="n">
-        <v>459450</v>
+        <v>458914</v>
       </c>
       <c r="R514" t="n">
-        <v>6808625</v>
+        <v>6808283</v>
       </c>
       <c r="S514" t="n">
         <v>10</v>
@@ -56674,12 +56674,12 @@
       </c>
       <c r="Y514" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA514" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD514" t="b">
@@ -56699,17 +56699,17 @@
       </c>
       <c r="AX514" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Niklas Rehn, Håkan Thenander, lennart karlsson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>123920815</v>
+        <v>123920484</v>
       </c>
       <c r="B515" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C515" t="inlineStr">
         <is>
@@ -56722,21 +56722,21 @@
         </is>
       </c>
       <c r="E515" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I515" t="inlineStr"/>
@@ -56746,10 +56746,10 @@
         </is>
       </c>
       <c r="Q515" t="n">
-        <v>459280</v>
+        <v>459592</v>
       </c>
       <c r="R515" t="n">
-        <v>6808403</v>
+        <v>6808153</v>
       </c>
       <c r="S515" t="n">
         <v>10</v>
@@ -56808,10 +56808,10 @@
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>123920662</v>
+        <v>123920918</v>
       </c>
       <c r="B516" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C516" t="inlineStr">
         <is>
@@ -56824,21 +56824,21 @@
         </is>
       </c>
       <c r="E516" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I516" t="inlineStr"/>
@@ -56848,10 +56848,10 @@
         </is>
       </c>
       <c r="Q516" t="n">
-        <v>458749</v>
+        <v>459805</v>
       </c>
       <c r="R516" t="n">
-        <v>6808795</v>
+        <v>6808635</v>
       </c>
       <c r="S516" t="n">
         <v>10</v>
@@ -57124,10 +57124,10 @@
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>123920911</v>
+        <v>123920443</v>
       </c>
       <c r="B519" t="n">
-        <v>92293</v>
+        <v>56722</v>
       </c>
       <c r="C519" t="inlineStr">
         <is>
@@ -57140,34 +57140,39 @@
         </is>
       </c>
       <c r="E519" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I519" t="inlineStr"/>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P519" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q519" t="n">
-        <v>459628</v>
+        <v>459076</v>
       </c>
       <c r="R519" t="n">
-        <v>6808232</v>
+        <v>6808337</v>
       </c>
       <c r="S519" t="n">
         <v>10</v>
@@ -57219,17 +57224,17 @@
       </c>
       <c r="AX519" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Niklas Rehn, Håkan Thenander, lennart karlsson, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>123920609</v>
+        <v>123920392</v>
       </c>
       <c r="B520" t="n">
-        <v>77738</v>
+        <v>79399</v>
       </c>
       <c r="C520" t="inlineStr">
         <is>
@@ -57242,21 +57247,21 @@
         </is>
       </c>
       <c r="E520" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I520" t="inlineStr"/>
@@ -57266,10 +57271,10 @@
         </is>
       </c>
       <c r="Q520" t="n">
-        <v>459783</v>
+        <v>459317</v>
       </c>
       <c r="R520" t="n">
-        <v>6808682</v>
+        <v>6808694</v>
       </c>
       <c r="S520" t="n">
         <v>10</v>
@@ -57310,7 +57315,6 @@
       <c r="AE520" t="b">
         <v>0</v>
       </c>
-      <c r="AF520" t="inlineStr"/>
       <c r="AG520" t="b">
         <v>0</v>
       </c>
@@ -57329,10 +57333,10 @@
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>123920476</v>
+        <v>123920609</v>
       </c>
       <c r="B521" t="n">
-        <v>79920</v>
+        <v>77738</v>
       </c>
       <c r="C521" t="inlineStr">
         <is>
@@ -57341,25 +57345,25 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E521" t="n">
-        <v>6462</v>
+        <v>6487</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I521" t="inlineStr"/>
@@ -57369,10 +57373,10 @@
         </is>
       </c>
       <c r="Q521" t="n">
-        <v>459568</v>
+        <v>459783</v>
       </c>
       <c r="R521" t="n">
-        <v>6808142</v>
+        <v>6808682</v>
       </c>
       <c r="S521" t="n">
         <v>10</v>
@@ -57399,12 +57403,12 @@
       </c>
       <c r="Y521" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA521" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD521" t="b">
@@ -57413,6 +57417,7 @@
       <c r="AE521" t="b">
         <v>0</v>
       </c>
+      <c r="AF521" t="inlineStr"/>
       <c r="AG521" t="b">
         <v>0</v>
       </c>
@@ -57424,17 +57429,17 @@
       </c>
       <c r="AX521" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>123920795</v>
+        <v>123920476</v>
       </c>
       <c r="B522" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C522" t="inlineStr">
         <is>
@@ -57443,25 +57448,25 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E522" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I522" t="inlineStr"/>
@@ -57471,10 +57476,10 @@
         </is>
       </c>
       <c r="Q522" t="n">
-        <v>458927</v>
+        <v>459568</v>
       </c>
       <c r="R522" t="n">
-        <v>6808282</v>
+        <v>6808142</v>
       </c>
       <c r="S522" t="n">
         <v>10</v>
@@ -57533,7 +57538,7 @@
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>123920694</v>
+        <v>123920795</v>
       </c>
       <c r="B523" t="n">
         <v>78810</v>
@@ -57573,10 +57578,10 @@
         </is>
       </c>
       <c r="Q523" t="n">
-        <v>459726</v>
+        <v>458927</v>
       </c>
       <c r="R523" t="n">
-        <v>6808665</v>
+        <v>6808282</v>
       </c>
       <c r="S523" t="n">
         <v>10</v>
@@ -57603,12 +57608,12 @@
       </c>
       <c r="Y523" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA523" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD523" t="b">
@@ -57628,14 +57633,14 @@
       </c>
       <c r="AX523" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>123920734</v>
+        <v>123920689</v>
       </c>
       <c r="B524" t="n">
         <v>78810</v>
@@ -57675,10 +57680,10 @@
         </is>
       </c>
       <c r="Q524" t="n">
-        <v>459613</v>
+        <v>459656</v>
       </c>
       <c r="R524" t="n">
-        <v>6807959</v>
+        <v>6808574</v>
       </c>
       <c r="S524" t="n">
         <v>10</v>
@@ -57705,12 +57710,12 @@
       </c>
       <c r="Y524" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA524" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD524" t="b">
@@ -57730,7 +57735,7 @@
       </c>
       <c r="AX524" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY524" t="inlineStr"/>
@@ -57839,10 +57844,10 @@
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>123920813</v>
+        <v>123920911</v>
       </c>
       <c r="B526" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C526" t="inlineStr">
         <is>
@@ -57851,25 +57856,25 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E526" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I526" t="inlineStr"/>
@@ -57879,10 +57884,10 @@
         </is>
       </c>
       <c r="Q526" t="n">
-        <v>459237</v>
+        <v>459628</v>
       </c>
       <c r="R526" t="n">
-        <v>6808364</v>
+        <v>6808232</v>
       </c>
       <c r="S526" t="n">
         <v>10</v>
@@ -57934,17 +57939,17 @@
       </c>
       <c r="AX526" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Niklas Rehn, Håkan Thenander, lennart karlsson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>123920443</v>
+        <v>123920694</v>
       </c>
       <c r="B527" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C527" t="inlineStr">
         <is>
@@ -57953,43 +57958,38 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E527" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I527" t="inlineStr"/>
-      <c r="M527" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P527" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q527" t="n">
-        <v>459076</v>
+        <v>459726</v>
       </c>
       <c r="R527" t="n">
-        <v>6808337</v>
+        <v>6808665</v>
       </c>
       <c r="S527" t="n">
         <v>10</v>
@@ -58016,12 +58016,12 @@
       </c>
       <c r="Y527" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA527" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD527" t="b">
@@ -58041,17 +58041,17 @@
       </c>
       <c r="AX527" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>123920392</v>
+        <v>123920734</v>
       </c>
       <c r="B528" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C528" t="inlineStr">
         <is>
@@ -58064,21 +58064,21 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I528" t="inlineStr"/>
@@ -58088,10 +58088,10 @@
         </is>
       </c>
       <c r="Q528" t="n">
-        <v>459317</v>
+        <v>459613</v>
       </c>
       <c r="R528" t="n">
-        <v>6808694</v>
+        <v>6807959</v>
       </c>
       <c r="S528" t="n">
         <v>10</v>
@@ -58118,12 +58118,12 @@
       </c>
       <c r="Y528" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA528" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD528" t="b">
@@ -58143,14 +58143,14 @@
       </c>
       <c r="AX528" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>123920689</v>
+        <v>123920813</v>
       </c>
       <c r="B529" t="n">
         <v>78810</v>
@@ -58190,10 +58190,10 @@
         </is>
       </c>
       <c r="Q529" t="n">
-        <v>459656</v>
+        <v>459237</v>
       </c>
       <c r="R529" t="n">
-        <v>6808574</v>
+        <v>6808364</v>
       </c>
       <c r="S529" t="n">
         <v>10</v>
@@ -58220,12 +58220,12 @@
       </c>
       <c r="Y529" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA529" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD529" t="b">
@@ -58245,7 +58245,7 @@
       </c>
       <c r="AX529" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY529" t="inlineStr"/>
@@ -59902,10 +59902,10 @@
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>123920458</v>
+        <v>123920676</v>
       </c>
       <c r="B546" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C546" t="inlineStr">
         <is>
@@ -59914,43 +59914,38 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E546" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I546" t="inlineStr"/>
-      <c r="M546" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P546" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q546" t="n">
-        <v>458745</v>
+        <v>459081</v>
       </c>
       <c r="R546" t="n">
-        <v>6808854</v>
+        <v>6808680</v>
       </c>
       <c r="S546" t="n">
         <v>10</v>
@@ -60009,10 +60004,10 @@
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>123920450</v>
+        <v>123920688</v>
       </c>
       <c r="B547" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C547" t="inlineStr">
         <is>
@@ -60021,43 +60016,38 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E547" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I547" t="inlineStr"/>
-      <c r="M547" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P547" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q547" t="n">
-        <v>459083</v>
+        <v>459629</v>
       </c>
       <c r="R547" t="n">
-        <v>6808668</v>
+        <v>6808646</v>
       </c>
       <c r="S547" t="n">
         <v>10</v>
@@ -60116,10 +60106,10 @@
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>123920461</v>
+        <v>123920669</v>
       </c>
       <c r="B548" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C548" t="inlineStr">
         <is>
@@ -60128,43 +60118,38 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E548" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I548" t="inlineStr"/>
-      <c r="M548" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P548" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q548" t="n">
-        <v>459317</v>
+        <v>458872</v>
       </c>
       <c r="R548" t="n">
-        <v>6808694</v>
+        <v>6808710</v>
       </c>
       <c r="S548" t="n">
         <v>10</v>
@@ -60223,10 +60208,10 @@
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>123920385</v>
+        <v>123920774</v>
       </c>
       <c r="B549" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C549" t="inlineStr">
         <is>
@@ -60239,21 +60224,21 @@
         </is>
       </c>
       <c r="E549" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I549" t="inlineStr"/>
@@ -60263,10 +60248,10 @@
         </is>
       </c>
       <c r="Q549" t="n">
-        <v>458755</v>
+        <v>459202</v>
       </c>
       <c r="R549" t="n">
-        <v>6808926</v>
+        <v>6808030</v>
       </c>
       <c r="S549" t="n">
         <v>10</v>
@@ -60293,12 +60278,12 @@
       </c>
       <c r="Y549" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA549" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD549" t="b">
@@ -60318,17 +60303,17 @@
       </c>
       <c r="AX549" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>123920378</v>
+        <v>123920691</v>
       </c>
       <c r="B550" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C550" t="inlineStr">
         <is>
@@ -60341,21 +60326,21 @@
         </is>
       </c>
       <c r="E550" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I550" t="inlineStr"/>
@@ -60365,10 +60350,10 @@
         </is>
       </c>
       <c r="Q550" t="n">
-        <v>459639</v>
+        <v>459688</v>
       </c>
       <c r="R550" t="n">
-        <v>6808598</v>
+        <v>6808555</v>
       </c>
       <c r="S550" t="n">
         <v>10</v>
@@ -60427,10 +60412,10 @@
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>123920594</v>
+        <v>123920378</v>
       </c>
       <c r="B551" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C551" t="inlineStr">
         <is>
@@ -60443,21 +60428,21 @@
         </is>
       </c>
       <c r="E551" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I551" t="inlineStr"/>
@@ -60467,10 +60452,10 @@
         </is>
       </c>
       <c r="Q551" t="n">
-        <v>459274</v>
+        <v>459639</v>
       </c>
       <c r="R551" t="n">
-        <v>6808674</v>
+        <v>6808598</v>
       </c>
       <c r="S551" t="n">
         <v>10</v>
@@ -60529,10 +60514,10 @@
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>123920730</v>
+        <v>123920594</v>
       </c>
       <c r="B552" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C552" t="inlineStr">
         <is>
@@ -60545,21 +60530,21 @@
         </is>
       </c>
       <c r="E552" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I552" t="inlineStr"/>
@@ -60569,10 +60554,10 @@
         </is>
       </c>
       <c r="Q552" t="n">
-        <v>459590</v>
+        <v>459274</v>
       </c>
       <c r="R552" t="n">
-        <v>6808062</v>
+        <v>6808674</v>
       </c>
       <c r="S552" t="n">
         <v>10</v>
@@ -60599,12 +60584,12 @@
       </c>
       <c r="Y552" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA552" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD552" t="b">
@@ -60624,17 +60609,17 @@
       </c>
       <c r="AX552" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>123920380</v>
+        <v>123920730</v>
       </c>
       <c r="B553" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C553" t="inlineStr">
         <is>
@@ -60647,21 +60632,21 @@
         </is>
       </c>
       <c r="E553" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I553" t="inlineStr"/>
@@ -60671,10 +60656,10 @@
         </is>
       </c>
       <c r="Q553" t="n">
-        <v>459217</v>
+        <v>459590</v>
       </c>
       <c r="R553" t="n">
-        <v>6808383</v>
+        <v>6808062</v>
       </c>
       <c r="S553" t="n">
         <v>10</v>
@@ -60726,14 +60711,14 @@
       </c>
       <c r="AX553" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>123920301</v>
+        <v>123920380</v>
       </c>
       <c r="B554" t="n">
         <v>79428</v>
@@ -60773,10 +60758,10 @@
         </is>
       </c>
       <c r="Q554" t="n">
-        <v>458755</v>
+        <v>459217</v>
       </c>
       <c r="R554" t="n">
-        <v>6808926</v>
+        <v>6808383</v>
       </c>
       <c r="S554" t="n">
         <v>10</v>
@@ -60803,12 +60788,12 @@
       </c>
       <c r="Y554" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA554" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD554" t="b">
@@ -60828,17 +60813,17 @@
       </c>
       <c r="AX554" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>123920676</v>
+        <v>123920301</v>
       </c>
       <c r="B555" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C555" t="inlineStr">
         <is>
@@ -60851,21 +60836,21 @@
         </is>
       </c>
       <c r="E555" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I555" t="inlineStr"/>
@@ -60875,10 +60860,10 @@
         </is>
       </c>
       <c r="Q555" t="n">
-        <v>459081</v>
+        <v>458755</v>
       </c>
       <c r="R555" t="n">
-        <v>6808680</v>
+        <v>6808926</v>
       </c>
       <c r="S555" t="n">
         <v>10</v>
@@ -60937,10 +60922,10 @@
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>123920688</v>
+        <v>123920458</v>
       </c>
       <c r="B556" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C556" t="inlineStr">
         <is>
@@ -60949,38 +60934,43 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E556" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I556" t="inlineStr"/>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P556" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q556" t="n">
-        <v>459629</v>
+        <v>458745</v>
       </c>
       <c r="R556" t="n">
-        <v>6808646</v>
+        <v>6808854</v>
       </c>
       <c r="S556" t="n">
         <v>10</v>
@@ -61039,10 +61029,10 @@
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>123920669</v>
+        <v>123920450</v>
       </c>
       <c r="B557" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C557" t="inlineStr">
         <is>
@@ -61051,38 +61041,43 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E557" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I557" t="inlineStr"/>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P557" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q557" t="n">
-        <v>458872</v>
+        <v>459083</v>
       </c>
       <c r="R557" t="n">
-        <v>6808710</v>
+        <v>6808668</v>
       </c>
       <c r="S557" t="n">
         <v>10</v>
@@ -61141,10 +61136,10 @@
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>123920774</v>
+        <v>123920461</v>
       </c>
       <c r="B558" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C558" t="inlineStr">
         <is>
@@ -61153,38 +61148,43 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E558" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I558" t="inlineStr"/>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P558" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q558" t="n">
-        <v>459202</v>
+        <v>459317</v>
       </c>
       <c r="R558" t="n">
-        <v>6808030</v>
+        <v>6808694</v>
       </c>
       <c r="S558" t="n">
         <v>10</v>
@@ -61211,12 +61211,12 @@
       </c>
       <c r="Y558" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA558" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD558" t="b">
@@ -61236,17 +61236,17 @@
       </c>
       <c r="AX558" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>123920691</v>
+        <v>123920385</v>
       </c>
       <c r="B559" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C559" t="inlineStr">
         <is>
@@ -61259,21 +61259,21 @@
         </is>
       </c>
       <c r="E559" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I559" t="inlineStr"/>
@@ -61283,10 +61283,10 @@
         </is>
       </c>
       <c r="Q559" t="n">
-        <v>459688</v>
+        <v>458755</v>
       </c>
       <c r="R559" t="n">
-        <v>6808555</v>
+        <v>6808926</v>
       </c>
       <c r="S559" t="n">
         <v>10</v>
@@ -61345,10 +61345,10 @@
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>123920916</v>
+        <v>123920320</v>
       </c>
       <c r="B560" t="n">
-        <v>88359</v>
+        <v>79428</v>
       </c>
       <c r="C560" t="inlineStr">
         <is>
@@ -61361,21 +61361,21 @@
         </is>
       </c>
       <c r="E560" t="n">
-        <v>510</v>
+        <v>6453</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I560" t="inlineStr"/>
@@ -61385,10 +61385,10 @@
         </is>
       </c>
       <c r="Q560" t="n">
-        <v>459694</v>
+        <v>459707</v>
       </c>
       <c r="R560" t="n">
-        <v>6808564</v>
+        <v>6808607</v>
       </c>
       <c r="S560" t="n">
         <v>10</v>
@@ -61447,10 +61447,10 @@
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>123920320</v>
+        <v>123920818</v>
       </c>
       <c r="B561" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C561" t="inlineStr">
         <is>
@@ -61463,21 +61463,21 @@
         </is>
       </c>
       <c r="E561" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I561" t="inlineStr"/>
@@ -61487,10 +61487,10 @@
         </is>
       </c>
       <c r="Q561" t="n">
-        <v>459707</v>
+        <v>459458</v>
       </c>
       <c r="R561" t="n">
-        <v>6808607</v>
+        <v>6808385</v>
       </c>
       <c r="S561" t="n">
         <v>10</v>
@@ -61517,12 +61517,12 @@
       </c>
       <c r="Y561" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA561" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD561" t="b">
@@ -61542,17 +61542,17 @@
       </c>
       <c r="AX561" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>123920727</v>
+        <v>123920307</v>
       </c>
       <c r="B562" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C562" t="inlineStr">
         <is>
@@ -61565,21 +61565,21 @@
         </is>
       </c>
       <c r="E562" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I562" t="inlineStr"/>
@@ -61589,10 +61589,10 @@
         </is>
       </c>
       <c r="Q562" t="n">
-        <v>459542</v>
+        <v>459042</v>
       </c>
       <c r="R562" t="n">
-        <v>6808123</v>
+        <v>6808653</v>
       </c>
       <c r="S562" t="n">
         <v>10</v>
@@ -61619,12 +61619,12 @@
       </c>
       <c r="Y562" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA562" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD562" t="b">
@@ -61644,17 +61644,17 @@
       </c>
       <c r="AX562" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>123920529</v>
+        <v>123920829</v>
       </c>
       <c r="B563" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C563" t="inlineStr">
         <is>
@@ -61667,21 +61667,21 @@
         </is>
       </c>
       <c r="E563" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I563" t="inlineStr"/>
@@ -61691,10 +61691,10 @@
         </is>
       </c>
       <c r="Q563" t="n">
-        <v>459828</v>
+        <v>459622</v>
       </c>
       <c r="R563" t="n">
-        <v>6808640</v>
+        <v>6808222</v>
       </c>
       <c r="S563" t="n">
         <v>10</v>
@@ -61721,12 +61721,12 @@
       </c>
       <c r="Y563" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA563" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD563" t="b">
@@ -61746,17 +61746,17 @@
       </c>
       <c r="AX563" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>123920548</v>
+        <v>123920300</v>
       </c>
       <c r="B564" t="n">
-        <v>78547</v>
+        <v>79428</v>
       </c>
       <c r="C564" t="inlineStr">
         <is>
@@ -61769,21 +61769,21 @@
         </is>
       </c>
       <c r="E564" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I564" t="inlineStr"/>
@@ -61793,10 +61793,10 @@
         </is>
       </c>
       <c r="Q564" t="n">
-        <v>459139</v>
+        <v>458749</v>
       </c>
       <c r="R564" t="n">
-        <v>6808358</v>
+        <v>6808795</v>
       </c>
       <c r="S564" t="n">
         <v>10</v>
@@ -61823,12 +61823,12 @@
       </c>
       <c r="Y564" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA564" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD564" t="b">
@@ -61848,17 +61848,17 @@
       </c>
       <c r="AX564" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="n">
-        <v>123920530</v>
+        <v>123920727</v>
       </c>
       <c r="B565" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C565" t="inlineStr">
         <is>
@@ -61871,21 +61871,21 @@
         </is>
       </c>
       <c r="E565" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I565" t="inlineStr"/>
@@ -61895,10 +61895,10 @@
         </is>
       </c>
       <c r="Q565" t="n">
-        <v>459850</v>
+        <v>459542</v>
       </c>
       <c r="R565" t="n">
-        <v>6808588</v>
+        <v>6808123</v>
       </c>
       <c r="S565" t="n">
         <v>10</v>
@@ -61925,12 +61925,12 @@
       </c>
       <c r="Y565" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA565" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD565" t="b">
@@ -61950,17 +61950,17 @@
       </c>
       <c r="AX565" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="n">
-        <v>123920396</v>
+        <v>123920916</v>
       </c>
       <c r="B566" t="n">
-        <v>79399</v>
+        <v>88359</v>
       </c>
       <c r="C566" t="inlineStr">
         <is>
@@ -61973,21 +61973,21 @@
         </is>
       </c>
       <c r="E566" t="n">
-        <v>229821</v>
+        <v>510</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I566" t="inlineStr"/>
@@ -61997,10 +61997,10 @@
         </is>
       </c>
       <c r="Q566" t="n">
-        <v>459516</v>
+        <v>459694</v>
       </c>
       <c r="R566" t="n">
-        <v>6808647</v>
+        <v>6808564</v>
       </c>
       <c r="S566" t="n">
         <v>10</v>
@@ -62059,10 +62059,10 @@
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>123920386</v>
+        <v>123920462</v>
       </c>
       <c r="B567" t="n">
-        <v>79399</v>
+        <v>56722</v>
       </c>
       <c r="C567" t="inlineStr">
         <is>
@@ -62071,38 +62071,43 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E567" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I567" t="inlineStr"/>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P567" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q567" t="n">
-        <v>458872</v>
+        <v>459568</v>
       </c>
       <c r="R567" t="n">
-        <v>6808771</v>
+        <v>6808641</v>
       </c>
       <c r="S567" t="n">
         <v>10</v>
@@ -62161,10 +62166,10 @@
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>123920818</v>
+        <v>123920529</v>
       </c>
       <c r="B568" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C568" t="inlineStr">
         <is>
@@ -62177,21 +62182,21 @@
         </is>
       </c>
       <c r="E568" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I568" t="inlineStr"/>
@@ -62201,10 +62206,10 @@
         </is>
       </c>
       <c r="Q568" t="n">
-        <v>459458</v>
+        <v>459828</v>
       </c>
       <c r="R568" t="n">
-        <v>6808385</v>
+        <v>6808640</v>
       </c>
       <c r="S568" t="n">
         <v>10</v>
@@ -62231,12 +62236,12 @@
       </c>
       <c r="Y568" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA568" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD568" t="b">
@@ -62256,17 +62261,17 @@
       </c>
       <c r="AX568" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>123920307</v>
+        <v>123920548</v>
       </c>
       <c r="B569" t="n">
-        <v>79428</v>
+        <v>78547</v>
       </c>
       <c r="C569" t="inlineStr">
         <is>
@@ -62279,21 +62284,21 @@
         </is>
       </c>
       <c r="E569" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I569" t="inlineStr"/>
@@ -62303,10 +62308,10 @@
         </is>
       </c>
       <c r="Q569" t="n">
-        <v>459042</v>
+        <v>459139</v>
       </c>
       <c r="R569" t="n">
-        <v>6808653</v>
+        <v>6808358</v>
       </c>
       <c r="S569" t="n">
         <v>10</v>
@@ -62333,12 +62338,12 @@
       </c>
       <c r="Y569" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA569" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD569" t="b">
@@ -62358,17 +62363,17 @@
       </c>
       <c r="AX569" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>123920829</v>
+        <v>123920530</v>
       </c>
       <c r="B570" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C570" t="inlineStr">
         <is>
@@ -62381,21 +62386,21 @@
         </is>
       </c>
       <c r="E570" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I570" t="inlineStr"/>
@@ -62405,10 +62410,10 @@
         </is>
       </c>
       <c r="Q570" t="n">
-        <v>459622</v>
+        <v>459850</v>
       </c>
       <c r="R570" t="n">
-        <v>6808222</v>
+        <v>6808588</v>
       </c>
       <c r="S570" t="n">
         <v>10</v>
@@ -62435,12 +62440,12 @@
       </c>
       <c r="Y570" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA570" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD570" t="b">
@@ -62460,17 +62465,17 @@
       </c>
       <c r="AX570" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>123920300</v>
+        <v>123920396</v>
       </c>
       <c r="B571" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C571" t="inlineStr">
         <is>
@@ -62483,21 +62488,21 @@
         </is>
       </c>
       <c r="E571" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I571" t="inlineStr"/>
@@ -62507,10 +62512,10 @@
         </is>
       </c>
       <c r="Q571" t="n">
-        <v>458749</v>
+        <v>459516</v>
       </c>
       <c r="R571" t="n">
-        <v>6808795</v>
+        <v>6808647</v>
       </c>
       <c r="S571" t="n">
         <v>10</v>
@@ -62569,10 +62574,10 @@
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>123920462</v>
+        <v>123920386</v>
       </c>
       <c r="B572" t="n">
-        <v>56722</v>
+        <v>79399</v>
       </c>
       <c r="C572" t="inlineStr">
         <is>
@@ -62581,43 +62586,38 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E572" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I572" t="inlineStr"/>
-      <c r="M572" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P572" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q572" t="n">
-        <v>459568</v>
+        <v>458872</v>
       </c>
       <c r="R572" t="n">
-        <v>6808641</v>
+        <v>6808771</v>
       </c>
       <c r="S572" t="n">
         <v>10</v>
@@ -63186,10 +63186,10 @@
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>123920574</v>
+        <v>123920442</v>
       </c>
       <c r="B578" t="n">
-        <v>80763</v>
+        <v>56722</v>
       </c>
       <c r="C578" t="inlineStr">
         <is>
@@ -63198,38 +63198,43 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E578" t="n">
-        <v>1049</v>
+        <v>100138</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I578" t="inlineStr"/>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P578" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q578" t="n">
-        <v>459553</v>
+        <v>459593</v>
       </c>
       <c r="R578" t="n">
-        <v>6808239</v>
+        <v>6807978</v>
       </c>
       <c r="S578" t="n">
         <v>10</v>
@@ -63281,17 +63286,17 @@
       </c>
       <c r="AX578" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>123920597</v>
+        <v>123920574</v>
       </c>
       <c r="B579" t="n">
-        <v>78546</v>
+        <v>80763</v>
       </c>
       <c r="C579" t="inlineStr">
         <is>
@@ -63304,21 +63309,21 @@
         </is>
       </c>
       <c r="E579" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I579" t="inlineStr"/>
@@ -63328,10 +63333,10 @@
         </is>
       </c>
       <c r="Q579" t="n">
-        <v>459448</v>
+        <v>459553</v>
       </c>
       <c r="R579" t="n">
-        <v>6808388</v>
+        <v>6808239</v>
       </c>
       <c r="S579" t="n">
         <v>10</v>
@@ -63390,10 +63395,10 @@
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>123920442</v>
+        <v>123920597</v>
       </c>
       <c r="B580" t="n">
-        <v>56722</v>
+        <v>78546</v>
       </c>
       <c r="C580" t="inlineStr">
         <is>
@@ -63402,43 +63407,38 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E580" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I580" t="inlineStr"/>
-      <c r="M580" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P580" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q580" t="n">
-        <v>459593</v>
+        <v>459448</v>
       </c>
       <c r="R580" t="n">
-        <v>6807978</v>
+        <v>6808388</v>
       </c>
       <c r="S580" t="n">
         <v>10</v>
@@ -63490,7 +63490,7 @@
       </c>
       <c r="AX580" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY580" t="inlineStr"/>
@@ -66266,10 +66266,10 @@
     </row>
     <row r="608">
       <c r="A608" t="n">
-        <v>123920463</v>
+        <v>123920677</v>
       </c>
       <c r="B608" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C608" t="inlineStr">
         <is>
@@ -66278,43 +66278,38 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E608" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I608" t="inlineStr"/>
-      <c r="M608" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P608" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q608" t="n">
-        <v>459717</v>
+        <v>459121</v>
       </c>
       <c r="R608" t="n">
-        <v>6808604</v>
+        <v>6808649</v>
       </c>
       <c r="S608" t="n">
         <v>10</v>
@@ -66373,10 +66368,10 @@
     </row>
     <row r="609">
       <c r="A609" t="n">
-        <v>123920441</v>
+        <v>123920805</v>
       </c>
       <c r="B609" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C609" t="inlineStr">
         <is>
@@ -66385,43 +66380,38 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E609" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I609" t="inlineStr"/>
-      <c r="M609" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P609" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q609" t="n">
-        <v>459609</v>
+        <v>459076</v>
       </c>
       <c r="R609" t="n">
-        <v>6807987</v>
+        <v>6808337</v>
       </c>
       <c r="S609" t="n">
         <v>10</v>
@@ -66473,17 +66463,17 @@
       </c>
       <c r="AX609" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>123920445</v>
+        <v>123920811</v>
       </c>
       <c r="B610" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C610" t="inlineStr">
         <is>
@@ -66492,43 +66482,38 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E610" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I610" t="inlineStr"/>
-      <c r="M610" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P610" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q610" t="n">
-        <v>459187</v>
+        <v>459218</v>
       </c>
       <c r="R610" t="n">
-        <v>6808368</v>
+        <v>6808375</v>
       </c>
       <c r="S610" t="n">
         <v>10</v>
@@ -66580,17 +66565,17 @@
       </c>
       <c r="AX610" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>123920930</v>
+        <v>123920403</v>
       </c>
       <c r="B611" t="n">
-        <v>78455</v>
+        <v>79399</v>
       </c>
       <c r="C611" t="inlineStr">
         <is>
@@ -66603,21 +66588,21 @@
         </is>
       </c>
       <c r="E611" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I611" t="inlineStr"/>
@@ -66627,10 +66612,10 @@
         </is>
       </c>
       <c r="Q611" t="n">
-        <v>459600</v>
+        <v>458928</v>
       </c>
       <c r="R611" t="n">
-        <v>6807961</v>
+        <v>6808283</v>
       </c>
       <c r="S611" t="n">
         <v>10</v>
@@ -66682,17 +66667,17 @@
       </c>
       <c r="AX611" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Niklas Rehn, Håkan Thenander, lennart karlsson, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>123920677</v>
+        <v>123920540</v>
       </c>
       <c r="B612" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C612" t="inlineStr">
         <is>
@@ -66705,21 +66690,21 @@
         </is>
       </c>
       <c r="E612" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I612" t="inlineStr"/>
@@ -66729,10 +66714,10 @@
         </is>
       </c>
       <c r="Q612" t="n">
-        <v>459121</v>
+        <v>459589</v>
       </c>
       <c r="R612" t="n">
-        <v>6808649</v>
+        <v>6807980</v>
       </c>
       <c r="S612" t="n">
         <v>10</v>
@@ -66759,12 +66744,12 @@
       </c>
       <c r="Y612" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA612" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD612" t="b">
@@ -66784,17 +66769,17 @@
       </c>
       <c r="AX612" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY612" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" t="n">
-        <v>123920805</v>
+        <v>123920532</v>
       </c>
       <c r="B613" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C613" t="inlineStr">
         <is>
@@ -66807,21 +66792,21 @@
         </is>
       </c>
       <c r="E613" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I613" t="inlineStr"/>
@@ -66831,10 +66816,10 @@
         </is>
       </c>
       <c r="Q613" t="n">
-        <v>459076</v>
+        <v>459863</v>
       </c>
       <c r="R613" t="n">
-        <v>6808337</v>
+        <v>6808531</v>
       </c>
       <c r="S613" t="n">
         <v>10</v>
@@ -66861,12 +66846,12 @@
       </c>
       <c r="Y613" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA613" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD613" t="b">
@@ -66886,17 +66871,17 @@
       </c>
       <c r="AX613" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>123920811</v>
+        <v>123920930</v>
       </c>
       <c r="B614" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C614" t="inlineStr">
         <is>
@@ -66909,21 +66894,21 @@
         </is>
       </c>
       <c r="E614" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I614" t="inlineStr"/>
@@ -66933,10 +66918,10 @@
         </is>
       </c>
       <c r="Q614" t="n">
-        <v>459218</v>
+        <v>459600</v>
       </c>
       <c r="R614" t="n">
-        <v>6808375</v>
+        <v>6807961</v>
       </c>
       <c r="S614" t="n">
         <v>10</v>
@@ -66988,17 +66973,17 @@
       </c>
       <c r="AX614" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Niklas Rehn, Håkan Thenander, lennart karlsson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>123920403</v>
+        <v>123920463</v>
       </c>
       <c r="B615" t="n">
-        <v>79399</v>
+        <v>56722</v>
       </c>
       <c r="C615" t="inlineStr">
         <is>
@@ -67007,38 +66992,43 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E615" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I615" t="inlineStr"/>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P615" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q615" t="n">
-        <v>458928</v>
+        <v>459717</v>
       </c>
       <c r="R615" t="n">
-        <v>6808283</v>
+        <v>6808604</v>
       </c>
       <c r="S615" t="n">
         <v>10</v>
@@ -67065,12 +67055,12 @@
       </c>
       <c r="Y615" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA615" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD615" t="b">
@@ -67090,17 +67080,17 @@
       </c>
       <c r="AX615" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" t="n">
-        <v>123920540</v>
+        <v>123920441</v>
       </c>
       <c r="B616" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C616" t="inlineStr">
         <is>
@@ -67109,38 +67099,43 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E616" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I616" t="inlineStr"/>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P616" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q616" t="n">
-        <v>459589</v>
+        <v>459609</v>
       </c>
       <c r="R616" t="n">
-        <v>6807980</v>
+        <v>6807987</v>
       </c>
       <c r="S616" t="n">
         <v>10</v>
@@ -67192,17 +67187,17 @@
       </c>
       <c r="AX616" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>123920532</v>
+        <v>123920445</v>
       </c>
       <c r="B617" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C617" t="inlineStr">
         <is>
@@ -67211,38 +67206,43 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E617" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I617" t="inlineStr"/>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P617" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q617" t="n">
-        <v>459863</v>
+        <v>459187</v>
       </c>
       <c r="R617" t="n">
-        <v>6808531</v>
+        <v>6808368</v>
       </c>
       <c r="S617" t="n">
         <v>10</v>
@@ -67269,12 +67269,12 @@
       </c>
       <c r="Y617" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA617" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD617" t="b">
@@ -67294,17 +67294,17 @@
       </c>
       <c r="AX617" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>123920917</v>
+        <v>123920304</v>
       </c>
       <c r="B618" t="n">
-        <v>88359</v>
+        <v>79428</v>
       </c>
       <c r="C618" t="inlineStr">
         <is>
@@ -67317,21 +67317,21 @@
         </is>
       </c>
       <c r="E618" t="n">
-        <v>510</v>
+        <v>6453</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I618" t="inlineStr"/>
@@ -67341,10 +67341,10 @@
         </is>
       </c>
       <c r="Q618" t="n">
-        <v>459786</v>
+        <v>458899</v>
       </c>
       <c r="R618" t="n">
-        <v>6808645</v>
+        <v>6808695</v>
       </c>
       <c r="S618" t="n">
         <v>10</v>
@@ -67403,7 +67403,7 @@
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>123920684</v>
+        <v>123920803</v>
       </c>
       <c r="B619" t="n">
         <v>78810</v>
@@ -67443,10 +67443,10 @@
         </is>
       </c>
       <c r="Q619" t="n">
-        <v>459414</v>
+        <v>459061</v>
       </c>
       <c r="R619" t="n">
-        <v>6808641</v>
+        <v>6808332</v>
       </c>
       <c r="S619" t="n">
         <v>10</v>
@@ -67473,12 +67473,12 @@
       </c>
       <c r="Y619" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA619" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD619" t="b">
@@ -67498,17 +67498,17 @@
       </c>
       <c r="AX619" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>123920304</v>
+        <v>123920789</v>
       </c>
       <c r="B620" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C620" t="inlineStr">
         <is>
@@ -67521,21 +67521,21 @@
         </is>
       </c>
       <c r="E620" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I620" t="inlineStr"/>
@@ -67545,10 +67545,10 @@
         </is>
       </c>
       <c r="Q620" t="n">
-        <v>458899</v>
+        <v>458861</v>
       </c>
       <c r="R620" t="n">
-        <v>6808695</v>
+        <v>6808246</v>
       </c>
       <c r="S620" t="n">
         <v>10</v>
@@ -67575,12 +67575,12 @@
       </c>
       <c r="Y620" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA620" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD620" t="b">
@@ -67600,14 +67600,14 @@
       </c>
       <c r="AX620" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>123920449</v>
+        <v>123920434</v>
       </c>
       <c r="B621" t="n">
         <v>56722</v>
@@ -67643,7 +67643,7 @@
       <c r="I621" t="inlineStr"/>
       <c r="M621" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P621" t="inlineStr">
@@ -67652,10 +67652,10 @@
         </is>
       </c>
       <c r="Q621" t="n">
-        <v>458862</v>
+        <v>459116</v>
       </c>
       <c r="R621" t="n">
-        <v>6808791</v>
+        <v>6808108</v>
       </c>
       <c r="S621" t="n">
         <v>10</v>
@@ -67682,12 +67682,12 @@
       </c>
       <c r="Y621" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA621" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD621" t="b">
@@ -67707,14 +67707,14 @@
       </c>
       <c r="AX621" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" t="n">
-        <v>123920434</v>
+        <v>123920435</v>
       </c>
       <c r="B622" t="n">
         <v>56722</v>
@@ -67759,10 +67759,10 @@
         </is>
       </c>
       <c r="Q622" t="n">
-        <v>459116</v>
+        <v>459840</v>
       </c>
       <c r="R622" t="n">
-        <v>6808108</v>
+        <v>6808557</v>
       </c>
       <c r="S622" t="n">
         <v>10</v>
@@ -67789,12 +67789,12 @@
       </c>
       <c r="Y622" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA622" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD622" t="b">
@@ -67814,17 +67814,17 @@
       </c>
       <c r="AX622" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY622" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>123920435</v>
+        <v>123920408</v>
       </c>
       <c r="B623" t="n">
-        <v>56722</v>
+        <v>79399</v>
       </c>
       <c r="C623" t="inlineStr">
         <is>
@@ -67833,43 +67833,38 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E623" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I623" t="inlineStr"/>
-      <c r="M623" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P623" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q623" t="n">
-        <v>459840</v>
+        <v>459598</v>
       </c>
       <c r="R623" t="n">
-        <v>6808557</v>
+        <v>6808240</v>
       </c>
       <c r="S623" t="n">
         <v>10</v>
@@ -67896,12 +67891,12 @@
       </c>
       <c r="Y623" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA623" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD623" t="b">
@@ -67921,17 +67916,17 @@
       </c>
       <c r="AX623" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>123920456</v>
+        <v>123920523</v>
       </c>
       <c r="B624" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C624" t="inlineStr">
         <is>
@@ -67940,43 +67935,38 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E624" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I624" t="inlineStr"/>
-      <c r="M624" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P624" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q624" t="n">
-        <v>458796</v>
+        <v>458899</v>
       </c>
       <c r="R624" t="n">
-        <v>6808681</v>
+        <v>6808695</v>
       </c>
       <c r="S624" t="n">
         <v>10</v>
@@ -68035,10 +68025,10 @@
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>123920408</v>
+        <v>123920917</v>
       </c>
       <c r="B625" t="n">
-        <v>79399</v>
+        <v>88359</v>
       </c>
       <c r="C625" t="inlineStr">
         <is>
@@ -68051,21 +68041,21 @@
         </is>
       </c>
       <c r="E625" t="n">
-        <v>229821</v>
+        <v>510</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I625" t="inlineStr"/>
@@ -68075,10 +68065,10 @@
         </is>
       </c>
       <c r="Q625" t="n">
-        <v>459598</v>
+        <v>459786</v>
       </c>
       <c r="R625" t="n">
-        <v>6808240</v>
+        <v>6808645</v>
       </c>
       <c r="S625" t="n">
         <v>10</v>
@@ -68105,12 +68095,12 @@
       </c>
       <c r="Y625" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA625" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD625" t="b">
@@ -68130,17 +68120,17 @@
       </c>
       <c r="AX625" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>123920523</v>
+        <v>123920684</v>
       </c>
       <c r="B626" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C626" t="inlineStr">
         <is>
@@ -68153,21 +68143,21 @@
         </is>
       </c>
       <c r="E626" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I626" t="inlineStr"/>
@@ -68177,10 +68167,10 @@
         </is>
       </c>
       <c r="Q626" t="n">
-        <v>458899</v>
+        <v>459414</v>
       </c>
       <c r="R626" t="n">
-        <v>6808695</v>
+        <v>6808641</v>
       </c>
       <c r="S626" t="n">
         <v>10</v>
@@ -68749,10 +68739,10 @@
     </row>
     <row r="632">
       <c r="A632" t="n">
-        <v>123920803</v>
+        <v>123920449</v>
       </c>
       <c r="B632" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C632" t="inlineStr">
         <is>
@@ -68761,38 +68751,43 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E632" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I632" t="inlineStr"/>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P632" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q632" t="n">
-        <v>459061</v>
+        <v>458862</v>
       </c>
       <c r="R632" t="n">
-        <v>6808332</v>
+        <v>6808791</v>
       </c>
       <c r="S632" t="n">
         <v>10</v>
@@ -68819,12 +68814,12 @@
       </c>
       <c r="Y632" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA632" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD632" t="b">
@@ -68844,17 +68839,17 @@
       </c>
       <c r="AX632" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="n">
-        <v>123920789</v>
+        <v>123920456</v>
       </c>
       <c r="B633" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C633" t="inlineStr">
         <is>
@@ -68863,38 +68858,43 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E633" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I633" t="inlineStr"/>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P633" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q633" t="n">
-        <v>458861</v>
+        <v>458796</v>
       </c>
       <c r="R633" t="n">
-        <v>6808246</v>
+        <v>6808681</v>
       </c>
       <c r="S633" t="n">
         <v>10</v>
@@ -68921,12 +68921,12 @@
       </c>
       <c r="Y633" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA633" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD633" t="b">
@@ -68946,7 +68946,7 @@
       </c>
       <c r="AX633" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY633" t="inlineStr"/>
@@ -70386,7 +70386,7 @@
     </row>
     <row r="648">
       <c r="A648" t="n">
-        <v>123920807</v>
+        <v>123920794</v>
       </c>
       <c r="B648" t="n">
         <v>78810</v>
@@ -70426,10 +70426,10 @@
         </is>
       </c>
       <c r="Q648" t="n">
-        <v>459115</v>
+        <v>458919</v>
       </c>
       <c r="R648" t="n">
-        <v>6808339</v>
+        <v>6808281</v>
       </c>
       <c r="S648" t="n">
         <v>10</v>
@@ -70488,10 +70488,10 @@
     </row>
     <row r="649">
       <c r="A649" t="n">
-        <v>123920466</v>
+        <v>123920807</v>
       </c>
       <c r="B649" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C649" t="inlineStr">
         <is>
@@ -70500,43 +70500,38 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E649" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I649" t="inlineStr"/>
-      <c r="M649" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P649" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q649" t="n">
-        <v>459735</v>
+        <v>459115</v>
       </c>
       <c r="R649" t="n">
-        <v>6808618</v>
+        <v>6808339</v>
       </c>
       <c r="S649" t="n">
         <v>10</v>
@@ -70563,12 +70558,12 @@
       </c>
       <c r="Y649" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA649" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD649" t="b">
@@ -70588,17 +70583,17 @@
       </c>
       <c r="AX649" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" t="n">
-        <v>123920547</v>
+        <v>123920466</v>
       </c>
       <c r="B650" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C650" t="inlineStr">
         <is>
@@ -70607,38 +70602,43 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E650" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I650" t="inlineStr"/>
+      <c r="M650" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P650" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q650" t="n">
-        <v>459076</v>
+        <v>459735</v>
       </c>
       <c r="R650" t="n">
-        <v>6808337</v>
+        <v>6808618</v>
       </c>
       <c r="S650" t="n">
         <v>10</v>
@@ -70665,12 +70665,12 @@
       </c>
       <c r="Y650" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA650" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD650" t="b">
@@ -70690,17 +70690,17 @@
       </c>
       <c r="AX650" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY650" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>123920395</v>
+        <v>123920573</v>
       </c>
       <c r="B651" t="n">
-        <v>79399</v>
+        <v>80763</v>
       </c>
       <c r="C651" t="inlineStr">
         <is>
@@ -70713,21 +70713,21 @@
         </is>
       </c>
       <c r="E651" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I651" t="inlineStr"/>
@@ -70737,10 +70737,10 @@
         </is>
       </c>
       <c r="Q651" t="n">
-        <v>459512</v>
+        <v>458988</v>
       </c>
       <c r="R651" t="n">
-        <v>6808645</v>
+        <v>6808278</v>
       </c>
       <c r="S651" t="n">
         <v>10</v>
@@ -70767,12 +70767,12 @@
       </c>
       <c r="Y651" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA651" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD651" t="b">
@@ -70792,17 +70792,17 @@
       </c>
       <c r="AX651" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>123920573</v>
+        <v>123920361</v>
       </c>
       <c r="B652" t="n">
-        <v>80763</v>
+        <v>78842</v>
       </c>
       <c r="C652" t="inlineStr">
         <is>
@@ -70815,21 +70815,21 @@
         </is>
       </c>
       <c r="E652" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I652" t="inlineStr"/>
@@ -70839,10 +70839,10 @@
         </is>
       </c>
       <c r="Q652" t="n">
-        <v>458988</v>
+        <v>459744</v>
       </c>
       <c r="R652" t="n">
-        <v>6808278</v>
+        <v>6808628</v>
       </c>
       <c r="S652" t="n">
         <v>10</v>
@@ -70869,12 +70869,12 @@
       </c>
       <c r="Y652" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA652" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD652" t="b">
@@ -70894,17 +70894,17 @@
       </c>
       <c r="AX652" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY652" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>123920361</v>
+        <v>123920316</v>
       </c>
       <c r="B653" t="n">
-        <v>78842</v>
+        <v>79428</v>
       </c>
       <c r="C653" t="inlineStr">
         <is>
@@ -70917,21 +70917,21 @@
         </is>
       </c>
       <c r="E653" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I653" t="inlineStr"/>
@@ -70941,10 +70941,10 @@
         </is>
       </c>
       <c r="Q653" t="n">
-        <v>459744</v>
+        <v>459455</v>
       </c>
       <c r="R653" t="n">
-        <v>6808628</v>
+        <v>6808627</v>
       </c>
       <c r="S653" t="n">
         <v>10</v>
@@ -71003,10 +71003,10 @@
     </row>
     <row r="654">
       <c r="A654" t="n">
-        <v>123920316</v>
+        <v>123920812</v>
       </c>
       <c r="B654" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C654" t="inlineStr">
         <is>
@@ -71019,21 +71019,21 @@
         </is>
       </c>
       <c r="E654" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I654" t="inlineStr"/>
@@ -71043,10 +71043,10 @@
         </is>
       </c>
       <c r="Q654" t="n">
-        <v>459455</v>
+        <v>459239</v>
       </c>
       <c r="R654" t="n">
-        <v>6808627</v>
+        <v>6808359</v>
       </c>
       <c r="S654" t="n">
         <v>10</v>
@@ -71073,12 +71073,12 @@
       </c>
       <c r="Y654" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA654" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD654" t="b">
@@ -71098,17 +71098,17 @@
       </c>
       <c r="AX654" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY654" t="inlineStr"/>
     </row>
     <row r="655">
       <c r="A655" t="n">
-        <v>123920812</v>
+        <v>123920592</v>
       </c>
       <c r="B655" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C655" t="inlineStr">
         <is>
@@ -71121,21 +71121,21 @@
         </is>
       </c>
       <c r="E655" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I655" t="inlineStr"/>
@@ -71145,10 +71145,10 @@
         </is>
       </c>
       <c r="Q655" t="n">
-        <v>459239</v>
+        <v>459228</v>
       </c>
       <c r="R655" t="n">
-        <v>6808359</v>
+        <v>6808636</v>
       </c>
       <c r="S655" t="n">
         <v>10</v>
@@ -71175,12 +71175,12 @@
       </c>
       <c r="Y655" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA655" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD655" t="b">
@@ -71200,17 +71200,17 @@
       </c>
       <c r="AX655" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY655" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>123920592</v>
+        <v>123920321</v>
       </c>
       <c r="B656" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C656" t="inlineStr">
         <is>
@@ -71223,21 +71223,21 @@
         </is>
       </c>
       <c r="E656" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I656" t="inlineStr"/>
@@ -71247,10 +71247,10 @@
         </is>
       </c>
       <c r="Q656" t="n">
-        <v>459228</v>
+        <v>459817</v>
       </c>
       <c r="R656" t="n">
-        <v>6808636</v>
+        <v>6808649</v>
       </c>
       <c r="S656" t="n">
         <v>10</v>
@@ -71309,10 +71309,10 @@
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>123920321</v>
+        <v>123920547</v>
       </c>
       <c r="B657" t="n">
-        <v>79428</v>
+        <v>78547</v>
       </c>
       <c r="C657" t="inlineStr">
         <is>
@@ -71325,21 +71325,21 @@
         </is>
       </c>
       <c r="E657" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I657" t="inlineStr"/>
@@ -71349,10 +71349,10 @@
         </is>
       </c>
       <c r="Q657" t="n">
-        <v>459817</v>
+        <v>459076</v>
       </c>
       <c r="R657" t="n">
-        <v>6808649</v>
+        <v>6808337</v>
       </c>
       <c r="S657" t="n">
         <v>10</v>
@@ -71379,12 +71379,12 @@
       </c>
       <c r="Y657" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA657" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD657" t="b">
@@ -71404,17 +71404,17 @@
       </c>
       <c r="AX657" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY657" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>123920794</v>
+        <v>123920395</v>
       </c>
       <c r="B658" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C658" t="inlineStr">
         <is>
@@ -71427,21 +71427,21 @@
         </is>
       </c>
       <c r="E658" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I658" t="inlineStr"/>
@@ -71451,10 +71451,10 @@
         </is>
       </c>
       <c r="Q658" t="n">
-        <v>458919</v>
+        <v>459512</v>
       </c>
       <c r="R658" t="n">
-        <v>6808281</v>
+        <v>6808645</v>
       </c>
       <c r="S658" t="n">
         <v>10</v>
@@ -71481,12 +71481,12 @@
       </c>
       <c r="Y658" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA658" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD658" t="b">
@@ -71506,7 +71506,7 @@
       </c>
       <c r="AX658" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY658" t="inlineStr"/>
@@ -78519,10 +78519,10 @@
     </row>
     <row r="727">
       <c r="A727" t="n">
-        <v>123920444</v>
+        <v>123920370</v>
       </c>
       <c r="B727" t="n">
-        <v>56722</v>
+        <v>78842</v>
       </c>
       <c r="C727" t="inlineStr">
         <is>
@@ -78531,43 +78531,38 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E727" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I727" t="inlineStr"/>
-      <c r="M727" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P727" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q727" t="n">
-        <v>459153</v>
+        <v>459007</v>
       </c>
       <c r="R727" t="n">
-        <v>6808356</v>
+        <v>6808305</v>
       </c>
       <c r="S727" t="n">
         <v>10</v>
@@ -78626,10 +78621,10 @@
     </row>
     <row r="728">
       <c r="A728" t="n">
-        <v>123920549</v>
+        <v>123920591</v>
       </c>
       <c r="B728" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C728" t="inlineStr">
         <is>
@@ -78642,21 +78637,21 @@
         </is>
       </c>
       <c r="E728" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I728" t="inlineStr"/>
@@ -78666,10 +78661,10 @@
         </is>
       </c>
       <c r="Q728" t="n">
-        <v>459425</v>
+        <v>459083</v>
       </c>
       <c r="R728" t="n">
-        <v>6808381</v>
+        <v>6808668</v>
       </c>
       <c r="S728" t="n">
         <v>10</v>
@@ -78696,12 +78691,12 @@
       </c>
       <c r="Y728" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA728" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD728" t="b">
@@ -78721,17 +78716,17 @@
       </c>
       <c r="AX728" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY728" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" t="n">
-        <v>123920525</v>
+        <v>123920940</v>
       </c>
       <c r="B729" t="n">
-        <v>78547</v>
+        <v>78194</v>
       </c>
       <c r="C729" t="inlineStr">
         <is>
@@ -78744,21 +78739,21 @@
         </is>
       </c>
       <c r="E729" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I729" t="inlineStr"/>
@@ -78768,10 +78763,10 @@
         </is>
       </c>
       <c r="Q729" t="n">
-        <v>459300</v>
+        <v>459783</v>
       </c>
       <c r="R729" t="n">
-        <v>6808710</v>
+        <v>6808682</v>
       </c>
       <c r="S729" t="n">
         <v>10</v>
@@ -78830,10 +78825,10 @@
     </row>
     <row r="730">
       <c r="A730" t="n">
-        <v>123920406</v>
+        <v>123920327</v>
       </c>
       <c r="B730" t="n">
-        <v>79399</v>
+        <v>79428</v>
       </c>
       <c r="C730" t="inlineStr">
         <is>
@@ -78846,21 +78841,21 @@
         </is>
       </c>
       <c r="E730" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I730" t="inlineStr"/>
@@ -78870,10 +78865,10 @@
         </is>
       </c>
       <c r="Q730" t="n">
-        <v>459448</v>
+        <v>459583</v>
       </c>
       <c r="R730" t="n">
-        <v>6808388</v>
+        <v>6808141</v>
       </c>
       <c r="S730" t="n">
         <v>10</v>
@@ -78932,10 +78927,10 @@
     </row>
     <row r="731">
       <c r="A731" t="n">
-        <v>123920370</v>
+        <v>123920827</v>
       </c>
       <c r="B731" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C731" t="inlineStr">
         <is>
@@ -78948,21 +78943,21 @@
         </is>
       </c>
       <c r="E731" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I731" t="inlineStr"/>
@@ -78972,10 +78967,10 @@
         </is>
       </c>
       <c r="Q731" t="n">
-        <v>459007</v>
+        <v>459598</v>
       </c>
       <c r="R731" t="n">
-        <v>6808305</v>
+        <v>6808240</v>
       </c>
       <c r="S731" t="n">
         <v>10</v>
@@ -79027,17 +79022,17 @@
       </c>
       <c r="AX731" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY731" t="inlineStr"/>
     </row>
     <row r="732">
       <c r="A732" t="n">
-        <v>123920591</v>
+        <v>123920799</v>
       </c>
       <c r="B732" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C732" t="inlineStr">
         <is>
@@ -79050,21 +79045,21 @@
         </is>
       </c>
       <c r="E732" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I732" t="inlineStr"/>
@@ -79074,10 +79069,10 @@
         </is>
       </c>
       <c r="Q732" t="n">
-        <v>459083</v>
+        <v>459007</v>
       </c>
       <c r="R732" t="n">
-        <v>6808668</v>
+        <v>6808305</v>
       </c>
       <c r="S732" t="n">
         <v>10</v>
@@ -79104,12 +79099,12 @@
       </c>
       <c r="Y732" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA732" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD732" t="b">
@@ -79129,17 +79124,17 @@
       </c>
       <c r="AX732" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY732" t="inlineStr"/>
     </row>
     <row r="733">
       <c r="A733" t="n">
-        <v>123920940</v>
+        <v>123920830</v>
       </c>
       <c r="B733" t="n">
-        <v>78194</v>
+        <v>78810</v>
       </c>
       <c r="C733" t="inlineStr">
         <is>
@@ -79152,21 +79147,21 @@
         </is>
       </c>
       <c r="E733" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I733" t="inlineStr"/>
@@ -79176,10 +79171,10 @@
         </is>
       </c>
       <c r="Q733" t="n">
-        <v>459783</v>
+        <v>459650</v>
       </c>
       <c r="R733" t="n">
-        <v>6808682</v>
+        <v>6808252</v>
       </c>
       <c r="S733" t="n">
         <v>10</v>
@@ -79206,12 +79201,12 @@
       </c>
       <c r="Y733" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA733" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD733" t="b">
@@ -79231,17 +79226,17 @@
       </c>
       <c r="AX733" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY733" t="inlineStr"/>
     </row>
     <row r="734">
       <c r="A734" t="n">
-        <v>123920327</v>
+        <v>123920825</v>
       </c>
       <c r="B734" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C734" t="inlineStr">
         <is>
@@ -79254,21 +79249,21 @@
         </is>
       </c>
       <c r="E734" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I734" t="inlineStr"/>
@@ -79278,10 +79273,10 @@
         </is>
       </c>
       <c r="Q734" t="n">
-        <v>459583</v>
+        <v>459553</v>
       </c>
       <c r="R734" t="n">
-        <v>6808141</v>
+        <v>6808240</v>
       </c>
       <c r="S734" t="n">
         <v>10</v>
@@ -79333,14 +79328,14 @@
       </c>
       <c r="AX734" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY734" t="inlineStr"/>
     </row>
     <row r="735">
       <c r="A735" t="n">
-        <v>123920827</v>
+        <v>123920828</v>
       </c>
       <c r="B735" t="n">
         <v>78810</v>
@@ -79380,10 +79375,10 @@
         </is>
       </c>
       <c r="Q735" t="n">
-        <v>459598</v>
+        <v>459599</v>
       </c>
       <c r="R735" t="n">
-        <v>6808240</v>
+        <v>6808237</v>
       </c>
       <c r="S735" t="n">
         <v>10</v>
@@ -79442,7 +79437,7 @@
     </row>
     <row r="736">
       <c r="A736" t="n">
-        <v>123920799</v>
+        <v>123920670</v>
       </c>
       <c r="B736" t="n">
         <v>78810</v>
@@ -79482,10 +79477,10 @@
         </is>
       </c>
       <c r="Q736" t="n">
-        <v>459007</v>
+        <v>458914</v>
       </c>
       <c r="R736" t="n">
-        <v>6808305</v>
+        <v>6808701</v>
       </c>
       <c r="S736" t="n">
         <v>10</v>
@@ -79512,12 +79507,12 @@
       </c>
       <c r="Y736" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA736" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD736" t="b">
@@ -79537,14 +79532,14 @@
       </c>
       <c r="AX736" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY736" t="inlineStr"/>
     </row>
     <row r="737">
       <c r="A737" t="n">
-        <v>123920830</v>
+        <v>123920801</v>
       </c>
       <c r="B737" t="n">
         <v>78810</v>
@@ -79584,10 +79579,10 @@
         </is>
       </c>
       <c r="Q737" t="n">
-        <v>459650</v>
+        <v>459014</v>
       </c>
       <c r="R737" t="n">
-        <v>6808252</v>
+        <v>6808348</v>
       </c>
       <c r="S737" t="n">
         <v>10</v>
@@ -79646,7 +79641,7 @@
     </row>
     <row r="738">
       <c r="A738" t="n">
-        <v>123920825</v>
+        <v>123920687</v>
       </c>
       <c r="B738" t="n">
         <v>78810</v>
@@ -79686,10 +79681,10 @@
         </is>
       </c>
       <c r="Q738" t="n">
-        <v>459553</v>
+        <v>459508</v>
       </c>
       <c r="R738" t="n">
-        <v>6808240</v>
+        <v>6808645</v>
       </c>
       <c r="S738" t="n">
         <v>10</v>
@@ -79716,12 +79711,12 @@
       </c>
       <c r="Y738" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA738" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD738" t="b">
@@ -79741,17 +79736,17 @@
       </c>
       <c r="AX738" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY738" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" t="n">
-        <v>123920828</v>
+        <v>123920444</v>
       </c>
       <c r="B739" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C739" t="inlineStr">
         <is>
@@ -79760,38 +79755,43 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E739" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I739" t="inlineStr"/>
+      <c r="M739" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P739" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q739" t="n">
-        <v>459599</v>
+        <v>459153</v>
       </c>
       <c r="R739" t="n">
-        <v>6808237</v>
+        <v>6808356</v>
       </c>
       <c r="S739" t="n">
         <v>10</v>
@@ -79843,17 +79843,17 @@
       </c>
       <c r="AX739" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY739" t="inlineStr"/>
     </row>
     <row r="740">
       <c r="A740" t="n">
-        <v>123920670</v>
+        <v>123920570</v>
       </c>
       <c r="B740" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C740" t="inlineStr">
         <is>
@@ -79862,25 +79862,25 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E740" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I740" t="inlineStr"/>
@@ -79890,10 +79890,10 @@
         </is>
       </c>
       <c r="Q740" t="n">
-        <v>458914</v>
+        <v>459727</v>
       </c>
       <c r="R740" t="n">
-        <v>6808701</v>
+        <v>6808650</v>
       </c>
       <c r="S740" t="n">
         <v>10</v>
@@ -79952,10 +79952,10 @@
     </row>
     <row r="741">
       <c r="A741" t="n">
-        <v>123920801</v>
+        <v>123920549</v>
       </c>
       <c r="B741" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C741" t="inlineStr">
         <is>
@@ -79968,21 +79968,21 @@
         </is>
       </c>
       <c r="E741" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I741" t="inlineStr"/>
@@ -79992,10 +79992,10 @@
         </is>
       </c>
       <c r="Q741" t="n">
-        <v>459014</v>
+        <v>459425</v>
       </c>
       <c r="R741" t="n">
-        <v>6808348</v>
+        <v>6808381</v>
       </c>
       <c r="S741" t="n">
         <v>10</v>
@@ -80054,10 +80054,10 @@
     </row>
     <row r="742">
       <c r="A742" t="n">
-        <v>123920687</v>
+        <v>123920525</v>
       </c>
       <c r="B742" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C742" t="inlineStr">
         <is>
@@ -80070,21 +80070,21 @@
         </is>
       </c>
       <c r="E742" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I742" t="inlineStr"/>
@@ -80094,10 +80094,10 @@
         </is>
       </c>
       <c r="Q742" t="n">
-        <v>459508</v>
+        <v>459300</v>
       </c>
       <c r="R742" t="n">
-        <v>6808645</v>
+        <v>6808710</v>
       </c>
       <c r="S742" t="n">
         <v>10</v>
@@ -80156,10 +80156,10 @@
     </row>
     <row r="743">
       <c r="A743" t="n">
-        <v>123920570</v>
+        <v>123920406</v>
       </c>
       <c r="B743" t="n">
-        <v>57883</v>
+        <v>79399</v>
       </c>
       <c r="C743" t="inlineStr">
         <is>
@@ -80168,25 +80168,25 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E743" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I743" t="inlineStr"/>
@@ -80196,10 +80196,10 @@
         </is>
       </c>
       <c r="Q743" t="n">
-        <v>459727</v>
+        <v>459448</v>
       </c>
       <c r="R743" t="n">
-        <v>6808650</v>
+        <v>6808388</v>
       </c>
       <c r="S743" t="n">
         <v>10</v>
@@ -80226,12 +80226,12 @@
       </c>
       <c r="Y743" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA743" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD743" t="b">
@@ -80251,7 +80251,7 @@
       </c>
       <c r="AX743" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY743" t="inlineStr"/>

--- a/artfynd/A 13728-2025 artfynd.xlsx
+++ b/artfynd/A 13728-2025 artfynd.xlsx
@@ -80258,10 +80258,10 @@
     </row>
     <row r="744">
       <c r="A744" t="n">
-        <v>123564139</v>
+        <v>123565682</v>
       </c>
       <c r="B744" t="n">
-        <v>57513</v>
+        <v>78547</v>
       </c>
       <c r="C744" t="inlineStr">
         <is>
@@ -80274,21 +80274,21 @@
         </is>
       </c>
       <c r="E744" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I744" t="inlineStr"/>
@@ -80298,10 +80298,10 @@
         </is>
       </c>
       <c r="Q744" t="n">
-        <v>459734</v>
+        <v>459687</v>
       </c>
       <c r="R744" t="n">
-        <v>6808851</v>
+        <v>6808829</v>
       </c>
       <c r="S744" t="n">
         <v>11</v>
@@ -80333,7 +80333,7 @@
       </c>
       <c r="Z744" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA744" t="inlineStr">
@@ -80343,7 +80343,7 @@
       </c>
       <c r="AB744" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD744" t="b">
@@ -80370,10 +80370,10 @@
     </row>
     <row r="745">
       <c r="A745" t="n">
-        <v>123565682</v>
+        <v>123564139</v>
       </c>
       <c r="B745" t="n">
-        <v>78547</v>
+        <v>57513</v>
       </c>
       <c r="C745" t="inlineStr">
         <is>
@@ -80386,21 +80386,21 @@
         </is>
       </c>
       <c r="E745" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I745" t="inlineStr"/>
@@ -80410,10 +80410,10 @@
         </is>
       </c>
       <c r="Q745" t="n">
-        <v>459687</v>
+        <v>459734</v>
       </c>
       <c r="R745" t="n">
-        <v>6808829</v>
+        <v>6808851</v>
       </c>
       <c r="S745" t="n">
         <v>11</v>
@@ -80445,7 +80445,7 @@
       </c>
       <c r="Z745" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA745" t="inlineStr">
@@ -80455,7 +80455,7 @@
       </c>
       <c r="AB745" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD745" t="b">

--- a/artfynd/A 13728-2025 artfynd.xlsx
+++ b/artfynd/A 13728-2025 artfynd.xlsx
@@ -80258,10 +80258,10 @@
     </row>
     <row r="744">
       <c r="A744" t="n">
-        <v>123565682</v>
+        <v>123564139</v>
       </c>
       <c r="B744" t="n">
-        <v>78547</v>
+        <v>57513</v>
       </c>
       <c r="C744" t="inlineStr">
         <is>
@@ -80274,21 +80274,21 @@
         </is>
       </c>
       <c r="E744" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I744" t="inlineStr"/>
@@ -80298,10 +80298,10 @@
         </is>
       </c>
       <c r="Q744" t="n">
-        <v>459687</v>
+        <v>459734</v>
       </c>
       <c r="R744" t="n">
-        <v>6808829</v>
+        <v>6808851</v>
       </c>
       <c r="S744" t="n">
         <v>11</v>
@@ -80333,7 +80333,7 @@
       </c>
       <c r="Z744" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA744" t="inlineStr">
@@ -80343,7 +80343,7 @@
       </c>
       <c r="AB744" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD744" t="b">
@@ -80370,10 +80370,10 @@
     </row>
     <row r="745">
       <c r="A745" t="n">
-        <v>123564139</v>
+        <v>123565682</v>
       </c>
       <c r="B745" t="n">
-        <v>57513</v>
+        <v>78547</v>
       </c>
       <c r="C745" t="inlineStr">
         <is>
@@ -80386,21 +80386,21 @@
         </is>
       </c>
       <c r="E745" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I745" t="inlineStr"/>
@@ -80410,10 +80410,10 @@
         </is>
       </c>
       <c r="Q745" t="n">
-        <v>459734</v>
+        <v>459687</v>
       </c>
       <c r="R745" t="n">
-        <v>6808851</v>
+        <v>6808829</v>
       </c>
       <c r="S745" t="n">
         <v>11</v>
@@ -80445,7 +80445,7 @@
       </c>
       <c r="Z745" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA745" t="inlineStr">
@@ -80455,7 +80455,7 @@
       </c>
       <c r="AB745" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD745" t="b">

--- a/artfynd/A 13728-2025 artfynd.xlsx
+++ b/artfynd/A 13728-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY745"/>
+  <dimension ref="A1:AY746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80480,6 +80480,118 @@
       </c>
       <c r="AY745" t="inlineStr"/>
     </row>
+    <row r="746">
+      <c r="A746" t="n">
+        <v>123825901</v>
+      </c>
+      <c r="B746" t="n">
+        <v>57811</v>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E746" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr"/>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P746" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q746" t="n">
+        <v>458873</v>
+      </c>
+      <c r="R746" t="n">
+        <v>6809079</v>
+      </c>
+      <c r="S746" t="n">
+        <v>15</v>
+      </c>
+      <c r="T746" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U746" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V746" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W746" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y746" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z746" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA746" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB746" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AD746" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE746" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG746" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT746" t="inlineStr"/>
+      <c r="AW746" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX746" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY746" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13728-2025 artfynd.xlsx
+++ b/artfynd/A 13728-2025 artfynd.xlsx
@@ -80485,7 +80485,7 @@
         <v>123825901</v>
       </c>
       <c r="B746" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>

--- a/artfynd/A 13728-2025 artfynd.xlsx
+++ b/artfynd/A 13728-2025 artfynd.xlsx
@@ -80485,7 +80485,7 @@
         <v>123825901</v>
       </c>
       <c r="B746" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>

--- a/artfynd/A 13728-2025 artfynd.xlsx
+++ b/artfynd/A 13728-2025 artfynd.xlsx
@@ -80485,7 +80485,7 @@
         <v>123825901</v>
       </c>
       <c r="B746" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>

--- a/artfynd/A 13728-2025 artfynd.xlsx
+++ b/artfynd/A 13728-2025 artfynd.xlsx
@@ -22414,7 +22414,7 @@
         <v>0</v>
       </c>
       <c r="AE193" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG193" t="b">
         <v>0</v>
@@ -31435,7 +31435,7 @@
         <v>0</v>
       </c>
       <c r="AE274" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG274" t="b">
         <v>0</v>
